--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8594" uniqueCount="1234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8866" uniqueCount="1249">
   <si>
     <t>S.No</t>
   </si>
@@ -3713,6 +3713,51 @@
   </si>
   <si>
     <t>Decorative Colour Bank (Safoora Chawrangi)</t>
+  </si>
+  <si>
+    <t>22/07/2026, 10:56:04 am</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1967 PEANUT SHELL-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 04 CREAM-G</t>
+  </si>
+  <si>
+    <t>EXTRA 3IN1 PLASTIC PASTE BS-1 PLAIN-Q</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1918 BLUE MAGIC-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 02 ASH WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 2685 CAMEO-D</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 301 MORNING GREY-D</t>
+  </si>
+  <si>
+    <t>22/07/2026, 11:06:52 am</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 320 LEMON-Q</t>
+  </si>
+  <si>
+    <t>22/07/2026, 11:32:51 am</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI U8764 AZALEA-G</t>
+  </si>
+  <si>
+    <t>22/07/2026, 11:37:26 am</t>
+  </si>
+  <si>
+    <t>New Jeddah Paint</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 217 SP PURPLE PARTY-Q</t>
   </si>
 </sst>
 </file>
@@ -4108,7 +4153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2094"/>
+  <dimension ref="A1:K2161"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -50043,8 +50088,1505 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2096" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2096" s="2">
+        <v>208</v>
+      </c>
+      <c r="B2096" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="C2096" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2096" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2096" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F2096" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2096" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H2096" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2096">
+        <v>1</v>
+      </c>
+      <c r="J2096" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2096" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2097" s="2"/>
+      <c r="B2097" s="2"/>
+      <c r="C2097" s="2"/>
+      <c r="D2097" s="2"/>
+      <c r="E2097" s="3"/>
+      <c r="F2097" s="2"/>
+      <c r="G2097" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H2097" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2097">
+        <v>1</v>
+      </c>
+      <c r="J2097" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2097" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2098" s="2"/>
+      <c r="B2098" s="2"/>
+      <c r="C2098" s="2"/>
+      <c r="D2098" s="2"/>
+      <c r="E2098" s="3"/>
+      <c r="F2098" s="2"/>
+      <c r="G2098" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2098" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2098">
+        <v>1</v>
+      </c>
+      <c r="J2098" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2098" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2099" s="2"/>
+      <c r="B2099" s="2"/>
+      <c r="C2099" s="2"/>
+      <c r="D2099" s="2"/>
+      <c r="E2099" s="3"/>
+      <c r="F2099" s="2"/>
+      <c r="G2099" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2099" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2099">
+        <v>1</v>
+      </c>
+      <c r="J2099" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2099" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2100" s="2"/>
+      <c r="B2100" s="2"/>
+      <c r="C2100" s="2"/>
+      <c r="D2100" s="2"/>
+      <c r="E2100" s="3"/>
+      <c r="F2100" s="2"/>
+      <c r="G2100" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H2100" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2100">
+        <v>1</v>
+      </c>
+      <c r="J2100" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2100" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2101" s="2"/>
+      <c r="B2101" s="2"/>
+      <c r="C2101" s="2"/>
+      <c r="D2101" s="2"/>
+      <c r="E2101" s="3"/>
+      <c r="F2101" s="2"/>
+      <c r="G2101" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H2101" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2101">
+        <v>2</v>
+      </c>
+      <c r="J2101" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2102" s="2"/>
+      <c r="B2102" s="2"/>
+      <c r="C2102" s="2"/>
+      <c r="D2102" s="2"/>
+      <c r="E2102" s="3"/>
+      <c r="F2102" s="2"/>
+      <c r="G2102" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H2102" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2102">
+        <v>1</v>
+      </c>
+      <c r="J2102" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2102" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2103" s="2"/>
+      <c r="B2103" s="2"/>
+      <c r="C2103" s="2"/>
+      <c r="D2103" s="2"/>
+      <c r="E2103" s="3"/>
+      <c r="F2103" s="2"/>
+      <c r="G2103" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H2103" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2103">
+        <v>2</v>
+      </c>
+      <c r="J2103" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2103" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2104" s="2"/>
+      <c r="B2104" s="2"/>
+      <c r="C2104" s="2"/>
+      <c r="D2104" s="2"/>
+      <c r="E2104" s="3"/>
+      <c r="F2104" s="2"/>
+      <c r="G2104" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2104" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2104">
+        <v>1</v>
+      </c>
+      <c r="J2104" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2104" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2105" s="2"/>
+      <c r="B2105" s="2"/>
+      <c r="C2105" s="2"/>
+      <c r="D2105" s="2"/>
+      <c r="E2105" s="3"/>
+      <c r="F2105" s="2"/>
+      <c r="G2105" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2105" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2105">
+        <v>1</v>
+      </c>
+      <c r="J2105" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2105" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2106" s="2"/>
+      <c r="B2106" s="2"/>
+      <c r="C2106" s="2"/>
+      <c r="D2106" s="2"/>
+      <c r="E2106" s="3"/>
+      <c r="F2106" s="2"/>
+      <c r="G2106" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H2106" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2106">
+        <v>1</v>
+      </c>
+      <c r="J2106" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2106" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2107" s="2"/>
+      <c r="B2107" s="2"/>
+      <c r="C2107" s="2"/>
+      <c r="D2107" s="2"/>
+      <c r="E2107" s="3"/>
+      <c r="F2107" s="2"/>
+      <c r="G2107" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H2107" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2107">
+        <v>2</v>
+      </c>
+      <c r="J2107" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2107" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2108" s="2"/>
+      <c r="B2108" s="2"/>
+      <c r="C2108" s="2"/>
+      <c r="D2108" s="2"/>
+      <c r="E2108" s="3"/>
+      <c r="F2108" s="2"/>
+      <c r="G2108" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H2108" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2108">
+        <v>2</v>
+      </c>
+      <c r="J2108" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2108" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2109" s="2"/>
+      <c r="B2109" s="2"/>
+      <c r="C2109" s="2"/>
+      <c r="D2109" s="2"/>
+      <c r="E2109" s="3"/>
+      <c r="F2109" s="2"/>
+      <c r="G2109" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H2109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2109">
+        <v>2</v>
+      </c>
+      <c r="J2109" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2109" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2110" s="2"/>
+      <c r="B2110" s="2"/>
+      <c r="C2110" s="2"/>
+      <c r="D2110" s="2"/>
+      <c r="E2110" s="3"/>
+      <c r="F2110" s="2"/>
+      <c r="G2110" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H2110" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2110">
+        <v>2</v>
+      </c>
+      <c r="J2110" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2110" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2111" s="2"/>
+      <c r="B2111" s="2"/>
+      <c r="C2111" s="2"/>
+      <c r="D2111" s="2"/>
+      <c r="E2111" s="3"/>
+      <c r="F2111" s="2"/>
+      <c r="G2111" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H2111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2111">
+        <v>4</v>
+      </c>
+      <c r="J2111" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2111" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2112" s="2"/>
+      <c r="B2112" s="2"/>
+      <c r="C2112" s="2"/>
+      <c r="D2112" s="2"/>
+      <c r="E2112" s="3"/>
+      <c r="F2112" s="2"/>
+      <c r="G2112" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H2112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2112">
+        <v>4</v>
+      </c>
+      <c r="J2112" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2112" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2113" s="2"/>
+      <c r="B2113" s="2"/>
+      <c r="C2113" s="2"/>
+      <c r="D2113" s="2"/>
+      <c r="E2113" s="3"/>
+      <c r="F2113" s="2"/>
+      <c r="G2113" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H2113" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2113">
+        <v>2</v>
+      </c>
+      <c r="J2113" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2113" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2114" s="2"/>
+      <c r="B2114" s="2"/>
+      <c r="C2114" s="2"/>
+      <c r="D2114" s="2"/>
+      <c r="E2114" s="3"/>
+      <c r="F2114" s="2"/>
+      <c r="G2114" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H2114" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2114">
+        <v>1</v>
+      </c>
+      <c r="J2114" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2114" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2115" s="2"/>
+      <c r="B2115" s="2"/>
+      <c r="C2115" s="2"/>
+      <c r="D2115" s="2"/>
+      <c r="E2115" s="3"/>
+      <c r="F2115" s="2"/>
+      <c r="G2115" t="s">
+        <v>766</v>
+      </c>
+      <c r="H2115" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2115">
+        <v>4</v>
+      </c>
+      <c r="J2115" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2115" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2116" s="2"/>
+      <c r="B2116" s="2"/>
+      <c r="C2116" s="2"/>
+      <c r="D2116" s="2"/>
+      <c r="E2116" s="3"/>
+      <c r="F2116" s="2"/>
+      <c r="G2116" t="s">
+        <v>962</v>
+      </c>
+      <c r="H2116" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2116">
+        <v>1</v>
+      </c>
+      <c r="J2116" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2116" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2117" s="2"/>
+      <c r="B2117" s="2"/>
+      <c r="C2117" s="2"/>
+      <c r="D2117" s="2"/>
+      <c r="E2117" s="3"/>
+      <c r="F2117" s="2"/>
+      <c r="G2117" t="s">
+        <v>261</v>
+      </c>
+      <c r="H2117" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2117">
+        <v>4</v>
+      </c>
+      <c r="J2117" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2117" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2118" s="2"/>
+      <c r="B2118" s="2"/>
+      <c r="C2118" s="2"/>
+      <c r="D2118" s="2"/>
+      <c r="E2118" s="3"/>
+      <c r="F2118" s="2"/>
+      <c r="G2118" t="s">
+        <v>379</v>
+      </c>
+      <c r="H2118" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2118">
+        <v>2</v>
+      </c>
+      <c r="J2118" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2118" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2119" s="2"/>
+      <c r="B2119" s="2"/>
+      <c r="C2119" s="2"/>
+      <c r="D2119" s="2"/>
+      <c r="E2119" s="3"/>
+      <c r="F2119" s="2"/>
+      <c r="G2119" t="s">
+        <v>831</v>
+      </c>
+      <c r="H2119" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2119">
+        <v>2</v>
+      </c>
+      <c r="J2119" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2119" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2120" s="2"/>
+      <c r="B2120" s="2"/>
+      <c r="C2120" s="2"/>
+      <c r="D2120" s="2"/>
+      <c r="E2120" s="3"/>
+      <c r="F2120" s="2"/>
+      <c r="G2120" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H2120" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2120">
+        <v>1</v>
+      </c>
+      <c r="J2120" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2120" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2121" s="2"/>
+      <c r="B2121" s="2"/>
+      <c r="C2121" s="2"/>
+      <c r="D2121" s="2"/>
+      <c r="E2121" s="3"/>
+      <c r="F2121" s="2"/>
+      <c r="G2121" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H2121" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2121">
+        <v>1</v>
+      </c>
+      <c r="J2121" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2121" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2122" s="2"/>
+      <c r="B2122" s="2"/>
+      <c r="C2122" s="2"/>
+      <c r="D2122" s="2"/>
+      <c r="E2122" s="3"/>
+      <c r="F2122" s="2"/>
+      <c r="G2122" t="s">
+        <v>244</v>
+      </c>
+      <c r="H2122" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2122">
+        <v>1</v>
+      </c>
+      <c r="J2122" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2122" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2123" s="2"/>
+      <c r="B2123" s="2"/>
+      <c r="C2123" s="2"/>
+      <c r="D2123" s="2"/>
+      <c r="E2123" s="3"/>
+      <c r="F2123" s="2"/>
+      <c r="G2123" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H2123" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2123">
+        <v>4</v>
+      </c>
+      <c r="J2123" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2123" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2124" s="2"/>
+      <c r="B2124" s="2"/>
+      <c r="C2124" s="2"/>
+      <c r="D2124" s="2"/>
+      <c r="E2124" s="3"/>
+      <c r="F2124" s="2"/>
+      <c r="G2124" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H2124" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2124">
+        <v>1</v>
+      </c>
+      <c r="J2124" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2124" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2125" s="2"/>
+      <c r="B2125" s="2"/>
+      <c r="C2125" s="2"/>
+      <c r="D2125" s="2"/>
+      <c r="E2125" s="3"/>
+      <c r="F2125" s="2"/>
+      <c r="G2125" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H2125" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2125">
+        <v>2</v>
+      </c>
+      <c r="J2125" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2125" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2126" s="2"/>
+      <c r="B2126" s="2"/>
+      <c r="C2126" s="2"/>
+      <c r="D2126" s="2"/>
+      <c r="E2126" s="3"/>
+      <c r="F2126" s="2"/>
+      <c r="G2126" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H2126" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2126">
+        <v>1</v>
+      </c>
+      <c r="J2126" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2126" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2127" s="2"/>
+      <c r="B2127" s="2"/>
+      <c r="C2127" s="2"/>
+      <c r="D2127" s="2"/>
+      <c r="E2127" s="3"/>
+      <c r="F2127" s="2"/>
+      <c r="G2127" t="s">
+        <v>720</v>
+      </c>
+      <c r="H2127" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2127">
+        <v>1</v>
+      </c>
+      <c r="J2127" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2127" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2128" s="2"/>
+      <c r="B2128" s="2"/>
+      <c r="C2128" s="2"/>
+      <c r="D2128" s="2"/>
+      <c r="E2128" s="3"/>
+      <c r="F2128" s="2"/>
+      <c r="G2128" t="s">
+        <v>538</v>
+      </c>
+      <c r="H2128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2128">
+        <v>1</v>
+      </c>
+      <c r="J2128" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2128" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2130" s="2">
+        <v>209</v>
+      </c>
+      <c r="B2130" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="C2130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2130" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2130" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F2130" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G2130" t="s">
+        <v>251</v>
+      </c>
+      <c r="H2130" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2130">
+        <v>1</v>
+      </c>
+      <c r="J2130" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2130" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2131" s="2"/>
+      <c r="B2131" s="2"/>
+      <c r="C2131" s="2"/>
+      <c r="D2131" s="2"/>
+      <c r="E2131" s="3"/>
+      <c r="F2131" s="2"/>
+      <c r="G2131" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2131" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2131">
+        <v>1</v>
+      </c>
+      <c r="J2131" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2131" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2132" s="2"/>
+      <c r="B2132" s="2"/>
+      <c r="C2132" s="2"/>
+      <c r="D2132" s="2"/>
+      <c r="E2132" s="3"/>
+      <c r="F2132" s="2"/>
+      <c r="G2132" t="s">
+        <v>605</v>
+      </c>
+      <c r="H2132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2132">
+        <v>2</v>
+      </c>
+      <c r="J2132" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2132" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2133" s="2"/>
+      <c r="B2133" s="2"/>
+      <c r="C2133" s="2"/>
+      <c r="D2133" s="2"/>
+      <c r="E2133" s="3"/>
+      <c r="F2133" s="2"/>
+      <c r="G2133" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H2133" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2133">
+        <v>2</v>
+      </c>
+      <c r="J2133" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2133" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2134" s="2"/>
+      <c r="B2134" s="2"/>
+      <c r="C2134" s="2"/>
+      <c r="D2134" s="2"/>
+      <c r="E2134" s="3"/>
+      <c r="F2134" s="2"/>
+      <c r="G2134" t="s">
+        <v>536</v>
+      </c>
+      <c r="H2134" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2134">
+        <v>1</v>
+      </c>
+      <c r="J2134" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2134" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2135" s="2"/>
+      <c r="B2135" s="2"/>
+      <c r="C2135" s="2"/>
+      <c r="D2135" s="2"/>
+      <c r="E2135" s="3"/>
+      <c r="F2135" s="2"/>
+      <c r="G2135" t="s">
+        <v>963</v>
+      </c>
+      <c r="H2135" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2135">
+        <v>1</v>
+      </c>
+      <c r="J2135" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2135" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2136" s="2"/>
+      <c r="B2136" s="2"/>
+      <c r="C2136" s="2"/>
+      <c r="D2136" s="2"/>
+      <c r="E2136" s="3"/>
+      <c r="F2136" s="2"/>
+      <c r="G2136" t="s">
+        <v>681</v>
+      </c>
+      <c r="H2136" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2136">
+        <v>1</v>
+      </c>
+      <c r="J2136" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2136" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2137" s="2"/>
+      <c r="B2137" s="2"/>
+      <c r="C2137" s="2"/>
+      <c r="D2137" s="2"/>
+      <c r="E2137" s="3"/>
+      <c r="F2137" s="2"/>
+      <c r="G2137" t="s">
+        <v>150</v>
+      </c>
+      <c r="H2137" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2137">
+        <v>4</v>
+      </c>
+      <c r="J2137" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2137" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2138" s="2"/>
+      <c r="B2138" s="2"/>
+      <c r="C2138" s="2"/>
+      <c r="D2138" s="2"/>
+      <c r="E2138" s="3"/>
+      <c r="F2138" s="2"/>
+      <c r="G2138" t="s">
+        <v>670</v>
+      </c>
+      <c r="H2138" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2138">
+        <v>3</v>
+      </c>
+      <c r="J2138" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2138" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2139" s="2"/>
+      <c r="B2139" s="2"/>
+      <c r="C2139" s="2"/>
+      <c r="D2139" s="2"/>
+      <c r="E2139" s="3"/>
+      <c r="F2139" s="2"/>
+      <c r="G2139" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2139" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2139">
+        <v>2</v>
+      </c>
+      <c r="J2139" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2139" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2140" s="2"/>
+      <c r="B2140" s="2"/>
+      <c r="C2140" s="2"/>
+      <c r="D2140" s="2"/>
+      <c r="E2140" s="3"/>
+      <c r="F2140" s="2"/>
+      <c r="G2140" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H2140" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2140">
+        <v>1</v>
+      </c>
+      <c r="J2140" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2140" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2141" s="2"/>
+      <c r="B2141" s="2"/>
+      <c r="C2141" s="2"/>
+      <c r="D2141" s="2"/>
+      <c r="E2141" s="3"/>
+      <c r="F2141" s="2"/>
+      <c r="G2141" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2141" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2141">
+        <v>3</v>
+      </c>
+      <c r="J2141" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2141" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2142" s="2"/>
+      <c r="B2142" s="2"/>
+      <c r="C2142" s="2"/>
+      <c r="D2142" s="2"/>
+      <c r="E2142" s="3"/>
+      <c r="F2142" s="2"/>
+      <c r="G2142" t="s">
+        <v>1126</v>
+      </c>
+      <c r="H2142" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2142">
+        <v>3</v>
+      </c>
+      <c r="J2142" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2142" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2144" s="2">
+        <v>210</v>
+      </c>
+      <c r="B2144" s="2" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C2144" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2144" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2144" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F2144" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G2144" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2144" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2144">
+        <v>1</v>
+      </c>
+      <c r="J2144" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2144" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2145" s="2"/>
+      <c r="B2145" s="2"/>
+      <c r="C2145" s="2"/>
+      <c r="D2145" s="2"/>
+      <c r="E2145" s="3"/>
+      <c r="F2145" s="2"/>
+      <c r="G2145" t="s">
+        <v>832</v>
+      </c>
+      <c r="H2145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2145">
+        <v>2</v>
+      </c>
+      <c r="J2145" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2145" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2146" s="2"/>
+      <c r="B2146" s="2"/>
+      <c r="C2146" s="2"/>
+      <c r="D2146" s="2"/>
+      <c r="E2146" s="3"/>
+      <c r="F2146" s="2"/>
+      <c r="G2146" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H2146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2146">
+        <v>2</v>
+      </c>
+      <c r="J2146" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2146" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2147" s="2"/>
+      <c r="B2147" s="2"/>
+      <c r="C2147" s="2"/>
+      <c r="D2147" s="2"/>
+      <c r="E2147" s="3"/>
+      <c r="F2147" s="2"/>
+      <c r="G2147" t="s">
+        <v>538</v>
+      </c>
+      <c r="H2147" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2147">
+        <v>2</v>
+      </c>
+      <c r="J2147" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2147" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2148" s="2"/>
+      <c r="B2148" s="2"/>
+      <c r="C2148" s="2"/>
+      <c r="D2148" s="2"/>
+      <c r="E2148" s="3"/>
+      <c r="F2148" s="2"/>
+      <c r="G2148" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2148" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2148">
+        <v>3</v>
+      </c>
+      <c r="J2148" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2148" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2150" s="2">
+        <v>211</v>
+      </c>
+      <c r="B2150" s="2" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C2150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2150" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2150" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F2150" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="G2150" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H2150" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2150">
+        <v>3</v>
+      </c>
+      <c r="J2150" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2150" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2151" s="2"/>
+      <c r="B2151" s="2"/>
+      <c r="C2151" s="2"/>
+      <c r="D2151" s="2"/>
+      <c r="E2151" s="3"/>
+      <c r="F2151" s="2"/>
+      <c r="G2151" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2151" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2151">
+        <v>5</v>
+      </c>
+      <c r="J2151" t="s">
+        <v>39</v>
+      </c>
+      <c r="K2151" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2152" s="2"/>
+      <c r="B2152" s="2"/>
+      <c r="C2152" s="2"/>
+      <c r="D2152" s="2"/>
+      <c r="E2152" s="3"/>
+      <c r="F2152" s="2"/>
+      <c r="G2152" t="s">
+        <v>442</v>
+      </c>
+      <c r="H2152" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2152">
+        <v>4</v>
+      </c>
+      <c r="J2152" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2152" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2153" s="2"/>
+      <c r="B2153" s="2"/>
+      <c r="C2153" s="2"/>
+      <c r="D2153" s="2"/>
+      <c r="E2153" s="3"/>
+      <c r="F2153" s="2"/>
+      <c r="G2153" t="s">
+        <v>1248</v>
+      </c>
+      <c r="H2153" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2153">
+        <v>4</v>
+      </c>
+      <c r="J2153" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2153" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2154" s="2"/>
+      <c r="B2154" s="2"/>
+      <c r="C2154" s="2"/>
+      <c r="D2154" s="2"/>
+      <c r="E2154" s="3"/>
+      <c r="F2154" s="2"/>
+      <c r="G2154" t="s">
+        <v>171</v>
+      </c>
+      <c r="H2154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2154">
+        <v>2</v>
+      </c>
+      <c r="J2154" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2154" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2155" s="2"/>
+      <c r="B2155" s="2"/>
+      <c r="C2155" s="2"/>
+      <c r="D2155" s="2"/>
+      <c r="E2155" s="3"/>
+      <c r="F2155" s="2"/>
+      <c r="G2155" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H2155" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2155">
+        <v>1</v>
+      </c>
+      <c r="J2155" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2155" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2156" s="2"/>
+      <c r="B2156" s="2"/>
+      <c r="C2156" s="2"/>
+      <c r="D2156" s="2"/>
+      <c r="E2156" s="3"/>
+      <c r="F2156" s="2"/>
+      <c r="G2156" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2156" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2156">
+        <v>2</v>
+      </c>
+      <c r="J2156" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2156" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2157" s="2"/>
+      <c r="B2157" s="2"/>
+      <c r="C2157" s="2"/>
+      <c r="D2157" s="2"/>
+      <c r="E2157" s="3"/>
+      <c r="F2157" s="2"/>
+      <c r="G2157" t="s">
+        <v>450</v>
+      </c>
+      <c r="H2157" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2157">
+        <v>1</v>
+      </c>
+      <c r="J2157" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2157" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2158" s="2"/>
+      <c r="B2158" s="2"/>
+      <c r="C2158" s="2"/>
+      <c r="D2158" s="2"/>
+      <c r="E2158" s="3"/>
+      <c r="F2158" s="2"/>
+      <c r="G2158" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2158" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2158">
+        <v>3</v>
+      </c>
+      <c r="J2158" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2158" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2159" s="2"/>
+      <c r="B2159" s="2"/>
+      <c r="C2159" s="2"/>
+      <c r="D2159" s="2"/>
+      <c r="E2159" s="3"/>
+      <c r="F2159" s="2"/>
+      <c r="G2159" t="s">
+        <v>241</v>
+      </c>
+      <c r="H2159" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2159">
+        <v>2</v>
+      </c>
+      <c r="J2159" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2159" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2160" s="2"/>
+      <c r="B2160" s="2"/>
+      <c r="C2160" s="2"/>
+      <c r="D2160" s="2"/>
+      <c r="E2160" s="3"/>
+      <c r="F2160" s="2"/>
+      <c r="G2160" t="s">
+        <v>553</v>
+      </c>
+      <c r="H2160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2160">
+        <v>4</v>
+      </c>
+      <c r="J2160" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2160" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2161" s="2"/>
+      <c r="B2161" s="2"/>
+      <c r="C2161" s="2"/>
+      <c r="D2161" s="2"/>
+      <c r="E2161" s="3"/>
+      <c r="F2161" s="2"/>
+      <c r="G2161" t="s">
+        <v>631</v>
+      </c>
+      <c r="H2161" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2161">
+        <v>6</v>
+      </c>
+      <c r="J2161" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2161" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1092">
+  <mergeCells count="1116">
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="B4:B9"/>
     <mergeCell ref="C4:C9"/>
@@ -51137,6 +52679,30 @@
     <mergeCell ref="D2089:D2094"/>
     <mergeCell ref="E2089:E2094"/>
     <mergeCell ref="F2089:F2094"/>
+    <mergeCell ref="A2096:A2128"/>
+    <mergeCell ref="B2096:B2128"/>
+    <mergeCell ref="C2096:C2128"/>
+    <mergeCell ref="D2096:D2128"/>
+    <mergeCell ref="E2096:E2128"/>
+    <mergeCell ref="F2096:F2128"/>
+    <mergeCell ref="A2130:A2142"/>
+    <mergeCell ref="B2130:B2142"/>
+    <mergeCell ref="C2130:C2142"/>
+    <mergeCell ref="D2130:D2142"/>
+    <mergeCell ref="E2130:E2142"/>
+    <mergeCell ref="F2130:F2142"/>
+    <mergeCell ref="A2144:A2148"/>
+    <mergeCell ref="B2144:B2148"/>
+    <mergeCell ref="C2144:C2148"/>
+    <mergeCell ref="D2144:D2148"/>
+    <mergeCell ref="E2144:E2148"/>
+    <mergeCell ref="F2144:F2148"/>
+    <mergeCell ref="A2150:A2161"/>
+    <mergeCell ref="B2150:B2161"/>
+    <mergeCell ref="C2150:C2161"/>
+    <mergeCell ref="D2150:D2161"/>
+    <mergeCell ref="E2150:E2161"/>
+    <mergeCell ref="F2150:F2161"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="128">
   <si>
     <t>S.No</t>
   </si>
@@ -329,6 +329,72 @@
   </si>
   <si>
     <t>EXTRA STAINLESS 9072 ROSE WHITE-G</t>
+  </si>
+  <si>
+    <t>29/07/2026, 5:45:23 pm</t>
+  </si>
+  <si>
+    <t>Rahel Traders</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9988 CAMEO-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9990 APRICOT-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9999 WHITE-D</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9997 ASH WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 74 KITTEN WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9056 LIME WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 36 SP DEEP BLUE-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S U1955 SWEET TULIP-Q</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9994 PEACH SHADOW-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 320 LEMON-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 314 ORANGE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 326 GRASS GREEN-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 342 SANDAL-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 338 ANTELOPE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 301 MORNING GREY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 318 SUNSTRAW-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 235 SKYLINE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 317 SOFT ASH WHITE-G</t>
+  </si>
+  <si>
+    <t>29/07/2026, 5:53:59 pm</t>
+  </si>
+  <si>
+    <t>Water Pump Traders</t>
   </si>
 </sst>
 </file>
@@ -724,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2230,8 +2296,699 @@
         <v>19</v>
       </c>
     </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>15</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="G72" t="s">
+        <v>108</v>
+      </c>
+      <c r="H72" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72">
+        <v>2</v>
+      </c>
+      <c r="J72" t="s">
+        <v>18</v>
+      </c>
+      <c r="K72" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="2"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="2"/>
+      <c r="G73" t="s">
+        <v>109</v>
+      </c>
+      <c r="H73" t="s">
+        <v>17</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="J73" t="s">
+        <v>18</v>
+      </c>
+      <c r="K73" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="2"/>
+      <c r="G74" t="s">
+        <v>110</v>
+      </c>
+      <c r="H74" t="s">
+        <v>36</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74" t="s">
+        <v>18</v>
+      </c>
+      <c r="K74" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="2"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="2"/>
+      <c r="G75" t="s">
+        <v>111</v>
+      </c>
+      <c r="H75" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75">
+        <v>5</v>
+      </c>
+      <c r="J75" t="s">
+        <v>18</v>
+      </c>
+      <c r="K75" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="2"/>
+      <c r="G76" t="s">
+        <v>112</v>
+      </c>
+      <c r="H76" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76">
+        <v>2</v>
+      </c>
+      <c r="J76" t="s">
+        <v>18</v>
+      </c>
+      <c r="K76" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="2"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="2"/>
+      <c r="G77" t="s">
+        <v>113</v>
+      </c>
+      <c r="H77" t="s">
+        <v>43</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="J77" t="s">
+        <v>18</v>
+      </c>
+      <c r="K77" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="2"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="2"/>
+      <c r="G78" t="s">
+        <v>114</v>
+      </c>
+      <c r="H78" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78">
+        <v>2</v>
+      </c>
+      <c r="J78" t="s">
+        <v>18</v>
+      </c>
+      <c r="K78" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="2"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+      <c r="D79" s="2"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="2"/>
+      <c r="G79" t="s">
+        <v>115</v>
+      </c>
+      <c r="H79" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79">
+        <v>3</v>
+      </c>
+      <c r="J79" t="s">
+        <v>18</v>
+      </c>
+      <c r="K79" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="2"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="2"/>
+      <c r="G80" t="s">
+        <v>116</v>
+      </c>
+      <c r="H80" t="s">
+        <v>17</v>
+      </c>
+      <c r="I80">
+        <v>3</v>
+      </c>
+      <c r="J80" t="s">
+        <v>18</v>
+      </c>
+      <c r="K80" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="2"/>
+      <c r="G81" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81">
+        <v>2</v>
+      </c>
+      <c r="J81" t="s">
+        <v>18</v>
+      </c>
+      <c r="K81" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="2"/>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="2"/>
+      <c r="G82" t="s">
+        <v>117</v>
+      </c>
+      <c r="H82" t="s">
+        <v>17</v>
+      </c>
+      <c r="I82">
+        <v>2</v>
+      </c>
+      <c r="J82" t="s">
+        <v>18</v>
+      </c>
+      <c r="K82" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="2"/>
+      <c r="G83" t="s">
+        <v>118</v>
+      </c>
+      <c r="H83" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83" t="s">
+        <v>18</v>
+      </c>
+      <c r="K83" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="2"/>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="2"/>
+      <c r="G84" t="s">
+        <v>119</v>
+      </c>
+      <c r="H84" t="s">
+        <v>43</v>
+      </c>
+      <c r="I84">
+        <v>4</v>
+      </c>
+      <c r="J84" t="s">
+        <v>18</v>
+      </c>
+      <c r="K84" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="2"/>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
+      <c r="D85" s="2"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="2"/>
+      <c r="G85" t="s">
+        <v>120</v>
+      </c>
+      <c r="H85" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85">
+        <v>3</v>
+      </c>
+      <c r="J85" t="s">
+        <v>18</v>
+      </c>
+      <c r="K85" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="2"/>
+      <c r="G86" t="s">
+        <v>79</v>
+      </c>
+      <c r="H86" t="s">
+        <v>43</v>
+      </c>
+      <c r="I86">
+        <v>5</v>
+      </c>
+      <c r="J86" t="s">
+        <v>18</v>
+      </c>
+      <c r="K86" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="2"/>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
+      <c r="D87" s="2"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="2"/>
+      <c r="G87" t="s">
+        <v>121</v>
+      </c>
+      <c r="H87" t="s">
+        <v>43</v>
+      </c>
+      <c r="I87">
+        <v>5</v>
+      </c>
+      <c r="J87" t="s">
+        <v>18</v>
+      </c>
+      <c r="K87" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="2"/>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
+      <c r="D88" s="2"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="2"/>
+      <c r="G88" t="s">
+        <v>59</v>
+      </c>
+      <c r="H88" t="s">
+        <v>43</v>
+      </c>
+      <c r="I88">
+        <v>4</v>
+      </c>
+      <c r="J88" t="s">
+        <v>18</v>
+      </c>
+      <c r="K88" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="2"/>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
+      <c r="D89" s="2"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="2"/>
+      <c r="G89" t="s">
+        <v>122</v>
+      </c>
+      <c r="H89" t="s">
+        <v>43</v>
+      </c>
+      <c r="I89">
+        <v>4</v>
+      </c>
+      <c r="J89" t="s">
+        <v>18</v>
+      </c>
+      <c r="K89" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="2"/>
+      <c r="G90" t="s">
+        <v>123</v>
+      </c>
+      <c r="H90" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90">
+        <v>3</v>
+      </c>
+      <c r="J90" t="s">
+        <v>18</v>
+      </c>
+      <c r="K90" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="2"/>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="2"/>
+      <c r="G91" t="s">
+        <v>97</v>
+      </c>
+      <c r="H91" t="s">
+        <v>17</v>
+      </c>
+      <c r="I91">
+        <v>3</v>
+      </c>
+      <c r="J91" t="s">
+        <v>18</v>
+      </c>
+      <c r="K91" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="2"/>
+      <c r="G92" t="s">
+        <v>124</v>
+      </c>
+      <c r="H92" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92" t="s">
+        <v>18</v>
+      </c>
+      <c r="K92" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="2"/>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
+      <c r="D93" s="2"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="2"/>
+      <c r="G93" t="s">
+        <v>125</v>
+      </c>
+      <c r="H93" t="s">
+        <v>17</v>
+      </c>
+      <c r="I93">
+        <v>3</v>
+      </c>
+      <c r="J93" t="s">
+        <v>18</v>
+      </c>
+      <c r="K93" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>16</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G95" t="s">
+        <v>97</v>
+      </c>
+      <c r="H95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>18</v>
+      </c>
+      <c r="K95" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="2"/>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
+      <c r="D96" s="2"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="2"/>
+      <c r="G96" t="s">
+        <v>98</v>
+      </c>
+      <c r="H96" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96">
+        <v>2</v>
+      </c>
+      <c r="J96" t="s">
+        <v>18</v>
+      </c>
+      <c r="K96" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="2"/>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
+      <c r="D97" s="2"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="2"/>
+      <c r="G97" t="s">
+        <v>99</v>
+      </c>
+      <c r="H97" t="s">
+        <v>17</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97" t="s">
+        <v>18</v>
+      </c>
+      <c r="K97" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="2"/>
+      <c r="G98" t="s">
+        <v>100</v>
+      </c>
+      <c r="H98" t="s">
+        <v>43</v>
+      </c>
+      <c r="I98">
+        <v>1</v>
+      </c>
+      <c r="J98" t="s">
+        <v>18</v>
+      </c>
+      <c r="K98" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="2"/>
+      <c r="G99" t="s">
+        <v>101</v>
+      </c>
+      <c r="H99" t="s">
+        <v>43</v>
+      </c>
+      <c r="I99">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
+        <v>18</v>
+      </c>
+      <c r="K99" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="2"/>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="2"/>
+      <c r="G100" t="s">
+        <v>102</v>
+      </c>
+      <c r="H100" t="s">
+        <v>43</v>
+      </c>
+      <c r="I100">
+        <v>2</v>
+      </c>
+      <c r="J100" t="s">
+        <v>18</v>
+      </c>
+      <c r="K100" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="2"/>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="2"/>
+      <c r="G101" t="s">
+        <v>80</v>
+      </c>
+      <c r="H101" t="s">
+        <v>43</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101" t="s">
+        <v>18</v>
+      </c>
+      <c r="K101" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="78">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
@@ -2298,6 +3055,18 @@
     <mergeCell ref="D62:D68"/>
     <mergeCell ref="E62:E68"/>
     <mergeCell ref="F62:F68"/>
+    <mergeCell ref="A72:A93"/>
+    <mergeCell ref="B72:B93"/>
+    <mergeCell ref="C72:C93"/>
+    <mergeCell ref="D72:D93"/>
+    <mergeCell ref="E72:E93"/>
+    <mergeCell ref="F72:F93"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="B95:B101"/>
+    <mergeCell ref="C95:C101"/>
+    <mergeCell ref="D95:D101"/>
+    <mergeCell ref="E95:E101"/>
+    <mergeCell ref="F95:F101"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="133">
   <si>
     <t>S.No</t>
   </si>
@@ -395,6 +395,21 @@
   </si>
   <si>
     <t>Water Pump Traders</t>
+  </si>
+  <si>
+    <t>29/07/2026, 6:17:57 pm</t>
+  </si>
+  <si>
+    <t>Rehan traders</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9991 BLOSSOM PINK-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE501 BLACK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 30 CAMEO-Q</t>
   </si>
 </sst>
 </file>
@@ -790,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -2987,8 +3002,526 @@
         <v>19</v>
       </c>
     </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>17</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G103" t="s">
+        <v>108</v>
+      </c>
+      <c r="H103" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103">
+        <v>2</v>
+      </c>
+      <c r="J103" t="s">
+        <v>18</v>
+      </c>
+      <c r="K103" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="2"/>
+      <c r="G104" t="s">
+        <v>109</v>
+      </c>
+      <c r="H104" t="s">
+        <v>17</v>
+      </c>
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104" t="s">
+        <v>18</v>
+      </c>
+      <c r="K104" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="2"/>
+      <c r="B105" s="2"/>
+      <c r="C105" s="2"/>
+      <c r="D105" s="2"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="2"/>
+      <c r="G105" t="s">
+        <v>110</v>
+      </c>
+      <c r="H105" t="s">
+        <v>36</v>
+      </c>
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105" t="s">
+        <v>18</v>
+      </c>
+      <c r="K105" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="2"/>
+      <c r="G106" t="s">
+        <v>111</v>
+      </c>
+      <c r="H106" t="s">
+        <v>36</v>
+      </c>
+      <c r="I106">
+        <v>5</v>
+      </c>
+      <c r="J106" t="s">
+        <v>18</v>
+      </c>
+      <c r="K106" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="2"/>
+      <c r="B107" s="2"/>
+      <c r="C107" s="2"/>
+      <c r="D107" s="2"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="2"/>
+      <c r="G107" t="s">
+        <v>112</v>
+      </c>
+      <c r="H107" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107">
+        <v>2</v>
+      </c>
+      <c r="J107" t="s">
+        <v>18</v>
+      </c>
+      <c r="K107" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="2"/>
+      <c r="B108" s="2"/>
+      <c r="C108" s="2"/>
+      <c r="D108" s="2"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="2"/>
+      <c r="G108" t="s">
+        <v>113</v>
+      </c>
+      <c r="H108" t="s">
+        <v>43</v>
+      </c>
+      <c r="I108">
+        <v>3</v>
+      </c>
+      <c r="J108" t="s">
+        <v>18</v>
+      </c>
+      <c r="K108" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="2"/>
+      <c r="B109" s="2"/>
+      <c r="C109" s="2"/>
+      <c r="D109" s="2"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="2"/>
+      <c r="G109" t="s">
+        <v>114</v>
+      </c>
+      <c r="H109" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109">
+        <v>2</v>
+      </c>
+      <c r="J109" t="s">
+        <v>18</v>
+      </c>
+      <c r="K109" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="2"/>
+      <c r="G110" t="s">
+        <v>115</v>
+      </c>
+      <c r="H110" t="s">
+        <v>43</v>
+      </c>
+      <c r="I110">
+        <v>3</v>
+      </c>
+      <c r="J110" t="s">
+        <v>18</v>
+      </c>
+      <c r="K110" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="2"/>
+      <c r="B111" s="2"/>
+      <c r="C111" s="2"/>
+      <c r="D111" s="2"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="2"/>
+      <c r="G111" t="s">
+        <v>130</v>
+      </c>
+      <c r="H111" t="s">
+        <v>17</v>
+      </c>
+      <c r="I111">
+        <v>3</v>
+      </c>
+      <c r="J111" t="s">
+        <v>18</v>
+      </c>
+      <c r="K111" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="2"/>
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="2"/>
+      <c r="G112" t="s">
+        <v>26</v>
+      </c>
+      <c r="H112" t="s">
+        <v>17</v>
+      </c>
+      <c r="I112">
+        <v>2</v>
+      </c>
+      <c r="J112" t="s">
+        <v>18</v>
+      </c>
+      <c r="K112" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="2"/>
+      <c r="G113" t="s">
+        <v>117</v>
+      </c>
+      <c r="H113" t="s">
+        <v>17</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113" t="s">
+        <v>18</v>
+      </c>
+      <c r="K113" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" s="2"/>
+      <c r="B114" s="2"/>
+      <c r="C114" s="2"/>
+      <c r="D114" s="2"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="2"/>
+      <c r="G114" t="s">
+        <v>118</v>
+      </c>
+      <c r="H114" t="s">
+        <v>17</v>
+      </c>
+      <c r="I114">
+        <v>2</v>
+      </c>
+      <c r="J114" t="s">
+        <v>18</v>
+      </c>
+      <c r="K114" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="2"/>
+      <c r="G115" t="s">
+        <v>131</v>
+      </c>
+      <c r="H115" t="s">
+        <v>43</v>
+      </c>
+      <c r="I115">
+        <v>10</v>
+      </c>
+      <c r="J115" t="s">
+        <v>18</v>
+      </c>
+      <c r="K115" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" s="2"/>
+      <c r="B116" s="2"/>
+      <c r="C116" s="2"/>
+      <c r="D116" s="2"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="2"/>
+      <c r="G116" t="s">
+        <v>119</v>
+      </c>
+      <c r="H116" t="s">
+        <v>43</v>
+      </c>
+      <c r="I116">
+        <v>4</v>
+      </c>
+      <c r="J116" t="s">
+        <v>18</v>
+      </c>
+      <c r="K116" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="2"/>
+      <c r="G117" t="s">
+        <v>120</v>
+      </c>
+      <c r="H117" t="s">
+        <v>43</v>
+      </c>
+      <c r="I117">
+        <v>3</v>
+      </c>
+      <c r="J117" t="s">
+        <v>18</v>
+      </c>
+      <c r="K117" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" s="2"/>
+      <c r="B118" s="2"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="2"/>
+      <c r="G118" t="s">
+        <v>79</v>
+      </c>
+      <c r="H118" t="s">
+        <v>43</v>
+      </c>
+      <c r="I118">
+        <v>5</v>
+      </c>
+      <c r="J118" t="s">
+        <v>18</v>
+      </c>
+      <c r="K118" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" s="2"/>
+      <c r="B119" s="2"/>
+      <c r="C119" s="2"/>
+      <c r="D119" s="2"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="2"/>
+      <c r="G119" t="s">
+        <v>121</v>
+      </c>
+      <c r="H119" t="s">
+        <v>43</v>
+      </c>
+      <c r="I119">
+        <v>5</v>
+      </c>
+      <c r="J119" t="s">
+        <v>18</v>
+      </c>
+      <c r="K119" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="2"/>
+      <c r="G120" t="s">
+        <v>59</v>
+      </c>
+      <c r="H120" t="s">
+        <v>43</v>
+      </c>
+      <c r="I120">
+        <v>4</v>
+      </c>
+      <c r="J120" t="s">
+        <v>18</v>
+      </c>
+      <c r="K120" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="2"/>
+      <c r="G121" t="s">
+        <v>132</v>
+      </c>
+      <c r="H121" t="s">
+        <v>43</v>
+      </c>
+      <c r="I121">
+        <v>4</v>
+      </c>
+      <c r="J121" t="s">
+        <v>18</v>
+      </c>
+      <c r="K121" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" s="2"/>
+      <c r="B122" s="2"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="2"/>
+      <c r="G122" t="s">
+        <v>97</v>
+      </c>
+      <c r="H122" t="s">
+        <v>17</v>
+      </c>
+      <c r="I122">
+        <v>3</v>
+      </c>
+      <c r="J122" t="s">
+        <v>18</v>
+      </c>
+      <c r="K122" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" s="2"/>
+      <c r="B123" s="2"/>
+      <c r="C123" s="2"/>
+      <c r="D123" s="2"/>
+      <c r="E123" s="3"/>
+      <c r="F123" s="2"/>
+      <c r="G123" t="s">
+        <v>124</v>
+      </c>
+      <c r="H123" t="s">
+        <v>17</v>
+      </c>
+      <c r="I123">
+        <v>1</v>
+      </c>
+      <c r="J123" t="s">
+        <v>18</v>
+      </c>
+      <c r="K123" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" s="2"/>
+      <c r="B124" s="2"/>
+      <c r="C124" s="2"/>
+      <c r="D124" s="2"/>
+      <c r="E124" s="3"/>
+      <c r="F124" s="2"/>
+      <c r="G124" t="s">
+        <v>125</v>
+      </c>
+      <c r="H124" t="s">
+        <v>17</v>
+      </c>
+      <c r="I124">
+        <v>3</v>
+      </c>
+      <c r="J124" t="s">
+        <v>18</v>
+      </c>
+      <c r="K124" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="84">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
@@ -3067,6 +3600,12 @@
     <mergeCell ref="D95:D101"/>
     <mergeCell ref="E95:E101"/>
     <mergeCell ref="F95:F101"/>
+    <mergeCell ref="A103:A124"/>
+    <mergeCell ref="B103:B124"/>
+    <mergeCell ref="C103:C124"/>
+    <mergeCell ref="D103:D124"/>
+    <mergeCell ref="E103:E124"/>
+    <mergeCell ref="F103:F124"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="383">
   <si>
     <t>S.No</t>
   </si>
@@ -410,6 +410,756 @@
   </si>
   <si>
     <t>EXTRA SEMI 30 CAMEO-Q</t>
+  </si>
+  <si>
+    <t>30/07/2026, 11:53:42 am</t>
+  </si>
+  <si>
+    <t>Azhar Paint Memon Goth</t>
+  </si>
+  <si>
+    <t>BOLD R.O.P 7704-G</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL WHITE 8801-G</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL SKY BLUE 8823-G</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL LEATHER BROWN 8806-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL WHITE GREEN 8831-Q</t>
+  </si>
+  <si>
+    <t>30/07/2026, 2:04:59 pm</t>
+  </si>
+  <si>
+    <t>Naseem shahfaisal</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 02 ASH WHITE-G</t>
+  </si>
+  <si>
+    <t>30/07/2026, 2:07:23 pm</t>
+  </si>
+  <si>
+    <t>Nelson Paint Saddar A</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 2087 BEIGE-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE511 SEA BLUE-Q</t>
+  </si>
+  <si>
+    <t>31/07/2026, 9:15:49 am</t>
+  </si>
+  <si>
+    <t>Khan traders</t>
+  </si>
+  <si>
+    <t>BOLD OIL BASED PRIMER 7703-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9071 BRAIN TREE ROAD-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE522 SMOKE GREY-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE507 PUMICE-G</t>
+  </si>
+  <si>
+    <t>31/07/2026, 1:41:03 pm</t>
+  </si>
+  <si>
+    <t>g.trader</t>
+  </si>
+  <si>
+    <t>54838209572925</t>
+  </si>
+  <si>
+    <t>نعمان پینٹ</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 03 WHITE-G</t>
+  </si>
+  <si>
+    <t>01/08/2026, 9:43:56 am</t>
+  </si>
+  <si>
+    <t>COLOUR CENTRE</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9970 FRESH GREEN-G</t>
+  </si>
+  <si>
+    <t>EXTRA WATER BASED PRIMER 8057-D</t>
+  </si>
+  <si>
+    <t>BOLD WATER BASED PRIMER 7702-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 68 WHITE ASH-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 92 GRAPE-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1949 SAND STONE-G</t>
+  </si>
+  <si>
+    <t>01/08/2026, 10:11:27 am</t>
+  </si>
+  <si>
+    <t>Shalimar Paint B/Pir</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE W/B PRIMER SEALER EX202-D</t>
+  </si>
+  <si>
+    <t>EXTRA WHITE PUTTY 315-D</t>
+  </si>
+  <si>
+    <t>BOLD ACRYLIC PUTTY 7701-D</t>
+  </si>
+  <si>
+    <t>BOLD WATER MATT 6620 THOUSAND NIGHT-G</t>
+  </si>
+  <si>
+    <t>BOLD WATER MATT 6611 COOL GREY-G</t>
+  </si>
+  <si>
+    <t>BOLD WATER MATT 6603 ASH WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9061 SILVER WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 2876 TILE RED-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1951 WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1964 WINTER SKY-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1972 PEARL-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1917 NEW SPICE-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 01 OFF WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 03 WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 26 SEA BLUE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 69 DIYAR-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 62 SIGNAL GREEN-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 51 GOLDEN BROWN-G</t>
+  </si>
+  <si>
+    <t>EXTRA RED OXIDE PRIMER 312-G</t>
+  </si>
+  <si>
+    <t>BOLD WATER MATT 6603 ASH WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1919 ASH WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA OIL BASED PRIMER 311-D</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 80 ONYX-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 97 GREY TOUCH-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 72 REFLECTION-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 230 LITE ASH WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 232 ICE GREY-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 233 WHISPER-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE532 COCOA BROWN-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE517 SIGNAL RED-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE528 CREAM-G</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8809 BEIGE-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8808 SUNSTRAW-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8828 ASH GREY-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8824 LIGHT BLUE-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8830 SMOKE GREY-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8825 VIVID BLUE-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9999 WHITE-G</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8802 OFF WHITE-Q</t>
+  </si>
+  <si>
+    <t>01/08/2026, 10:12:25 am</t>
+  </si>
+  <si>
+    <t>Pak paint saddar</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9069 ICE GREY-G</t>
+  </si>
+  <si>
+    <t>BOLD R.O.P 7704-Q</t>
+  </si>
+  <si>
+    <t>TREND T601 PUTTY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 212 BUFF-Q</t>
+  </si>
+  <si>
+    <t>01/08/2026, 10:27:47 am</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 3141 ALMOND-G</t>
+  </si>
+  <si>
+    <t>01/08/2026, 10:35:07 am</t>
+  </si>
+  <si>
+    <t>Colour Point Nursery</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 69 BLACK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 341 GOLDEN BEIGE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 61-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 57 BLUE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 60 GREEN-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 27 FLAME RED-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8 OXIDE RED-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 30 CHERRY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 98 CHALK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 232 WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 96 PURE WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 221 ANTIQUE WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 6172 SANDSTONE-G</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1970 PEACH-D</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1950 BLACK-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1950 BLACK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9029 IVORY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9021 APPLE WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9071 SMOKE WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9070 GREY-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9988 CAMEO-Q</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9961 STEEL GREY-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9962 WHISPER-Q</t>
+  </si>
+  <si>
+    <t>01/08/2026, 1:04:17 pm</t>
+  </si>
+  <si>
+    <t>karachi Paposh</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 47 GOLDEN YELLOW-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 61 LEATHER BROWN-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 316 SHARP BROWN-Q</t>
+  </si>
+  <si>
+    <t>01/08/2026, 2:08:41 pm</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 63 EARLY DAWN-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 60 SMOKE GREY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8743 ANTIQUE WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 51 GOLDEN BROWN-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 222 SP PRETTY PINK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 224 SP BUBBLE GUM-Q</t>
+  </si>
+  <si>
+    <t>01/08/2026, 2:17:50 pm</t>
+  </si>
+  <si>
+    <t>Test Trading Name</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9996 COCKLE SHEEL-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9996 COCKLE SHEEL-Q</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9996 COCKLE SHEEL-D</t>
+  </si>
+  <si>
+    <t>01/08/2026, 2:36:59 pm</t>
+  </si>
+  <si>
+    <t>Final Touch Classic Paints</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9001 WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9002 BLACK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9007 ZEPHYR-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9012 RED BRICK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9022 COOL GREY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9042 SP SWEET TULIP-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS U9054 OCEAN DIP-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9058 NEW OFF WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9061 SILVER WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9062 DECENT WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9067 WHITE ICE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9068 SP SHEESHAM-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9069 ICE GREY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8768 PEWTER-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 46 LIGHT BLUE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 337 ASH WHITE NEW-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 02 ASH WHITE-D</t>
+  </si>
+  <si>
+    <t>01/08/2026, 5:58:20 pm</t>
+  </si>
+  <si>
+    <t>Color Paint Nummy</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 341 CORIANDER-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 57 COURT GREY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 27 SP STEEL GREY-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 08 COCKLE SHELL-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 98 SP NAVY BLUE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 232 ICE GREY-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 96 SP ROSE LEMON-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 221 SP ALPINE RED-Q</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 6172 PINK PAVAL-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1970 NEW ASH WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1950 BLACK-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1950 BLACK-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9029 SOFT BLUE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9021 ASH WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9071 BRAIN TREE ROAD-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9070 WHISPER-G</t>
+  </si>
+  <si>
+    <t>01/08/2026, 6:05:18 pm</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1951 WHITE-D</t>
+  </si>
+  <si>
+    <t>TREND W/S TP1951 WHITE-G</t>
+  </si>
+  <si>
+    <t>TREND W/S TP1951 WHITE-Q</t>
+  </si>
+  <si>
+    <t>TREND W/S TP1951 WHITE-D</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1951 WHITE-G</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1951 WHITE-Q</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1951 WHITE-D</t>
+  </si>
+  <si>
+    <t>03/08/2026, 10:59:33 am</t>
+  </si>
+  <si>
+    <t>Color Point Nursery</t>
+  </si>
+  <si>
+    <t>03/08/2026, 12:47:00 pm</t>
+  </si>
+  <si>
+    <t>AZHAR BROTHERS PAINT</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 58 CREAM/ASH WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 55 SOFT GREY-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 327 DARK GREY-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 340 ALUMINIUM WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 63 EARLY DAWN-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 40 SP MANGO MOOD-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 22 APPLE GREEN-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8771 PHLOX PINK-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 209 PEACH-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 1:23:15 pm</t>
+  </si>
+  <si>
+    <t>03/08/2026, 2:09:26 pm</t>
+  </si>
+  <si>
+    <t>NELSON ZAVIYAR URGENT BIKE ORDER</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1968 DENIM-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 2:10:34 pm</t>
+  </si>
+  <si>
+    <t>Riaz up jannah Kor</t>
+  </si>
+  <si>
+    <t>03/08/2026, 2:11:38 pm</t>
+  </si>
+  <si>
+    <t>Al madina sita road</t>
+  </si>
+  <si>
+    <t>BOLD WATER BASED PRIMER 7702-D</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1918 BLUE MAGIC-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 2:12:42 pm</t>
+  </si>
+  <si>
+    <t>Dinesh Paint Hyderabad</t>
+  </si>
+  <si>
+    <t>03/08/2026, 2:52:05 pm</t>
+  </si>
+  <si>
+    <t>ZAKA PAINT</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9039 PRETTY PINK-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 48 CORIANDER-G(DPLT)</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8746 ABSTRACT WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8775 NEW ASH WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT U227 ABSTRACT WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 81 OPAL LILAC-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 218 CLASSICAL-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 75 ONION-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 2:57:53 pm</t>
+  </si>
+  <si>
+    <t>ZAKA PAINT G/J</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9059 AZALEA-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 49 MIDDLE BLUE-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8746 ABSTRACT WHITE-Q</t>
+  </si>
+  <si>
+    <t>03/08/2026, 3:10:10 pm</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 100 JET BLACK-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 3:20:49 pm</t>
+  </si>
+  <si>
+    <t>New khattak tipu sultan</t>
+  </si>
+  <si>
+    <t>EXTRA 3IN1 PLASTIC 8055 WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA OIL BASED PRIMER 311-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 3:44:45 pm</t>
+  </si>
+  <si>
+    <t>Al Anwar dhorajee</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1948 SUGAR CANE-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 236 COTTON BALL-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 3:57:28 pm</t>
+  </si>
+  <si>
+    <t>Bilal paint</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 39 SP CHILLI RED-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8772 SP PURPLE-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 39 SP CHILLI RED-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE FLAT PUTTY EX201-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 4:13:35 pm</t>
+  </si>
+  <si>
+    <t>Decorative Colour Bank</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 78 WHITE-G</t>
+  </si>
+  <si>
+    <t>03/08/2026, 4:16:17 pm</t>
+  </si>
+  <si>
+    <t>H.T. PAINTS</t>
+  </si>
+  <si>
+    <t>EXTRA PUTTY-G</t>
+  </si>
+  <si>
+    <t>EXTRA WATER PRIMER-G</t>
+  </si>
+  <si>
+    <t>STAINLESS 9001-G</t>
+  </si>
+  <si>
+    <t>STAINLESS 9050-G</t>
+  </si>
+  <si>
+    <t>KWS. GLOSS VARNISH 1974 CANTON-G</t>
+  </si>
+  <si>
+    <t>KWS. GLOSS VARNISH 3160 CANTON-G</t>
+  </si>
+  <si>
+    <t>KEN 336-G</t>
+  </si>
+  <si>
+    <t>KEN 66-G</t>
+  </si>
+  <si>
+    <t>KEN WHITE-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 8750-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 8751-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 39-G</t>
+  </si>
+  <si>
+    <t>N&amp;P WHITE-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 8766-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 8777-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 22-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 33-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 34-G</t>
+  </si>
+  <si>
+    <t>N&amp;P 8769-G</t>
   </si>
 </sst>
 </file>
@@ -805,7 +1555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K480"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -3520,8 +4270,7855 @@
         <v>19</v>
       </c>
     </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" s="2">
+        <v>18</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G126" t="s">
+        <v>135</v>
+      </c>
+      <c r="H126" t="s">
+        <v>17</v>
+      </c>
+      <c r="I126">
+        <v>5</v>
+      </c>
+      <c r="J126" t="s">
+        <v>18</v>
+      </c>
+      <c r="K126" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="3"/>
+      <c r="F127" s="2"/>
+      <c r="G127" t="s">
+        <v>136</v>
+      </c>
+      <c r="H127" t="s">
+        <v>17</v>
+      </c>
+      <c r="I127">
+        <v>2</v>
+      </c>
+      <c r="J127" t="s">
+        <v>18</v>
+      </c>
+      <c r="K127" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" s="2"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="3"/>
+      <c r="F128" s="2"/>
+      <c r="G128" t="s">
+        <v>137</v>
+      </c>
+      <c r="H128" t="s">
+        <v>17</v>
+      </c>
+      <c r="I128">
+        <v>2</v>
+      </c>
+      <c r="J128" t="s">
+        <v>18</v>
+      </c>
+      <c r="K128" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="3"/>
+      <c r="F129" s="2"/>
+      <c r="G129" t="s">
+        <v>138</v>
+      </c>
+      <c r="H129" t="s">
+        <v>43</v>
+      </c>
+      <c r="I129">
+        <v>4</v>
+      </c>
+      <c r="J129" t="s">
+        <v>18</v>
+      </c>
+      <c r="K129" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" s="2"/>
+      <c r="B130" s="2"/>
+      <c r="C130" s="2"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="3"/>
+      <c r="F130" s="2"/>
+      <c r="G130" t="s">
+        <v>139</v>
+      </c>
+      <c r="H130" t="s">
+        <v>43</v>
+      </c>
+      <c r="I130">
+        <v>2</v>
+      </c>
+      <c r="J130" t="s">
+        <v>18</v>
+      </c>
+      <c r="K130" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" s="2">
+        <v>19</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G132" t="s">
+        <v>142</v>
+      </c>
+      <c r="H132" t="s">
+        <v>17</v>
+      </c>
+      <c r="I132">
+        <v>10</v>
+      </c>
+      <c r="J132" t="s">
+        <v>18</v>
+      </c>
+      <c r="K132" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" s="2">
+        <v>20</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G134" t="s">
+        <v>145</v>
+      </c>
+      <c r="H134" t="s">
+        <v>68</v>
+      </c>
+      <c r="I134">
+        <v>1</v>
+      </c>
+      <c r="J134" t="s">
+        <v>18</v>
+      </c>
+      <c r="K134" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" s="2"/>
+      <c r="B135" s="2"/>
+      <c r="C135" s="2"/>
+      <c r="D135" s="2"/>
+      <c r="E135" s="3"/>
+      <c r="F135" s="2"/>
+      <c r="G135" t="s">
+        <v>146</v>
+      </c>
+      <c r="H135" t="s">
+        <v>68</v>
+      </c>
+      <c r="I135">
+        <v>3</v>
+      </c>
+      <c r="J135" t="s">
+        <v>18</v>
+      </c>
+      <c r="K135" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" s="2">
+        <v>21</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G137" t="s">
+        <v>149</v>
+      </c>
+      <c r="H137" t="s">
+        <v>43</v>
+      </c>
+      <c r="I137">
+        <v>4</v>
+      </c>
+      <c r="J137" t="s">
+        <v>18</v>
+      </c>
+      <c r="K137" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" s="2"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
+      <c r="D138" s="2"/>
+      <c r="E138" s="3"/>
+      <c r="F138" s="2"/>
+      <c r="G138" t="s">
+        <v>145</v>
+      </c>
+      <c r="H138" t="s">
+        <v>43</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138" t="s">
+        <v>18</v>
+      </c>
+      <c r="K138" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" s="2"/>
+      <c r="B139" s="2"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="3"/>
+      <c r="F139" s="2"/>
+      <c r="G139" t="s">
+        <v>146</v>
+      </c>
+      <c r="H139" t="s">
+        <v>43</v>
+      </c>
+      <c r="I139">
+        <v>3</v>
+      </c>
+      <c r="J139" t="s">
+        <v>18</v>
+      </c>
+      <c r="K139" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="2"/>
+      <c r="G140" t="s">
+        <v>150</v>
+      </c>
+      <c r="H140" t="s">
+        <v>17</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140" t="s">
+        <v>18</v>
+      </c>
+      <c r="K140" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="2"/>
+      <c r="G141" t="s">
+        <v>142</v>
+      </c>
+      <c r="H141" t="s">
+        <v>17</v>
+      </c>
+      <c r="I141">
+        <v>2</v>
+      </c>
+      <c r="J141" t="s">
+        <v>18</v>
+      </c>
+      <c r="K141" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" s="2"/>
+      <c r="B142" s="2"/>
+      <c r="C142" s="2"/>
+      <c r="D142" s="2"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="2"/>
+      <c r="G142" t="s">
+        <v>151</v>
+      </c>
+      <c r="H142" t="s">
+        <v>17</v>
+      </c>
+      <c r="I142">
+        <v>3</v>
+      </c>
+      <c r="J142" t="s">
+        <v>18</v>
+      </c>
+      <c r="K142" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" s="2"/>
+      <c r="B143" s="2"/>
+      <c r="C143" s="2"/>
+      <c r="D143" s="2"/>
+      <c r="E143" s="3"/>
+      <c r="F143" s="2"/>
+      <c r="G143" t="s">
+        <v>152</v>
+      </c>
+      <c r="H143" t="s">
+        <v>17</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143" t="s">
+        <v>18</v>
+      </c>
+      <c r="K143" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" s="2">
+        <v>22</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G145" t="s">
+        <v>157</v>
+      </c>
+      <c r="H145" t="s">
+        <v>17</v>
+      </c>
+      <c r="I145">
+        <v>2</v>
+      </c>
+      <c r="J145" t="s">
+        <v>18</v>
+      </c>
+      <c r="K145" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" s="2"/>
+      <c r="B146" s="2"/>
+      <c r="C146" s="2"/>
+      <c r="D146" s="2"/>
+      <c r="E146" s="3"/>
+      <c r="F146" s="2"/>
+      <c r="G146" t="s">
+        <v>142</v>
+      </c>
+      <c r="H146" t="s">
+        <v>17</v>
+      </c>
+      <c r="I146">
+        <v>3</v>
+      </c>
+      <c r="J146" t="s">
+        <v>18</v>
+      </c>
+      <c r="K146" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" s="2"/>
+      <c r="B147" s="2"/>
+      <c r="C147" s="2"/>
+      <c r="D147" s="2"/>
+      <c r="E147" s="3"/>
+      <c r="F147" s="2"/>
+      <c r="G147" t="s">
+        <v>52</v>
+      </c>
+      <c r="H147" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147">
+        <v>1</v>
+      </c>
+      <c r="J147" t="s">
+        <v>18</v>
+      </c>
+      <c r="K147" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" s="2">
+        <v>23</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G149" t="s">
+        <v>160</v>
+      </c>
+      <c r="H149" t="s">
+        <v>17</v>
+      </c>
+      <c r="I149">
+        <v>3</v>
+      </c>
+      <c r="J149" t="s">
+        <v>18</v>
+      </c>
+      <c r="K149" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" s="2"/>
+      <c r="B150" s="2"/>
+      <c r="C150" s="2"/>
+      <c r="D150" s="2"/>
+      <c r="E150" s="3"/>
+      <c r="F150" s="2"/>
+      <c r="G150" t="s">
+        <v>161</v>
+      </c>
+      <c r="H150" t="s">
+        <v>36</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="J150" t="s">
+        <v>18</v>
+      </c>
+      <c r="K150" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" s="2"/>
+      <c r="B151" s="2"/>
+      <c r="C151" s="2"/>
+      <c r="D151" s="2"/>
+      <c r="E151" s="3"/>
+      <c r="F151" s="2"/>
+      <c r="G151" t="s">
+        <v>162</v>
+      </c>
+      <c r="H151" t="s">
+        <v>17</v>
+      </c>
+      <c r="I151">
+        <v>5</v>
+      </c>
+      <c r="J151" t="s">
+        <v>18</v>
+      </c>
+      <c r="K151" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" s="2"/>
+      <c r="B152" s="2"/>
+      <c r="C152" s="2"/>
+      <c r="D152" s="2"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="2"/>
+      <c r="G152" t="s">
+        <v>163</v>
+      </c>
+      <c r="H152" t="s">
+        <v>43</v>
+      </c>
+      <c r="I152">
+        <v>2</v>
+      </c>
+      <c r="J152" t="s">
+        <v>18</v>
+      </c>
+      <c r="K152" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" s="2"/>
+      <c r="B153" s="2"/>
+      <c r="C153" s="2"/>
+      <c r="D153" s="2"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="2"/>
+      <c r="G153" t="s">
+        <v>164</v>
+      </c>
+      <c r="H153" t="s">
+        <v>17</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="J153" t="s">
+        <v>18</v>
+      </c>
+      <c r="K153" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" s="2"/>
+      <c r="B154" s="2"/>
+      <c r="C154" s="2"/>
+      <c r="D154" s="2"/>
+      <c r="E154" s="3"/>
+      <c r="F154" s="2"/>
+      <c r="G154" t="s">
+        <v>165</v>
+      </c>
+      <c r="H154" t="s">
+        <v>17</v>
+      </c>
+      <c r="I154">
+        <v>3</v>
+      </c>
+      <c r="J154" t="s">
+        <v>18</v>
+      </c>
+      <c r="K154" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>24</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G156" t="s">
+        <v>168</v>
+      </c>
+      <c r="H156" t="s">
+        <v>36</v>
+      </c>
+      <c r="I156">
+        <v>10</v>
+      </c>
+      <c r="J156" t="s">
+        <v>18</v>
+      </c>
+      <c r="K156" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="2"/>
+      <c r="B157" s="2"/>
+      <c r="C157" s="2"/>
+      <c r="D157" s="2"/>
+      <c r="E157" s="3"/>
+      <c r="F157" s="2"/>
+      <c r="G157" t="s">
+        <v>169</v>
+      </c>
+      <c r="H157" t="s">
+        <v>36</v>
+      </c>
+      <c r="I157">
+        <v>10</v>
+      </c>
+      <c r="J157" t="s">
+        <v>18</v>
+      </c>
+      <c r="K157" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" s="2"/>
+      <c r="B158" s="2"/>
+      <c r="C158" s="2"/>
+      <c r="D158" s="2"/>
+      <c r="E158" s="3"/>
+      <c r="F158" s="2"/>
+      <c r="G158" t="s">
+        <v>170</v>
+      </c>
+      <c r="H158" t="s">
+        <v>36</v>
+      </c>
+      <c r="I158">
+        <v>10</v>
+      </c>
+      <c r="J158" t="s">
+        <v>18</v>
+      </c>
+      <c r="K158" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" s="2"/>
+      <c r="B159" s="2"/>
+      <c r="C159" s="2"/>
+      <c r="D159" s="2"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="2"/>
+      <c r="G159" t="s">
+        <v>88</v>
+      </c>
+      <c r="H159" t="s">
+        <v>17</v>
+      </c>
+      <c r="I159">
+        <v>20</v>
+      </c>
+      <c r="J159" t="s">
+        <v>18</v>
+      </c>
+      <c r="K159" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" s="2"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="2"/>
+      <c r="D160" s="2"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="2"/>
+      <c r="G160" t="s">
+        <v>171</v>
+      </c>
+      <c r="H160" t="s">
+        <v>17</v>
+      </c>
+      <c r="I160">
+        <v>3</v>
+      </c>
+      <c r="J160" t="s">
+        <v>18</v>
+      </c>
+      <c r="K160" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" s="2"/>
+      <c r="B161" s="2"/>
+      <c r="C161" s="2"/>
+      <c r="D161" s="2"/>
+      <c r="E161" s="3"/>
+      <c r="F161" s="2"/>
+      <c r="G161" t="s">
+        <v>172</v>
+      </c>
+      <c r="H161" t="s">
+        <v>17</v>
+      </c>
+      <c r="I161">
+        <v>5</v>
+      </c>
+      <c r="J161" t="s">
+        <v>18</v>
+      </c>
+      <c r="K161" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" s="2"/>
+      <c r="B162" s="2"/>
+      <c r="C162" s="2"/>
+      <c r="D162" s="2"/>
+      <c r="E162" s="3"/>
+      <c r="F162" s="2"/>
+      <c r="G162" t="s">
+        <v>173</v>
+      </c>
+      <c r="H162" t="s">
+        <v>17</v>
+      </c>
+      <c r="I162">
+        <v>3</v>
+      </c>
+      <c r="J162" t="s">
+        <v>18</v>
+      </c>
+      <c r="K162" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" s="2"/>
+      <c r="B163" s="2"/>
+      <c r="C163" s="2"/>
+      <c r="D163" s="2"/>
+      <c r="E163" s="3"/>
+      <c r="F163" s="2"/>
+      <c r="G163" t="s">
+        <v>174</v>
+      </c>
+      <c r="H163" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163">
+        <v>5</v>
+      </c>
+      <c r="J163" t="s">
+        <v>18</v>
+      </c>
+      <c r="K163" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" s="2"/>
+      <c r="B164" s="2"/>
+      <c r="C164" s="2"/>
+      <c r="D164" s="2"/>
+      <c r="E164" s="3"/>
+      <c r="F164" s="2"/>
+      <c r="G164" t="s">
+        <v>175</v>
+      </c>
+      <c r="H164" t="s">
+        <v>17</v>
+      </c>
+      <c r="I164">
+        <v>18</v>
+      </c>
+      <c r="J164" t="s">
+        <v>18</v>
+      </c>
+      <c r="K164" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" s="2"/>
+      <c r="B165" s="2"/>
+      <c r="C165" s="2"/>
+      <c r="D165" s="2"/>
+      <c r="E165" s="3"/>
+      <c r="F165" s="2"/>
+      <c r="G165" t="s">
+        <v>176</v>
+      </c>
+      <c r="H165" t="s">
+        <v>17</v>
+      </c>
+      <c r="I165">
+        <v>14</v>
+      </c>
+      <c r="J165" t="s">
+        <v>18</v>
+      </c>
+      <c r="K165" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" s="2"/>
+      <c r="B166" s="2"/>
+      <c r="C166" s="2"/>
+      <c r="D166" s="2"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="2"/>
+      <c r="G166" t="s">
+        <v>177</v>
+      </c>
+      <c r="H166" t="s">
+        <v>17</v>
+      </c>
+      <c r="I166">
+        <v>3</v>
+      </c>
+      <c r="J166" t="s">
+        <v>18</v>
+      </c>
+      <c r="K166" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" s="2"/>
+      <c r="B167" s="2"/>
+      <c r="C167" s="2"/>
+      <c r="D167" s="2"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="2"/>
+      <c r="G167" t="s">
+        <v>178</v>
+      </c>
+      <c r="H167" t="s">
+        <v>17</v>
+      </c>
+      <c r="I167">
+        <v>5</v>
+      </c>
+      <c r="J167" t="s">
+        <v>18</v>
+      </c>
+      <c r="K167" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" s="2"/>
+      <c r="B168" s="2"/>
+      <c r="C168" s="2"/>
+      <c r="D168" s="2"/>
+      <c r="E168" s="3"/>
+      <c r="F168" s="2"/>
+      <c r="G168" t="s">
+        <v>179</v>
+      </c>
+      <c r="H168" t="s">
+        <v>17</v>
+      </c>
+      <c r="I168">
+        <v>4</v>
+      </c>
+      <c r="J168" t="s">
+        <v>18</v>
+      </c>
+      <c r="K168" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" s="2"/>
+      <c r="B169" s="2"/>
+      <c r="C169" s="2"/>
+      <c r="D169" s="2"/>
+      <c r="E169" s="3"/>
+      <c r="F169" s="2"/>
+      <c r="G169" t="s">
+        <v>180</v>
+      </c>
+      <c r="H169" t="s">
+        <v>17</v>
+      </c>
+      <c r="I169">
+        <v>5</v>
+      </c>
+      <c r="J169" t="s">
+        <v>18</v>
+      </c>
+      <c r="K169" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" s="2"/>
+      <c r="B170" s="2"/>
+      <c r="C170" s="2"/>
+      <c r="D170" s="2"/>
+      <c r="E170" s="3"/>
+      <c r="F170" s="2"/>
+      <c r="G170" t="s">
+        <v>181</v>
+      </c>
+      <c r="H170" t="s">
+        <v>36</v>
+      </c>
+      <c r="I170">
+        <v>5</v>
+      </c>
+      <c r="J170" t="s">
+        <v>18</v>
+      </c>
+      <c r="K170" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="3"/>
+      <c r="F171" s="2"/>
+      <c r="G171" t="s">
+        <v>181</v>
+      </c>
+      <c r="H171" t="s">
+        <v>36</v>
+      </c>
+      <c r="I171">
+        <v>5</v>
+      </c>
+      <c r="J171" t="s">
+        <v>18</v>
+      </c>
+      <c r="K171" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="2"/>
+      <c r="G172" t="s">
+        <v>157</v>
+      </c>
+      <c r="H172" t="s">
+        <v>17</v>
+      </c>
+      <c r="I172">
+        <v>10</v>
+      </c>
+      <c r="J172" t="s">
+        <v>18</v>
+      </c>
+      <c r="K172" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="2"/>
+      <c r="G173" t="s">
+        <v>182</v>
+      </c>
+      <c r="H173" t="s">
+        <v>17</v>
+      </c>
+      <c r="I173">
+        <v>4</v>
+      </c>
+      <c r="J173" t="s">
+        <v>18</v>
+      </c>
+      <c r="K173" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="3"/>
+      <c r="F174" s="2"/>
+      <c r="G174" t="s">
+        <v>183</v>
+      </c>
+      <c r="H174" t="s">
+        <v>17</v>
+      </c>
+      <c r="I174">
+        <v>5</v>
+      </c>
+      <c r="J174" t="s">
+        <v>18</v>
+      </c>
+      <c r="K174" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="3"/>
+      <c r="F175" s="2"/>
+      <c r="G175" t="s">
+        <v>184</v>
+      </c>
+      <c r="H175" t="s">
+        <v>17</v>
+      </c>
+      <c r="I175">
+        <v>3</v>
+      </c>
+      <c r="J175" t="s">
+        <v>18</v>
+      </c>
+      <c r="K175" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="3"/>
+      <c r="F176" s="2"/>
+      <c r="G176" t="s">
+        <v>185</v>
+      </c>
+      <c r="H176" t="s">
+        <v>17</v>
+      </c>
+      <c r="I176">
+        <v>5</v>
+      </c>
+      <c r="J176" t="s">
+        <v>18</v>
+      </c>
+      <c r="K176" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" s="2"/>
+      <c r="B177" s="2"/>
+      <c r="C177" s="2"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="3"/>
+      <c r="F177" s="2"/>
+      <c r="G177" t="s">
+        <v>186</v>
+      </c>
+      <c r="H177" t="s">
+        <v>17</v>
+      </c>
+      <c r="I177">
+        <v>5</v>
+      </c>
+      <c r="J177" t="s">
+        <v>18</v>
+      </c>
+      <c r="K177" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" s="2"/>
+      <c r="B178" s="2"/>
+      <c r="C178" s="2"/>
+      <c r="D178" s="2"/>
+      <c r="E178" s="3"/>
+      <c r="F178" s="2"/>
+      <c r="G178" t="s">
+        <v>187</v>
+      </c>
+      <c r="H178" t="s">
+        <v>36</v>
+      </c>
+      <c r="I178">
+        <v>2</v>
+      </c>
+      <c r="J178" t="s">
+        <v>18</v>
+      </c>
+      <c r="K178" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" s="2"/>
+      <c r="B179" s="2"/>
+      <c r="C179" s="2"/>
+      <c r="D179" s="2"/>
+      <c r="E179" s="3"/>
+      <c r="F179" s="2"/>
+      <c r="G179" t="s">
+        <v>188</v>
+      </c>
+      <c r="H179" t="s">
+        <v>36</v>
+      </c>
+      <c r="I179">
+        <v>2</v>
+      </c>
+      <c r="J179" t="s">
+        <v>18</v>
+      </c>
+      <c r="K179" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" s="2"/>
+      <c r="B180" s="2"/>
+      <c r="C180" s="2"/>
+      <c r="D180" s="2"/>
+      <c r="E180" s="3"/>
+      <c r="F180" s="2"/>
+      <c r="G180" t="s">
+        <v>161</v>
+      </c>
+      <c r="H180" t="s">
+        <v>36</v>
+      </c>
+      <c r="I180">
+        <v>5</v>
+      </c>
+      <c r="J180" t="s">
+        <v>18</v>
+      </c>
+      <c r="K180" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" s="2"/>
+      <c r="B181" s="2"/>
+      <c r="C181" s="2"/>
+      <c r="D181" s="2"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="2"/>
+      <c r="G181" t="s">
+        <v>189</v>
+      </c>
+      <c r="H181" t="s">
+        <v>36</v>
+      </c>
+      <c r="I181">
+        <v>5</v>
+      </c>
+      <c r="J181" t="s">
+        <v>18</v>
+      </c>
+      <c r="K181" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" s="2"/>
+      <c r="B182" s="2"/>
+      <c r="C182" s="2"/>
+      <c r="D182" s="2"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="2"/>
+      <c r="G182" t="s">
+        <v>190</v>
+      </c>
+      <c r="H182" t="s">
+        <v>17</v>
+      </c>
+      <c r="I182">
+        <v>2</v>
+      </c>
+      <c r="J182" t="s">
+        <v>18</v>
+      </c>
+      <c r="K182" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" s="2"/>
+      <c r="B183" s="2"/>
+      <c r="C183" s="2"/>
+      <c r="D183" s="2"/>
+      <c r="E183" s="3"/>
+      <c r="F183" s="2"/>
+      <c r="G183" t="s">
+        <v>191</v>
+      </c>
+      <c r="H183" t="s">
+        <v>17</v>
+      </c>
+      <c r="I183">
+        <v>2</v>
+      </c>
+      <c r="J183" t="s">
+        <v>18</v>
+      </c>
+      <c r="K183" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" s="2"/>
+      <c r="B184" s="2"/>
+      <c r="C184" s="2"/>
+      <c r="D184" s="2"/>
+      <c r="E184" s="3"/>
+      <c r="F184" s="2"/>
+      <c r="G184" t="s">
+        <v>192</v>
+      </c>
+      <c r="H184" t="s">
+        <v>17</v>
+      </c>
+      <c r="I184">
+        <v>2</v>
+      </c>
+      <c r="J184" t="s">
+        <v>18</v>
+      </c>
+      <c r="K184" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" s="2"/>
+      <c r="B185" s="2"/>
+      <c r="C185" s="2"/>
+      <c r="D185" s="2"/>
+      <c r="E185" s="3"/>
+      <c r="F185" s="2"/>
+      <c r="G185" t="s">
+        <v>193</v>
+      </c>
+      <c r="H185" t="s">
+        <v>17</v>
+      </c>
+      <c r="I185">
+        <v>3</v>
+      </c>
+      <c r="J185" t="s">
+        <v>18</v>
+      </c>
+      <c r="K185" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
+      <c r="E186" s="3"/>
+      <c r="F186" s="2"/>
+      <c r="G186" t="s">
+        <v>194</v>
+      </c>
+      <c r="H186" t="s">
+        <v>17</v>
+      </c>
+      <c r="I186">
+        <v>2</v>
+      </c>
+      <c r="J186" t="s">
+        <v>18</v>
+      </c>
+      <c r="K186" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" s="2"/>
+      <c r="B187" s="2"/>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
+      <c r="E187" s="3"/>
+      <c r="F187" s="2"/>
+      <c r="G187" t="s">
+        <v>195</v>
+      </c>
+      <c r="H187" t="s">
+        <v>17</v>
+      </c>
+      <c r="I187">
+        <v>2</v>
+      </c>
+      <c r="J187" t="s">
+        <v>18</v>
+      </c>
+      <c r="K187" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" s="2"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
+      <c r="D188" s="2"/>
+      <c r="E188" s="3"/>
+      <c r="F188" s="2"/>
+      <c r="G188" t="s">
+        <v>196</v>
+      </c>
+      <c r="H188" t="s">
+        <v>17</v>
+      </c>
+      <c r="I188">
+        <v>6</v>
+      </c>
+      <c r="J188" t="s">
+        <v>18</v>
+      </c>
+      <c r="K188" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" s="2"/>
+      <c r="B189" s="2"/>
+      <c r="C189" s="2"/>
+      <c r="D189" s="2"/>
+      <c r="E189" s="3"/>
+      <c r="F189" s="2"/>
+      <c r="G189" t="s">
+        <v>197</v>
+      </c>
+      <c r="H189" t="s">
+        <v>17</v>
+      </c>
+      <c r="I189">
+        <v>2</v>
+      </c>
+      <c r="J189" t="s">
+        <v>18</v>
+      </c>
+      <c r="K189" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" s="2"/>
+      <c r="B190" s="2"/>
+      <c r="C190" s="2"/>
+      <c r="D190" s="2"/>
+      <c r="E190" s="3"/>
+      <c r="F190" s="2"/>
+      <c r="G190" t="s">
+        <v>198</v>
+      </c>
+      <c r="H190" t="s">
+        <v>17</v>
+      </c>
+      <c r="I190">
+        <v>4</v>
+      </c>
+      <c r="J190" t="s">
+        <v>18</v>
+      </c>
+      <c r="K190" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" s="2"/>
+      <c r="B191" s="2"/>
+      <c r="C191" s="2"/>
+      <c r="D191" s="2"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="2"/>
+      <c r="G191" t="s">
+        <v>199</v>
+      </c>
+      <c r="H191" t="s">
+        <v>43</v>
+      </c>
+      <c r="I191">
+        <v>2</v>
+      </c>
+      <c r="J191" t="s">
+        <v>18</v>
+      </c>
+      <c r="K191" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" s="2"/>
+      <c r="B192" s="2"/>
+      <c r="C192" s="2"/>
+      <c r="D192" s="2"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="2"/>
+      <c r="G192" t="s">
+        <v>200</v>
+      </c>
+      <c r="H192" t="s">
+        <v>43</v>
+      </c>
+      <c r="I192">
+        <v>2</v>
+      </c>
+      <c r="J192" t="s">
+        <v>18</v>
+      </c>
+      <c r="K192" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" s="2"/>
+      <c r="B193" s="2"/>
+      <c r="C193" s="2"/>
+      <c r="D193" s="2"/>
+      <c r="E193" s="3"/>
+      <c r="F193" s="2"/>
+      <c r="G193" t="s">
+        <v>201</v>
+      </c>
+      <c r="H193" t="s">
+        <v>43</v>
+      </c>
+      <c r="I193">
+        <v>2</v>
+      </c>
+      <c r="J193" t="s">
+        <v>18</v>
+      </c>
+      <c r="K193" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" s="2"/>
+      <c r="B194" s="2"/>
+      <c r="C194" s="2"/>
+      <c r="D194" s="2"/>
+      <c r="E194" s="3"/>
+      <c r="F194" s="2"/>
+      <c r="G194" t="s">
+        <v>202</v>
+      </c>
+      <c r="H194" t="s">
+        <v>43</v>
+      </c>
+      <c r="I194">
+        <v>2</v>
+      </c>
+      <c r="J194" t="s">
+        <v>18</v>
+      </c>
+      <c r="K194" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" s="2"/>
+      <c r="B195" s="2"/>
+      <c r="C195" s="2"/>
+      <c r="D195" s="2"/>
+      <c r="E195" s="3"/>
+      <c r="F195" s="2"/>
+      <c r="G195" t="s">
+        <v>203</v>
+      </c>
+      <c r="H195" t="s">
+        <v>43</v>
+      </c>
+      <c r="I195">
+        <v>4</v>
+      </c>
+      <c r="J195" t="s">
+        <v>18</v>
+      </c>
+      <c r="K195" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" s="2"/>
+      <c r="B196" s="2"/>
+      <c r="C196" s="2"/>
+      <c r="D196" s="2"/>
+      <c r="E196" s="3"/>
+      <c r="F196" s="2"/>
+      <c r="G196" t="s">
+        <v>204</v>
+      </c>
+      <c r="H196" t="s">
+        <v>17</v>
+      </c>
+      <c r="I196">
+        <v>4</v>
+      </c>
+      <c r="J196" t="s">
+        <v>18</v>
+      </c>
+      <c r="K196" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" s="2"/>
+      <c r="B197" s="2"/>
+      <c r="C197" s="2"/>
+      <c r="D197" s="2"/>
+      <c r="E197" s="3"/>
+      <c r="F197" s="2"/>
+      <c r="G197" t="s">
+        <v>205</v>
+      </c>
+      <c r="H197" t="s">
+        <v>17</v>
+      </c>
+      <c r="I197">
+        <v>5</v>
+      </c>
+      <c r="J197" t="s">
+        <v>18</v>
+      </c>
+      <c r="K197" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" s="2"/>
+      <c r="B198" s="2"/>
+      <c r="C198" s="2"/>
+      <c r="D198" s="2"/>
+      <c r="E198" s="3"/>
+      <c r="F198" s="2"/>
+      <c r="G198" t="s">
+        <v>206</v>
+      </c>
+      <c r="H198" t="s">
+        <v>43</v>
+      </c>
+      <c r="I198">
+        <v>3</v>
+      </c>
+      <c r="J198" t="s">
+        <v>18</v>
+      </c>
+      <c r="K198" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" s="2">
+        <v>25</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E200" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G200" t="s">
+        <v>209</v>
+      </c>
+      <c r="H200" t="s">
+        <v>17</v>
+      </c>
+      <c r="I200">
+        <v>2</v>
+      </c>
+      <c r="J200" t="s">
+        <v>18</v>
+      </c>
+      <c r="K200" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" s="2"/>
+      <c r="B201" s="2"/>
+      <c r="C201" s="2"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="3"/>
+      <c r="F201" s="2"/>
+      <c r="G201" t="s">
+        <v>210</v>
+      </c>
+      <c r="H201" t="s">
+        <v>43</v>
+      </c>
+      <c r="I201">
+        <v>2</v>
+      </c>
+      <c r="J201" t="s">
+        <v>18</v>
+      </c>
+      <c r="K201" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" s="2"/>
+      <c r="B202" s="2"/>
+      <c r="C202" s="2"/>
+      <c r="D202" s="2"/>
+      <c r="E202" s="3"/>
+      <c r="F202" s="2"/>
+      <c r="G202" t="s">
+        <v>211</v>
+      </c>
+      <c r="H202" t="s">
+        <v>43</v>
+      </c>
+      <c r="I202">
+        <v>2</v>
+      </c>
+      <c r="J202" t="s">
+        <v>18</v>
+      </c>
+      <c r="K202" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" s="2"/>
+      <c r="B203" s="2"/>
+      <c r="C203" s="2"/>
+      <c r="D203" s="2"/>
+      <c r="E203" s="3"/>
+      <c r="F203" s="2"/>
+      <c r="G203" t="s">
+        <v>149</v>
+      </c>
+      <c r="H203" t="s">
+        <v>43</v>
+      </c>
+      <c r="I203">
+        <v>3</v>
+      </c>
+      <c r="J203" t="s">
+        <v>18</v>
+      </c>
+      <c r="K203" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="3"/>
+      <c r="F204" s="2"/>
+      <c r="G204" t="s">
+        <v>212</v>
+      </c>
+      <c r="H204" t="s">
+        <v>43</v>
+      </c>
+      <c r="I204">
+        <v>1</v>
+      </c>
+      <c r="J204" t="s">
+        <v>18</v>
+      </c>
+      <c r="K204" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" s="2">
+        <v>26</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" t="s">
+        <v>214</v>
+      </c>
+      <c r="H206" t="s">
+        <v>17</v>
+      </c>
+      <c r="I206">
+        <v>5</v>
+      </c>
+      <c r="J206" t="s">
+        <v>18</v>
+      </c>
+      <c r="K206" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="3"/>
+      <c r="F207" s="2"/>
+      <c r="G207" t="s">
+        <v>205</v>
+      </c>
+      <c r="H207" t="s">
+        <v>17</v>
+      </c>
+      <c r="I207">
+        <v>4</v>
+      </c>
+      <c r="J207" t="s">
+        <v>18</v>
+      </c>
+      <c r="K207" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" s="2">
+        <v>27</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G209" t="s">
+        <v>217</v>
+      </c>
+      <c r="H209" t="s">
+        <v>43</v>
+      </c>
+      <c r="I209">
+        <v>1</v>
+      </c>
+      <c r="J209" t="s">
+        <v>18</v>
+      </c>
+      <c r="K209" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" s="2"/>
+      <c r="B210" s="2"/>
+      <c r="C210" s="2"/>
+      <c r="D210" s="2"/>
+      <c r="E210" s="3"/>
+      <c r="F210" s="2"/>
+      <c r="G210" t="s">
+        <v>218</v>
+      </c>
+      <c r="H210" t="s">
+        <v>17</v>
+      </c>
+      <c r="I210">
+        <v>2</v>
+      </c>
+      <c r="J210" t="s">
+        <v>18</v>
+      </c>
+      <c r="K210" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" s="2"/>
+      <c r="B211" s="2"/>
+      <c r="C211" s="2"/>
+      <c r="D211" s="2"/>
+      <c r="E211" s="3"/>
+      <c r="F211" s="2"/>
+      <c r="G211" t="s">
+        <v>219</v>
+      </c>
+      <c r="H211" t="s">
+        <v>43</v>
+      </c>
+      <c r="I211">
+        <v>1</v>
+      </c>
+      <c r="J211" t="s">
+        <v>18</v>
+      </c>
+      <c r="K211" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" s="2"/>
+      <c r="B212" s="2"/>
+      <c r="C212" s="2"/>
+      <c r="D212" s="2"/>
+      <c r="E212" s="3"/>
+      <c r="F212" s="2"/>
+      <c r="G212" t="s">
+        <v>220</v>
+      </c>
+      <c r="H212" t="s">
+        <v>43</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212" t="s">
+        <v>18</v>
+      </c>
+      <c r="K212" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" s="2"/>
+      <c r="B213" s="2"/>
+      <c r="C213" s="2"/>
+      <c r="D213" s="2"/>
+      <c r="E213" s="3"/>
+      <c r="F213" s="2"/>
+      <c r="G213" t="s">
+        <v>221</v>
+      </c>
+      <c r="H213" t="s">
+        <v>43</v>
+      </c>
+      <c r="I213">
+        <v>1</v>
+      </c>
+      <c r="J213" t="s">
+        <v>18</v>
+      </c>
+      <c r="K213" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" s="2"/>
+      <c r="B214" s="2"/>
+      <c r="C214" s="2"/>
+      <c r="D214" s="2"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="2"/>
+      <c r="G214" t="s">
+        <v>222</v>
+      </c>
+      <c r="H214" t="s">
+        <v>17</v>
+      </c>
+      <c r="I214">
+        <v>12</v>
+      </c>
+      <c r="J214" t="s">
+        <v>18</v>
+      </c>
+      <c r="K214" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" s="2"/>
+      <c r="B215" s="2"/>
+      <c r="C215" s="2"/>
+      <c r="D215" s="2"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="2"/>
+      <c r="G215" t="s">
+        <v>223</v>
+      </c>
+      <c r="H215" t="s">
+        <v>17</v>
+      </c>
+      <c r="I215">
+        <v>1</v>
+      </c>
+      <c r="J215" t="s">
+        <v>18</v>
+      </c>
+      <c r="K215" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" s="2"/>
+      <c r="B216" s="2"/>
+      <c r="C216" s="2"/>
+      <c r="D216" s="2"/>
+      <c r="E216" s="3"/>
+      <c r="F216" s="2"/>
+      <c r="G216" t="s">
+        <v>224</v>
+      </c>
+      <c r="H216" t="s">
+        <v>43</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216" t="s">
+        <v>18</v>
+      </c>
+      <c r="K216" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" s="2"/>
+      <c r="B217" s="2"/>
+      <c r="C217" s="2"/>
+      <c r="D217" s="2"/>
+      <c r="E217" s="3"/>
+      <c r="F217" s="2"/>
+      <c r="G217" t="s">
+        <v>225</v>
+      </c>
+      <c r="H217" t="s">
+        <v>43</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217" t="s">
+        <v>18</v>
+      </c>
+      <c r="K217" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" s="2"/>
+      <c r="B218" s="2"/>
+      <c r="C218" s="2"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="3"/>
+      <c r="F218" s="2"/>
+      <c r="G218" t="s">
+        <v>226</v>
+      </c>
+      <c r="H218" t="s">
+        <v>43</v>
+      </c>
+      <c r="I218">
+        <v>1</v>
+      </c>
+      <c r="J218" t="s">
+        <v>18</v>
+      </c>
+      <c r="K218" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" s="2"/>
+      <c r="B219" s="2"/>
+      <c r="C219" s="2"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="3"/>
+      <c r="F219" s="2"/>
+      <c r="G219" t="s">
+        <v>227</v>
+      </c>
+      <c r="H219" t="s">
+        <v>43</v>
+      </c>
+      <c r="I219">
+        <v>4</v>
+      </c>
+      <c r="J219" t="s">
+        <v>18</v>
+      </c>
+      <c r="K219" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" s="2"/>
+      <c r="B220" s="2"/>
+      <c r="C220" s="2"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="3"/>
+      <c r="F220" s="2"/>
+      <c r="G220" t="s">
+        <v>228</v>
+      </c>
+      <c r="H220" t="s">
+        <v>43</v>
+      </c>
+      <c r="I220">
+        <v>1</v>
+      </c>
+      <c r="J220" t="s">
+        <v>18</v>
+      </c>
+      <c r="K220" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" s="2"/>
+      <c r="B221" s="2"/>
+      <c r="C221" s="2"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="3"/>
+      <c r="F221" s="2"/>
+      <c r="G221" t="s">
+        <v>229</v>
+      </c>
+      <c r="H221" t="s">
+        <v>17</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221" t="s">
+        <v>18</v>
+      </c>
+      <c r="K221" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" s="2"/>
+      <c r="B222" s="2"/>
+      <c r="C222" s="2"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="3"/>
+      <c r="F222" s="2"/>
+      <c r="G222" t="s">
+        <v>230</v>
+      </c>
+      <c r="H222" t="s">
+        <v>36</v>
+      </c>
+      <c r="I222">
+        <v>1</v>
+      </c>
+      <c r="J222" t="s">
+        <v>18</v>
+      </c>
+      <c r="K222" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223" s="2"/>
+      <c r="B223" s="2"/>
+      <c r="C223" s="2"/>
+      <c r="D223" s="2"/>
+      <c r="E223" s="3"/>
+      <c r="F223" s="2"/>
+      <c r="G223" t="s">
+        <v>231</v>
+      </c>
+      <c r="H223" t="s">
+        <v>17</v>
+      </c>
+      <c r="I223">
+        <v>3</v>
+      </c>
+      <c r="J223" t="s">
+        <v>18</v>
+      </c>
+      <c r="K223" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224" s="2"/>
+      <c r="B224" s="2"/>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2"/>
+      <c r="E224" s="3"/>
+      <c r="F224" s="2"/>
+      <c r="G224" t="s">
+        <v>232</v>
+      </c>
+      <c r="H224" t="s">
+        <v>43</v>
+      </c>
+      <c r="I224">
+        <v>2</v>
+      </c>
+      <c r="J224" t="s">
+        <v>18</v>
+      </c>
+      <c r="K224" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225" s="2"/>
+      <c r="B225" s="2"/>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2"/>
+      <c r="E225" s="3"/>
+      <c r="F225" s="2"/>
+      <c r="G225" t="s">
+        <v>233</v>
+      </c>
+      <c r="H225" t="s">
+        <v>43</v>
+      </c>
+      <c r="I225">
+        <v>2</v>
+      </c>
+      <c r="J225" t="s">
+        <v>18</v>
+      </c>
+      <c r="K225" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226" s="2"/>
+      <c r="B226" s="2"/>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2"/>
+      <c r="E226" s="3"/>
+      <c r="F226" s="2"/>
+      <c r="G226" t="s">
+        <v>234</v>
+      </c>
+      <c r="H226" t="s">
+        <v>43</v>
+      </c>
+      <c r="I226">
+        <v>2</v>
+      </c>
+      <c r="J226" t="s">
+        <v>18</v>
+      </c>
+      <c r="K226" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227" s="2"/>
+      <c r="B227" s="2"/>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2"/>
+      <c r="E227" s="3"/>
+      <c r="F227" s="2"/>
+      <c r="G227" t="s">
+        <v>235</v>
+      </c>
+      <c r="H227" t="s">
+        <v>43</v>
+      </c>
+      <c r="I227">
+        <v>3</v>
+      </c>
+      <c r="J227" t="s">
+        <v>18</v>
+      </c>
+      <c r="K227" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228" s="2"/>
+      <c r="B228" s="2"/>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2"/>
+      <c r="E228" s="3"/>
+      <c r="F228" s="2"/>
+      <c r="G228" t="s">
+        <v>236</v>
+      </c>
+      <c r="H228" t="s">
+        <v>17</v>
+      </c>
+      <c r="I228">
+        <v>2</v>
+      </c>
+      <c r="J228" t="s">
+        <v>18</v>
+      </c>
+      <c r="K228" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229" s="2"/>
+      <c r="B229" s="2"/>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2"/>
+      <c r="E229" s="3"/>
+      <c r="F229" s="2"/>
+      <c r="G229" t="s">
+        <v>237</v>
+      </c>
+      <c r="H229" t="s">
+        <v>43</v>
+      </c>
+      <c r="I229">
+        <v>2</v>
+      </c>
+      <c r="J229" t="s">
+        <v>18</v>
+      </c>
+      <c r="K229" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230" s="2"/>
+      <c r="B230" s="2"/>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2"/>
+      <c r="E230" s="3"/>
+      <c r="F230" s="2"/>
+      <c r="G230" t="s">
+        <v>238</v>
+      </c>
+      <c r="H230" t="s">
+        <v>17</v>
+      </c>
+      <c r="I230">
+        <v>1</v>
+      </c>
+      <c r="J230" t="s">
+        <v>18</v>
+      </c>
+      <c r="K230" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231" s="2"/>
+      <c r="B231" s="2"/>
+      <c r="C231" s="2"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="3"/>
+      <c r="F231" s="2"/>
+      <c r="G231" t="s">
+        <v>239</v>
+      </c>
+      <c r="H231" t="s">
+        <v>43</v>
+      </c>
+      <c r="I231">
+        <v>1</v>
+      </c>
+      <c r="J231" t="s">
+        <v>18</v>
+      </c>
+      <c r="K231" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232" s="2"/>
+      <c r="B232" s="2"/>
+      <c r="C232" s="2"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="3"/>
+      <c r="F232" s="2"/>
+      <c r="G232" t="s">
+        <v>48</v>
+      </c>
+      <c r="H232" t="s">
+        <v>17</v>
+      </c>
+      <c r="I232">
+        <v>10</v>
+      </c>
+      <c r="J232" t="s">
+        <v>18</v>
+      </c>
+      <c r="K232" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" s="2"/>
+      <c r="B233" s="2"/>
+      <c r="C233" s="2"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="3"/>
+      <c r="F233" s="2"/>
+      <c r="G233" t="s">
+        <v>71</v>
+      </c>
+      <c r="H233" t="s">
+        <v>43</v>
+      </c>
+      <c r="I233">
+        <v>5</v>
+      </c>
+      <c r="J233" t="s">
+        <v>18</v>
+      </c>
+      <c r="K233" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" s="2">
+        <v>28</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E235" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G235" t="s">
+        <v>52</v>
+      </c>
+      <c r="H235" t="s">
+        <v>43</v>
+      </c>
+      <c r="I235">
+        <v>4</v>
+      </c>
+      <c r="J235" t="s">
+        <v>18</v>
+      </c>
+      <c r="K235" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" s="2"/>
+      <c r="B236" s="2"/>
+      <c r="C236" s="2"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="3"/>
+      <c r="F236" s="2"/>
+      <c r="G236" t="s">
+        <v>242</v>
+      </c>
+      <c r="H236" t="s">
+        <v>43</v>
+      </c>
+      <c r="I236">
+        <v>2</v>
+      </c>
+      <c r="J236" t="s">
+        <v>18</v>
+      </c>
+      <c r="K236" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" s="2"/>
+      <c r="B237" s="2"/>
+      <c r="C237" s="2"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="3"/>
+      <c r="F237" s="2"/>
+      <c r="G237" t="s">
+        <v>243</v>
+      </c>
+      <c r="H237" t="s">
+        <v>43</v>
+      </c>
+      <c r="I237">
+        <v>2</v>
+      </c>
+      <c r="J237" t="s">
+        <v>18</v>
+      </c>
+      <c r="K237" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" s="2"/>
+      <c r="B238" s="2"/>
+      <c r="C238" s="2"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="3"/>
+      <c r="F238" s="2"/>
+      <c r="G238" t="s">
+        <v>58</v>
+      </c>
+      <c r="H238" t="s">
+        <v>43</v>
+      </c>
+      <c r="I238">
+        <v>2</v>
+      </c>
+      <c r="J238" t="s">
+        <v>18</v>
+      </c>
+      <c r="K238" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" s="2"/>
+      <c r="B239" s="2"/>
+      <c r="C239" s="2"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="3"/>
+      <c r="F239" s="2"/>
+      <c r="G239" t="s">
+        <v>82</v>
+      </c>
+      <c r="H239" t="s">
+        <v>43</v>
+      </c>
+      <c r="I239">
+        <v>2</v>
+      </c>
+      <c r="J239" t="s">
+        <v>18</v>
+      </c>
+      <c r="K239" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" s="2"/>
+      <c r="B240" s="2"/>
+      <c r="C240" s="2"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="3"/>
+      <c r="F240" s="2"/>
+      <c r="G240" t="s">
+        <v>244</v>
+      </c>
+      <c r="H240" t="s">
+        <v>43</v>
+      </c>
+      <c r="I240">
+        <v>2</v>
+      </c>
+      <c r="J240" t="s">
+        <v>18</v>
+      </c>
+      <c r="K240" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" s="2"/>
+      <c r="B241" s="2"/>
+      <c r="C241" s="2"/>
+      <c r="D241" s="2"/>
+      <c r="E241" s="3"/>
+      <c r="F241" s="2"/>
+      <c r="G241" t="s">
+        <v>80</v>
+      </c>
+      <c r="H241" t="s">
+        <v>43</v>
+      </c>
+      <c r="I241">
+        <v>2</v>
+      </c>
+      <c r="J241" t="s">
+        <v>18</v>
+      </c>
+      <c r="K241" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" s="2">
+        <v>29</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E243" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G243" t="s">
+        <v>62</v>
+      </c>
+      <c r="H243" t="s">
+        <v>43</v>
+      </c>
+      <c r="I243">
+        <v>1</v>
+      </c>
+      <c r="J243" t="s">
+        <v>18</v>
+      </c>
+      <c r="K243" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" s="2"/>
+      <c r="B244" s="2"/>
+      <c r="C244" s="2"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="3"/>
+      <c r="F244" s="2"/>
+      <c r="G244" t="s">
+        <v>246</v>
+      </c>
+      <c r="H244" t="s">
+        <v>43</v>
+      </c>
+      <c r="I244">
+        <v>1</v>
+      </c>
+      <c r="J244" t="s">
+        <v>18</v>
+      </c>
+      <c r="K244" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" s="2"/>
+      <c r="B245" s="2"/>
+      <c r="C245" s="2"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="3"/>
+      <c r="F245" s="2"/>
+      <c r="G245" t="s">
+        <v>247</v>
+      </c>
+      <c r="H245" t="s">
+        <v>43</v>
+      </c>
+      <c r="I245">
+        <v>2</v>
+      </c>
+      <c r="J245" t="s">
+        <v>18</v>
+      </c>
+      <c r="K245" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" s="2"/>
+      <c r="B246" s="2"/>
+      <c r="C246" s="2"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="3"/>
+      <c r="F246" s="2"/>
+      <c r="G246" t="s">
+        <v>248</v>
+      </c>
+      <c r="H246" t="s">
+        <v>17</v>
+      </c>
+      <c r="I246">
+        <v>2</v>
+      </c>
+      <c r="J246" t="s">
+        <v>18</v>
+      </c>
+      <c r="K246" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" s="2"/>
+      <c r="B247" s="2"/>
+      <c r="C247" s="2"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="3"/>
+      <c r="F247" s="2"/>
+      <c r="G247" t="s">
+        <v>249</v>
+      </c>
+      <c r="H247" t="s">
+        <v>43</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247" t="s">
+        <v>18</v>
+      </c>
+      <c r="K247" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248" s="2"/>
+      <c r="B248" s="2"/>
+      <c r="C248" s="2"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="3"/>
+      <c r="F248" s="2"/>
+      <c r="G248" t="s">
+        <v>250</v>
+      </c>
+      <c r="H248" t="s">
+        <v>43</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248" t="s">
+        <v>18</v>
+      </c>
+      <c r="K248" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249" s="2"/>
+      <c r="B249" s="2"/>
+      <c r="C249" s="2"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="3"/>
+      <c r="F249" s="2"/>
+      <c r="G249" t="s">
+        <v>251</v>
+      </c>
+      <c r="H249" t="s">
+        <v>43</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249" t="s">
+        <v>18</v>
+      </c>
+      <c r="K249" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251" s="2">
+        <v>30</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E251" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G251" t="s">
+        <v>254</v>
+      </c>
+      <c r="H251" t="s">
+        <v>17</v>
+      </c>
+      <c r="I251">
+        <v>2</v>
+      </c>
+      <c r="J251" t="s">
+        <v>18</v>
+      </c>
+      <c r="K251" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" s="2"/>
+      <c r="B252" s="2"/>
+      <c r="C252" s="2"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="3"/>
+      <c r="F252" s="2"/>
+      <c r="G252" t="s">
+        <v>255</v>
+      </c>
+      <c r="H252" t="s">
+        <v>43</v>
+      </c>
+      <c r="I252">
+        <v>2</v>
+      </c>
+      <c r="J252" t="s">
+        <v>18</v>
+      </c>
+      <c r="K252" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253" s="2"/>
+      <c r="B253" s="2"/>
+      <c r="C253" s="2"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="3"/>
+      <c r="F253" s="2"/>
+      <c r="G253" t="s">
+        <v>256</v>
+      </c>
+      <c r="H253" t="s">
+        <v>36</v>
+      </c>
+      <c r="I253">
+        <v>2</v>
+      </c>
+      <c r="J253" t="s">
+        <v>18</v>
+      </c>
+      <c r="K253" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254" s="2"/>
+      <c r="B254" s="2"/>
+      <c r="C254" s="2"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="3"/>
+      <c r="F254" s="2"/>
+      <c r="G254" t="s">
+        <v>108</v>
+      </c>
+      <c r="H254" t="s">
+        <v>17</v>
+      </c>
+      <c r="I254">
+        <v>1</v>
+      </c>
+      <c r="J254" t="s">
+        <v>18</v>
+      </c>
+      <c r="K254" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255" s="2"/>
+      <c r="B255" s="2"/>
+      <c r="C255" s="2"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="3"/>
+      <c r="F255" s="2"/>
+      <c r="G255" t="s">
+        <v>237</v>
+      </c>
+      <c r="H255" t="s">
+        <v>43</v>
+      </c>
+      <c r="I255">
+        <v>2</v>
+      </c>
+      <c r="J255" t="s">
+        <v>18</v>
+      </c>
+      <c r="K255" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256" s="2"/>
+      <c r="B256" s="2"/>
+      <c r="C256" s="2"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="3"/>
+      <c r="F256" s="2"/>
+      <c r="G256" t="s">
+        <v>111</v>
+      </c>
+      <c r="H256" t="s">
+        <v>36</v>
+      </c>
+      <c r="I256">
+        <v>3</v>
+      </c>
+      <c r="J256" t="s">
+        <v>18</v>
+      </c>
+      <c r="K256" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A258" s="2">
+        <v>31</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E258" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="G258" t="s">
+        <v>52</v>
+      </c>
+      <c r="H258" t="s">
+        <v>43</v>
+      </c>
+      <c r="I258">
+        <v>4</v>
+      </c>
+      <c r="J258" t="s">
+        <v>18</v>
+      </c>
+      <c r="K258" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A259" s="2"/>
+      <c r="B259" s="2"/>
+      <c r="C259" s="2"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="3"/>
+      <c r="F259" s="2"/>
+      <c r="G259" t="s">
+        <v>242</v>
+      </c>
+      <c r="H259" t="s">
+        <v>43</v>
+      </c>
+      <c r="I259">
+        <v>2</v>
+      </c>
+      <c r="J259" t="s">
+        <v>18</v>
+      </c>
+      <c r="K259" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A260" s="2"/>
+      <c r="B260" s="2"/>
+      <c r="C260" s="2"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="3"/>
+      <c r="F260" s="2"/>
+      <c r="G260" t="s">
+        <v>243</v>
+      </c>
+      <c r="H260" t="s">
+        <v>43</v>
+      </c>
+      <c r="I260">
+        <v>2</v>
+      </c>
+      <c r="J260" t="s">
+        <v>18</v>
+      </c>
+      <c r="K260" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A261" s="2"/>
+      <c r="B261" s="2"/>
+      <c r="C261" s="2"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="3"/>
+      <c r="F261" s="2"/>
+      <c r="G261" t="s">
+        <v>58</v>
+      </c>
+      <c r="H261" t="s">
+        <v>43</v>
+      </c>
+      <c r="I261">
+        <v>2</v>
+      </c>
+      <c r="J261" t="s">
+        <v>18</v>
+      </c>
+      <c r="K261" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A262" s="2"/>
+      <c r="B262" s="2"/>
+      <c r="C262" s="2"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="3"/>
+      <c r="F262" s="2"/>
+      <c r="G262" t="s">
+        <v>82</v>
+      </c>
+      <c r="H262" t="s">
+        <v>43</v>
+      </c>
+      <c r="I262">
+        <v>2</v>
+      </c>
+      <c r="J262" t="s">
+        <v>18</v>
+      </c>
+      <c r="K262" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A263" s="2"/>
+      <c r="B263" s="2"/>
+      <c r="C263" s="2"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="3"/>
+      <c r="F263" s="2"/>
+      <c r="G263" t="s">
+        <v>244</v>
+      </c>
+      <c r="H263" t="s">
+        <v>43</v>
+      </c>
+      <c r="I263">
+        <v>2</v>
+      </c>
+      <c r="J263" t="s">
+        <v>18</v>
+      </c>
+      <c r="K263" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A264" s="2"/>
+      <c r="B264" s="2"/>
+      <c r="C264" s="2"/>
+      <c r="D264" s="2"/>
+      <c r="E264" s="3"/>
+      <c r="F264" s="2"/>
+      <c r="G264" t="s">
+        <v>80</v>
+      </c>
+      <c r="H264" t="s">
+        <v>43</v>
+      </c>
+      <c r="I264">
+        <v>2</v>
+      </c>
+      <c r="J264" t="s">
+        <v>18</v>
+      </c>
+      <c r="K264" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A265" s="2"/>
+      <c r="B265" s="2"/>
+      <c r="C265" s="2"/>
+      <c r="D265" s="2"/>
+      <c r="E265" s="3"/>
+      <c r="F265" s="2"/>
+      <c r="G265" t="s">
+        <v>259</v>
+      </c>
+      <c r="H265" t="s">
+        <v>43</v>
+      </c>
+      <c r="I265">
+        <v>2</v>
+      </c>
+      <c r="J265" t="s">
+        <v>18</v>
+      </c>
+      <c r="K265" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A266" s="2"/>
+      <c r="B266" s="2"/>
+      <c r="C266" s="2"/>
+      <c r="D266" s="2"/>
+      <c r="E266" s="3"/>
+      <c r="F266" s="2"/>
+      <c r="G266" t="s">
+        <v>260</v>
+      </c>
+      <c r="H266" t="s">
+        <v>43</v>
+      </c>
+      <c r="I266">
+        <v>2</v>
+      </c>
+      <c r="J266" t="s">
+        <v>18</v>
+      </c>
+      <c r="K266" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A267" s="2"/>
+      <c r="B267" s="2"/>
+      <c r="C267" s="2"/>
+      <c r="D267" s="2"/>
+      <c r="E267" s="3"/>
+      <c r="F267" s="2"/>
+      <c r="G267" t="s">
+        <v>261</v>
+      </c>
+      <c r="H267" t="s">
+        <v>43</v>
+      </c>
+      <c r="I267">
+        <v>2</v>
+      </c>
+      <c r="J267" t="s">
+        <v>18</v>
+      </c>
+      <c r="K267" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A268" s="2"/>
+      <c r="B268" s="2"/>
+      <c r="C268" s="2"/>
+      <c r="D268" s="2"/>
+      <c r="E268" s="3"/>
+      <c r="F268" s="2"/>
+      <c r="G268" t="s">
+        <v>262</v>
+      </c>
+      <c r="H268" t="s">
+        <v>43</v>
+      </c>
+      <c r="I268">
+        <v>2</v>
+      </c>
+      <c r="J268" t="s">
+        <v>18</v>
+      </c>
+      <c r="K268" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A269" s="2"/>
+      <c r="B269" s="2"/>
+      <c r="C269" s="2"/>
+      <c r="D269" s="2"/>
+      <c r="E269" s="3"/>
+      <c r="F269" s="2"/>
+      <c r="G269" t="s">
+        <v>263</v>
+      </c>
+      <c r="H269" t="s">
+        <v>43</v>
+      </c>
+      <c r="I269">
+        <v>2</v>
+      </c>
+      <c r="J269" t="s">
+        <v>18</v>
+      </c>
+      <c r="K269" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A270" s="2"/>
+      <c r="B270" s="2"/>
+      <c r="C270" s="2"/>
+      <c r="D270" s="2"/>
+      <c r="E270" s="3"/>
+      <c r="F270" s="2"/>
+      <c r="G270" t="s">
+        <v>264</v>
+      </c>
+      <c r="H270" t="s">
+        <v>43</v>
+      </c>
+      <c r="I270">
+        <v>2</v>
+      </c>
+      <c r="J270" t="s">
+        <v>18</v>
+      </c>
+      <c r="K270" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A271" s="2"/>
+      <c r="B271" s="2"/>
+      <c r="C271" s="2"/>
+      <c r="D271" s="2"/>
+      <c r="E271" s="3"/>
+      <c r="F271" s="2"/>
+      <c r="G271" t="s">
+        <v>265</v>
+      </c>
+      <c r="H271" t="s">
+        <v>43</v>
+      </c>
+      <c r="I271">
+        <v>2</v>
+      </c>
+      <c r="J271" t="s">
+        <v>18</v>
+      </c>
+      <c r="K271" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A272" s="2"/>
+      <c r="B272" s="2"/>
+      <c r="C272" s="2"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="3"/>
+      <c r="F272" s="2"/>
+      <c r="G272" t="s">
+        <v>266</v>
+      </c>
+      <c r="H272" t="s">
+        <v>43</v>
+      </c>
+      <c r="I272">
+        <v>2</v>
+      </c>
+      <c r="J272" t="s">
+        <v>18</v>
+      </c>
+      <c r="K272" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A273" s="2"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="3"/>
+      <c r="F273" s="2"/>
+      <c r="G273" t="s">
+        <v>267</v>
+      </c>
+      <c r="H273" t="s">
+        <v>43</v>
+      </c>
+      <c r="I273">
+        <v>2</v>
+      </c>
+      <c r="J273" t="s">
+        <v>18</v>
+      </c>
+      <c r="K273" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A274" s="2"/>
+      <c r="B274" s="2"/>
+      <c r="C274" s="2"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="3"/>
+      <c r="F274" s="2"/>
+      <c r="G274" t="s">
+        <v>268</v>
+      </c>
+      <c r="H274" t="s">
+        <v>43</v>
+      </c>
+      <c r="I274">
+        <v>2</v>
+      </c>
+      <c r="J274" t="s">
+        <v>18</v>
+      </c>
+      <c r="K274" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A275" s="2"/>
+      <c r="B275" s="2"/>
+      <c r="C275" s="2"/>
+      <c r="D275" s="2"/>
+      <c r="E275" s="3"/>
+      <c r="F275" s="2"/>
+      <c r="G275" t="s">
+        <v>269</v>
+      </c>
+      <c r="H275" t="s">
+        <v>43</v>
+      </c>
+      <c r="I275">
+        <v>2</v>
+      </c>
+      <c r="J275" t="s">
+        <v>18</v>
+      </c>
+      <c r="K275" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A276" s="2"/>
+      <c r="B276" s="2"/>
+      <c r="C276" s="2"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="3"/>
+      <c r="F276" s="2"/>
+      <c r="G276" t="s">
+        <v>270</v>
+      </c>
+      <c r="H276" t="s">
+        <v>43</v>
+      </c>
+      <c r="I276">
+        <v>2</v>
+      </c>
+      <c r="J276" t="s">
+        <v>18</v>
+      </c>
+      <c r="K276" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A277" s="2"/>
+      <c r="B277" s="2"/>
+      <c r="C277" s="2"/>
+      <c r="D277" s="2"/>
+      <c r="E277" s="3"/>
+      <c r="F277" s="2"/>
+      <c r="G277" t="s">
+        <v>271</v>
+      </c>
+      <c r="H277" t="s">
+        <v>43</v>
+      </c>
+      <c r="I277">
+        <v>2</v>
+      </c>
+      <c r="J277" t="s">
+        <v>18</v>
+      </c>
+      <c r="K277" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A278" s="2"/>
+      <c r="B278" s="2"/>
+      <c r="C278" s="2"/>
+      <c r="D278" s="2"/>
+      <c r="E278" s="3"/>
+      <c r="F278" s="2"/>
+      <c r="G278" t="s">
+        <v>157</v>
+      </c>
+      <c r="H278" t="s">
+        <v>17</v>
+      </c>
+      <c r="I278">
+        <v>6</v>
+      </c>
+      <c r="J278" t="s">
+        <v>18</v>
+      </c>
+      <c r="K278" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A279" s="2"/>
+      <c r="B279" s="2"/>
+      <c r="C279" s="2"/>
+      <c r="D279" s="2"/>
+      <c r="E279" s="3"/>
+      <c r="F279" s="2"/>
+      <c r="G279" t="s">
+        <v>142</v>
+      </c>
+      <c r="H279" t="s">
+        <v>17</v>
+      </c>
+      <c r="I279">
+        <v>2</v>
+      </c>
+      <c r="J279" t="s">
+        <v>18</v>
+      </c>
+      <c r="K279" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A280" s="2"/>
+      <c r="B280" s="2"/>
+      <c r="C280" s="2"/>
+      <c r="D280" s="2"/>
+      <c r="E280" s="3"/>
+      <c r="F280" s="2"/>
+      <c r="G280" t="s">
+        <v>272</v>
+      </c>
+      <c r="H280" t="s">
+        <v>17</v>
+      </c>
+      <c r="I280">
+        <v>2</v>
+      </c>
+      <c r="J280" t="s">
+        <v>18</v>
+      </c>
+      <c r="K280" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A281" s="2"/>
+      <c r="B281" s="2"/>
+      <c r="C281" s="2"/>
+      <c r="D281" s="2"/>
+      <c r="E281" s="3"/>
+      <c r="F281" s="2"/>
+      <c r="G281" t="s">
+        <v>31</v>
+      </c>
+      <c r="H281" t="s">
+        <v>17</v>
+      </c>
+      <c r="I281">
+        <v>2</v>
+      </c>
+      <c r="J281" t="s">
+        <v>18</v>
+      </c>
+      <c r="K281" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A282" s="2"/>
+      <c r="B282" s="2"/>
+      <c r="C282" s="2"/>
+      <c r="D282" s="2"/>
+      <c r="E282" s="3"/>
+      <c r="F282" s="2"/>
+      <c r="G282" t="s">
+        <v>273</v>
+      </c>
+      <c r="H282" t="s">
+        <v>17</v>
+      </c>
+      <c r="I282">
+        <v>2</v>
+      </c>
+      <c r="J282" t="s">
+        <v>18</v>
+      </c>
+      <c r="K282" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A283" s="2"/>
+      <c r="B283" s="2"/>
+      <c r="C283" s="2"/>
+      <c r="D283" s="2"/>
+      <c r="E283" s="3"/>
+      <c r="F283" s="2"/>
+      <c r="G283" t="s">
+        <v>185</v>
+      </c>
+      <c r="H283" t="s">
+        <v>17</v>
+      </c>
+      <c r="I283">
+        <v>2</v>
+      </c>
+      <c r="J283" t="s">
+        <v>18</v>
+      </c>
+      <c r="K283" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A284" s="2"/>
+      <c r="B284" s="2"/>
+      <c r="C284" s="2"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="3"/>
+      <c r="F284" s="2"/>
+      <c r="G284" t="s">
+        <v>274</v>
+      </c>
+      <c r="H284" t="s">
+        <v>17</v>
+      </c>
+      <c r="I284">
+        <v>2</v>
+      </c>
+      <c r="J284" t="s">
+        <v>18</v>
+      </c>
+      <c r="K284" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A285" s="2"/>
+      <c r="B285" s="2"/>
+      <c r="C285" s="2"/>
+      <c r="D285" s="2"/>
+      <c r="E285" s="3"/>
+      <c r="F285" s="2"/>
+      <c r="G285" t="s">
+        <v>181</v>
+      </c>
+      <c r="H285" t="s">
+        <v>36</v>
+      </c>
+      <c r="I285">
+        <v>2</v>
+      </c>
+      <c r="J285" t="s">
+        <v>18</v>
+      </c>
+      <c r="K285" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A286" s="2"/>
+      <c r="B286" s="2"/>
+      <c r="C286" s="2"/>
+      <c r="D286" s="2"/>
+      <c r="E286" s="3"/>
+      <c r="F286" s="2"/>
+      <c r="G286" t="s">
+        <v>275</v>
+      </c>
+      <c r="H286" t="s">
+        <v>36</v>
+      </c>
+      <c r="I286">
+        <v>4</v>
+      </c>
+      <c r="J286" t="s">
+        <v>18</v>
+      </c>
+      <c r="K286" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A287" s="2"/>
+      <c r="B287" s="2"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="3"/>
+      <c r="F287" s="2"/>
+      <c r="G287" t="s">
+        <v>35</v>
+      </c>
+      <c r="H287" t="s">
+        <v>36</v>
+      </c>
+      <c r="I287">
+        <v>1</v>
+      </c>
+      <c r="J287" t="s">
+        <v>18</v>
+      </c>
+      <c r="K287" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A289" s="2">
+        <v>32</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E289" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="G289" t="s">
+        <v>62</v>
+      </c>
+      <c r="H289" t="s">
+        <v>43</v>
+      </c>
+      <c r="I289">
+        <v>1</v>
+      </c>
+      <c r="J289" t="s">
+        <v>18</v>
+      </c>
+      <c r="K289" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A290" s="2"/>
+      <c r="B290" s="2"/>
+      <c r="C290" s="2"/>
+      <c r="D290" s="2"/>
+      <c r="E290" s="3"/>
+      <c r="F290" s="2"/>
+      <c r="G290" t="s">
+        <v>278</v>
+      </c>
+      <c r="H290" t="s">
+        <v>17</v>
+      </c>
+      <c r="I290">
+        <v>2</v>
+      </c>
+      <c r="J290" t="s">
+        <v>18</v>
+      </c>
+      <c r="K290" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A291" s="2"/>
+      <c r="B291" s="2"/>
+      <c r="C291" s="2"/>
+      <c r="D291" s="2"/>
+      <c r="E291" s="3"/>
+      <c r="F291" s="2"/>
+      <c r="G291" t="s">
+        <v>243</v>
+      </c>
+      <c r="H291" t="s">
+        <v>43</v>
+      </c>
+      <c r="I291">
+        <v>1</v>
+      </c>
+      <c r="J291" t="s">
+        <v>18</v>
+      </c>
+      <c r="K291" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A292" s="2"/>
+      <c r="B292" s="2"/>
+      <c r="C292" s="2"/>
+      <c r="D292" s="2"/>
+      <c r="E292" s="3"/>
+      <c r="F292" s="2"/>
+      <c r="G292" t="s">
+        <v>279</v>
+      </c>
+      <c r="H292" t="s">
+        <v>43</v>
+      </c>
+      <c r="I292">
+        <v>1</v>
+      </c>
+      <c r="J292" t="s">
+        <v>18</v>
+      </c>
+      <c r="K292" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A293" s="2"/>
+      <c r="B293" s="2"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
+      <c r="E293" s="3"/>
+      <c r="F293" s="2"/>
+      <c r="G293" t="s">
+        <v>247</v>
+      </c>
+      <c r="H293" t="s">
+        <v>43</v>
+      </c>
+      <c r="I293">
+        <v>1</v>
+      </c>
+      <c r="J293" t="s">
+        <v>18</v>
+      </c>
+      <c r="K293" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A294" s="2"/>
+      <c r="B294" s="2"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="3"/>
+      <c r="F294" s="2"/>
+      <c r="G294" t="s">
+        <v>280</v>
+      </c>
+      <c r="H294" t="s">
+        <v>17</v>
+      </c>
+      <c r="I294">
+        <v>12</v>
+      </c>
+      <c r="J294" t="s">
+        <v>18</v>
+      </c>
+      <c r="K294" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A295" s="2"/>
+      <c r="B295" s="2"/>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="3"/>
+      <c r="F295" s="2"/>
+      <c r="G295" t="s">
+        <v>281</v>
+      </c>
+      <c r="H295" t="s">
+        <v>17</v>
+      </c>
+      <c r="I295">
+        <v>1</v>
+      </c>
+      <c r="J295" t="s">
+        <v>18</v>
+      </c>
+      <c r="K295" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A296" s="2"/>
+      <c r="B296" s="2"/>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="3"/>
+      <c r="F296" s="2"/>
+      <c r="G296" t="s">
+        <v>132</v>
+      </c>
+      <c r="H296" t="s">
+        <v>43</v>
+      </c>
+      <c r="I296">
+        <v>1</v>
+      </c>
+      <c r="J296" t="s">
+        <v>18</v>
+      </c>
+      <c r="K296" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A297" s="2"/>
+      <c r="B297" s="2"/>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
+      <c r="E297" s="3"/>
+      <c r="F297" s="2"/>
+      <c r="G297" t="s">
+        <v>282</v>
+      </c>
+      <c r="H297" t="s">
+        <v>43</v>
+      </c>
+      <c r="I297">
+        <v>1</v>
+      </c>
+      <c r="J297" t="s">
+        <v>18</v>
+      </c>
+      <c r="K297" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A298" s="2"/>
+      <c r="B298" s="2"/>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="3"/>
+      <c r="F298" s="2"/>
+      <c r="G298" t="s">
+        <v>283</v>
+      </c>
+      <c r="H298" t="s">
+        <v>43</v>
+      </c>
+      <c r="I298">
+        <v>1</v>
+      </c>
+      <c r="J298" t="s">
+        <v>18</v>
+      </c>
+      <c r="K298" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A299" s="2"/>
+      <c r="B299" s="2"/>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
+      <c r="E299" s="3"/>
+      <c r="F299" s="2"/>
+      <c r="G299" t="s">
+        <v>284</v>
+      </c>
+      <c r="H299" t="s">
+        <v>43</v>
+      </c>
+      <c r="I299">
+        <v>4</v>
+      </c>
+      <c r="J299" t="s">
+        <v>18</v>
+      </c>
+      <c r="K299" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A300" s="2"/>
+      <c r="B300" s="2"/>
+      <c r="C300" s="2"/>
+      <c r="D300" s="2"/>
+      <c r="E300" s="3"/>
+      <c r="F300" s="2"/>
+      <c r="G300" t="s">
+        <v>285</v>
+      </c>
+      <c r="H300" t="s">
+        <v>43</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+      <c r="J300" t="s">
+        <v>18</v>
+      </c>
+      <c r="K300" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A301" s="2"/>
+      <c r="B301" s="2"/>
+      <c r="C301" s="2"/>
+      <c r="D301" s="2"/>
+      <c r="E301" s="3"/>
+      <c r="F301" s="2"/>
+      <c r="G301" t="s">
+        <v>286</v>
+      </c>
+      <c r="H301" t="s">
+        <v>17</v>
+      </c>
+      <c r="I301">
+        <v>2</v>
+      </c>
+      <c r="J301" t="s">
+        <v>18</v>
+      </c>
+      <c r="K301" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A302" s="2"/>
+      <c r="B302" s="2"/>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="3"/>
+      <c r="F302" s="2"/>
+      <c r="G302" t="s">
+        <v>287</v>
+      </c>
+      <c r="H302" t="s">
+        <v>36</v>
+      </c>
+      <c r="I302">
+        <v>1</v>
+      </c>
+      <c r="J302" t="s">
+        <v>18</v>
+      </c>
+      <c r="K302" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A303" s="2"/>
+      <c r="B303" s="2"/>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="3"/>
+      <c r="F303" s="2"/>
+      <c r="G303" t="s">
+        <v>288</v>
+      </c>
+      <c r="H303" t="s">
+        <v>17</v>
+      </c>
+      <c r="I303">
+        <v>3</v>
+      </c>
+      <c r="J303" t="s">
+        <v>18</v>
+      </c>
+      <c r="K303" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A304" s="2"/>
+      <c r="B304" s="2"/>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
+      <c r="E304" s="3"/>
+      <c r="F304" s="2"/>
+      <c r="G304" t="s">
+        <v>289</v>
+      </c>
+      <c r="H304" t="s">
+        <v>43</v>
+      </c>
+      <c r="I304">
+        <v>2</v>
+      </c>
+      <c r="J304" t="s">
+        <v>18</v>
+      </c>
+      <c r="K304" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A305" s="2"/>
+      <c r="B305" s="2"/>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
+      <c r="E305" s="3"/>
+      <c r="F305" s="2"/>
+      <c r="G305" t="s">
+        <v>290</v>
+      </c>
+      <c r="H305" t="s">
+        <v>43</v>
+      </c>
+      <c r="I305">
+        <v>2</v>
+      </c>
+      <c r="J305" t="s">
+        <v>18</v>
+      </c>
+      <c r="K305" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A306" s="2"/>
+      <c r="B306" s="2"/>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="3"/>
+      <c r="F306" s="2"/>
+      <c r="G306" t="s">
+        <v>291</v>
+      </c>
+      <c r="H306" t="s">
+        <v>43</v>
+      </c>
+      <c r="I306">
+        <v>2</v>
+      </c>
+      <c r="J306" t="s">
+        <v>18</v>
+      </c>
+      <c r="K306" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A307" s="2"/>
+      <c r="B307" s="2"/>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
+      <c r="E307" s="3"/>
+      <c r="F307" s="2"/>
+      <c r="G307" t="s">
+        <v>292</v>
+      </c>
+      <c r="H307" t="s">
+        <v>43</v>
+      </c>
+      <c r="I307">
+        <v>3</v>
+      </c>
+      <c r="J307" t="s">
+        <v>18</v>
+      </c>
+      <c r="K307" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A308" s="2"/>
+      <c r="B308" s="2"/>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="3"/>
+      <c r="F308" s="2"/>
+      <c r="G308" t="s">
+        <v>293</v>
+      </c>
+      <c r="H308" t="s">
+        <v>17</v>
+      </c>
+      <c r="I308">
+        <v>2</v>
+      </c>
+      <c r="J308" t="s">
+        <v>18</v>
+      </c>
+      <c r="K308" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A309" s="2"/>
+      <c r="B309" s="2"/>
+      <c r="C309" s="2"/>
+      <c r="D309" s="2"/>
+      <c r="E309" s="3"/>
+      <c r="F309" s="2"/>
+      <c r="G309" t="s">
+        <v>237</v>
+      </c>
+      <c r="H309" t="s">
+        <v>43</v>
+      </c>
+      <c r="I309">
+        <v>2</v>
+      </c>
+      <c r="J309" t="s">
+        <v>18</v>
+      </c>
+      <c r="K309" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A310" s="2"/>
+      <c r="B310" s="2"/>
+      <c r="C310" s="2"/>
+      <c r="D310" s="2"/>
+      <c r="E310" s="3"/>
+      <c r="F310" s="2"/>
+      <c r="G310" t="s">
+        <v>238</v>
+      </c>
+      <c r="H310" t="s">
+        <v>17</v>
+      </c>
+      <c r="I310">
+        <v>1</v>
+      </c>
+      <c r="J310" t="s">
+        <v>18</v>
+      </c>
+      <c r="K310" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A311" s="2"/>
+      <c r="B311" s="2"/>
+      <c r="C311" s="2"/>
+      <c r="D311" s="2"/>
+      <c r="E311" s="3"/>
+      <c r="F311" s="2"/>
+      <c r="G311" t="s">
+        <v>239</v>
+      </c>
+      <c r="H311" t="s">
+        <v>43</v>
+      </c>
+      <c r="I311">
+        <v>1</v>
+      </c>
+      <c r="J311" t="s">
+        <v>18</v>
+      </c>
+      <c r="K311" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A312" s="2"/>
+      <c r="B312" s="2"/>
+      <c r="C312" s="2"/>
+      <c r="D312" s="2"/>
+      <c r="E312" s="3"/>
+      <c r="F312" s="2"/>
+      <c r="G312" t="s">
+        <v>67</v>
+      </c>
+      <c r="H312" t="s">
+        <v>43</v>
+      </c>
+      <c r="I312">
+        <v>2</v>
+      </c>
+      <c r="J312" t="s">
+        <v>18</v>
+      </c>
+      <c r="K312" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A313" s="2"/>
+      <c r="B313" s="2"/>
+      <c r="C313" s="2"/>
+      <c r="D313" s="2"/>
+      <c r="E313" s="3"/>
+      <c r="F313" s="2"/>
+      <c r="G313" t="s">
+        <v>48</v>
+      </c>
+      <c r="H313" t="s">
+        <v>17</v>
+      </c>
+      <c r="I313">
+        <v>10</v>
+      </c>
+      <c r="J313" t="s">
+        <v>18</v>
+      </c>
+      <c r="K313" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A314" s="2"/>
+      <c r="B314" s="2"/>
+      <c r="C314" s="2"/>
+      <c r="D314" s="2"/>
+      <c r="E314" s="3"/>
+      <c r="F314" s="2"/>
+      <c r="G314" t="s">
+        <v>71</v>
+      </c>
+      <c r="H314" t="s">
+        <v>43</v>
+      </c>
+      <c r="I314">
+        <v>5</v>
+      </c>
+      <c r="J314" t="s">
+        <v>18</v>
+      </c>
+      <c r="K314" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A316" s="2">
+        <v>33</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E316" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G316" t="s">
+        <v>176</v>
+      </c>
+      <c r="H316" t="s">
+        <v>17</v>
+      </c>
+      <c r="I316">
+        <v>10</v>
+      </c>
+      <c r="J316" t="s">
+        <v>18</v>
+      </c>
+      <c r="K316" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A317" s="2"/>
+      <c r="B317" s="2"/>
+      <c r="C317" s="2"/>
+      <c r="D317" s="2"/>
+      <c r="E317" s="3"/>
+      <c r="F317" s="2"/>
+      <c r="G317" t="s">
+        <v>295</v>
+      </c>
+      <c r="H317" t="s">
+        <v>36</v>
+      </c>
+      <c r="I317">
+        <v>2</v>
+      </c>
+      <c r="J317" t="s">
+        <v>18</v>
+      </c>
+      <c r="K317" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A318" s="2"/>
+      <c r="B318" s="2"/>
+      <c r="C318" s="2"/>
+      <c r="D318" s="2"/>
+      <c r="E318" s="3"/>
+      <c r="F318" s="2"/>
+      <c r="G318" t="s">
+        <v>296</v>
+      </c>
+      <c r="H318" t="s">
+        <v>17</v>
+      </c>
+      <c r="I318">
+        <v>10</v>
+      </c>
+      <c r="J318" t="s">
+        <v>18</v>
+      </c>
+      <c r="K318" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A319" s="2"/>
+      <c r="B319" s="2"/>
+      <c r="C319" s="2"/>
+      <c r="D319" s="2"/>
+      <c r="E319" s="3"/>
+      <c r="F319" s="2"/>
+      <c r="G319" t="s">
+        <v>297</v>
+      </c>
+      <c r="H319" t="s">
+        <v>43</v>
+      </c>
+      <c r="I319">
+        <v>2</v>
+      </c>
+      <c r="J319" t="s">
+        <v>18</v>
+      </c>
+      <c r="K319" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A320" s="2"/>
+      <c r="B320" s="2"/>
+      <c r="C320" s="2"/>
+      <c r="D320" s="2"/>
+      <c r="E320" s="3"/>
+      <c r="F320" s="2"/>
+      <c r="G320" t="s">
+        <v>298</v>
+      </c>
+      <c r="H320" t="s">
+        <v>36</v>
+      </c>
+      <c r="I320">
+        <v>2</v>
+      </c>
+      <c r="J320" t="s">
+        <v>18</v>
+      </c>
+      <c r="K320" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A321" s="2"/>
+      <c r="B321" s="2"/>
+      <c r="C321" s="2"/>
+      <c r="D321" s="2"/>
+      <c r="E321" s="3"/>
+      <c r="F321" s="2"/>
+      <c r="G321" t="s">
+        <v>299</v>
+      </c>
+      <c r="H321" t="s">
+        <v>17</v>
+      </c>
+      <c r="I321">
+        <v>10</v>
+      </c>
+      <c r="J321" t="s">
+        <v>18</v>
+      </c>
+      <c r="K321" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A322" s="2"/>
+      <c r="B322" s="2"/>
+      <c r="C322" s="2"/>
+      <c r="D322" s="2"/>
+      <c r="E322" s="3"/>
+      <c r="F322" s="2"/>
+      <c r="G322" t="s">
+        <v>300</v>
+      </c>
+      <c r="H322" t="s">
+        <v>43</v>
+      </c>
+      <c r="I322">
+        <v>2</v>
+      </c>
+      <c r="J322" t="s">
+        <v>18</v>
+      </c>
+      <c r="K322" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A323" s="2"/>
+      <c r="B323" s="2"/>
+      <c r="C323" s="2"/>
+      <c r="D323" s="2"/>
+      <c r="E323" s="3"/>
+      <c r="F323" s="2"/>
+      <c r="G323" t="s">
+        <v>301</v>
+      </c>
+      <c r="H323" t="s">
+        <v>36</v>
+      </c>
+      <c r="I323">
+        <v>2</v>
+      </c>
+      <c r="J323" t="s">
+        <v>18</v>
+      </c>
+      <c r="K323" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A325" s="2">
+        <v>34</v>
+      </c>
+      <c r="B325" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C325" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E325" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F325" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G325" t="s">
+        <v>62</v>
+      </c>
+      <c r="H325" t="s">
+        <v>43</v>
+      </c>
+      <c r="I325">
+        <v>1</v>
+      </c>
+      <c r="J325" t="s">
+        <v>18</v>
+      </c>
+      <c r="K325" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A326" s="2"/>
+      <c r="B326" s="2"/>
+      <c r="C326" s="2"/>
+      <c r="D326" s="2"/>
+      <c r="E326" s="3"/>
+      <c r="F326" s="2"/>
+      <c r="G326" t="s">
+        <v>278</v>
+      </c>
+      <c r="H326" t="s">
+        <v>17</v>
+      </c>
+      <c r="I326">
+        <v>2</v>
+      </c>
+      <c r="J326" t="s">
+        <v>18</v>
+      </c>
+      <c r="K326" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A327" s="2"/>
+      <c r="B327" s="2"/>
+      <c r="C327" s="2"/>
+      <c r="D327" s="2"/>
+      <c r="E327" s="3"/>
+      <c r="F327" s="2"/>
+      <c r="G327" t="s">
+        <v>243</v>
+      </c>
+      <c r="H327" t="s">
+        <v>43</v>
+      </c>
+      <c r="I327">
+        <v>1</v>
+      </c>
+      <c r="J327" t="s">
+        <v>18</v>
+      </c>
+      <c r="K327" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A328" s="2"/>
+      <c r="B328" s="2"/>
+      <c r="C328" s="2"/>
+      <c r="D328" s="2"/>
+      <c r="E328" s="3"/>
+      <c r="F328" s="2"/>
+      <c r="G328" t="s">
+        <v>279</v>
+      </c>
+      <c r="H328" t="s">
+        <v>43</v>
+      </c>
+      <c r="I328">
+        <v>1</v>
+      </c>
+      <c r="J328" t="s">
+        <v>18</v>
+      </c>
+      <c r="K328" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A329" s="2"/>
+      <c r="B329" s="2"/>
+      <c r="C329" s="2"/>
+      <c r="D329" s="2"/>
+      <c r="E329" s="3"/>
+      <c r="F329" s="2"/>
+      <c r="G329" t="s">
+        <v>247</v>
+      </c>
+      <c r="H329" t="s">
+        <v>43</v>
+      </c>
+      <c r="I329">
+        <v>1</v>
+      </c>
+      <c r="J329" t="s">
+        <v>18</v>
+      </c>
+      <c r="K329" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A330" s="2"/>
+      <c r="B330" s="2"/>
+      <c r="C330" s="2"/>
+      <c r="D330" s="2"/>
+      <c r="E330" s="3"/>
+      <c r="F330" s="2"/>
+      <c r="G330" t="s">
+        <v>280</v>
+      </c>
+      <c r="H330" t="s">
+        <v>17</v>
+      </c>
+      <c r="I330">
+        <v>12</v>
+      </c>
+      <c r="J330" t="s">
+        <v>18</v>
+      </c>
+      <c r="K330" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A331" s="2"/>
+      <c r="B331" s="2"/>
+      <c r="C331" s="2"/>
+      <c r="D331" s="2"/>
+      <c r="E331" s="3"/>
+      <c r="F331" s="2"/>
+      <c r="G331" t="s">
+        <v>281</v>
+      </c>
+      <c r="H331" t="s">
+        <v>17</v>
+      </c>
+      <c r="I331">
+        <v>1</v>
+      </c>
+      <c r="J331" t="s">
+        <v>18</v>
+      </c>
+      <c r="K331" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A332" s="2"/>
+      <c r="B332" s="2"/>
+      <c r="C332" s="2"/>
+      <c r="D332" s="2"/>
+      <c r="E332" s="3"/>
+      <c r="F332" s="2"/>
+      <c r="G332" t="s">
+        <v>132</v>
+      </c>
+      <c r="H332" t="s">
+        <v>43</v>
+      </c>
+      <c r="I332">
+        <v>1</v>
+      </c>
+      <c r="J332" t="s">
+        <v>18</v>
+      </c>
+      <c r="K332" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A333" s="2"/>
+      <c r="B333" s="2"/>
+      <c r="C333" s="2"/>
+      <c r="D333" s="2"/>
+      <c r="E333" s="3"/>
+      <c r="F333" s="2"/>
+      <c r="G333" t="s">
+        <v>282</v>
+      </c>
+      <c r="H333" t="s">
+        <v>43</v>
+      </c>
+      <c r="I333">
+        <v>1</v>
+      </c>
+      <c r="J333" t="s">
+        <v>18</v>
+      </c>
+      <c r="K333" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A334" s="2"/>
+      <c r="B334" s="2"/>
+      <c r="C334" s="2"/>
+      <c r="D334" s="2"/>
+      <c r="E334" s="3"/>
+      <c r="F334" s="2"/>
+      <c r="G334" t="s">
+        <v>283</v>
+      </c>
+      <c r="H334" t="s">
+        <v>43</v>
+      </c>
+      <c r="I334">
+        <v>1</v>
+      </c>
+      <c r="J334" t="s">
+        <v>18</v>
+      </c>
+      <c r="K334" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A335" s="2"/>
+      <c r="B335" s="2"/>
+      <c r="C335" s="2"/>
+      <c r="D335" s="2"/>
+      <c r="E335" s="3"/>
+      <c r="F335" s="2"/>
+      <c r="G335" t="s">
+        <v>284</v>
+      </c>
+      <c r="H335" t="s">
+        <v>43</v>
+      </c>
+      <c r="I335">
+        <v>4</v>
+      </c>
+      <c r="J335" t="s">
+        <v>18</v>
+      </c>
+      <c r="K335" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A336" s="2"/>
+      <c r="B336" s="2"/>
+      <c r="C336" s="2"/>
+      <c r="D336" s="2"/>
+      <c r="E336" s="3"/>
+      <c r="F336" s="2"/>
+      <c r="G336" t="s">
+        <v>285</v>
+      </c>
+      <c r="H336" t="s">
+        <v>43</v>
+      </c>
+      <c r="I336">
+        <v>1</v>
+      </c>
+      <c r="J336" t="s">
+        <v>18</v>
+      </c>
+      <c r="K336" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A337" s="2"/>
+      <c r="B337" s="2"/>
+      <c r="C337" s="2"/>
+      <c r="D337" s="2"/>
+      <c r="E337" s="3"/>
+      <c r="F337" s="2"/>
+      <c r="G337" t="s">
+        <v>286</v>
+      </c>
+      <c r="H337" t="s">
+        <v>17</v>
+      </c>
+      <c r="I337">
+        <v>2</v>
+      </c>
+      <c r="J337" t="s">
+        <v>18</v>
+      </c>
+      <c r="K337" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A338" s="2"/>
+      <c r="B338" s="2"/>
+      <c r="C338" s="2"/>
+      <c r="D338" s="2"/>
+      <c r="E338" s="3"/>
+      <c r="F338" s="2"/>
+      <c r="G338" t="s">
+        <v>287</v>
+      </c>
+      <c r="H338" t="s">
+        <v>36</v>
+      </c>
+      <c r="I338">
+        <v>1</v>
+      </c>
+      <c r="J338" t="s">
+        <v>18</v>
+      </c>
+      <c r="K338" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A339" s="2"/>
+      <c r="B339" s="2"/>
+      <c r="C339" s="2"/>
+      <c r="D339" s="2"/>
+      <c r="E339" s="3"/>
+      <c r="F339" s="2"/>
+      <c r="G339" t="s">
+        <v>288</v>
+      </c>
+      <c r="H339" t="s">
+        <v>17</v>
+      </c>
+      <c r="I339">
+        <v>3</v>
+      </c>
+      <c r="J339" t="s">
+        <v>18</v>
+      </c>
+      <c r="K339" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A340" s="2"/>
+      <c r="B340" s="2"/>
+      <c r="C340" s="2"/>
+      <c r="D340" s="2"/>
+      <c r="E340" s="3"/>
+      <c r="F340" s="2"/>
+      <c r="G340" t="s">
+        <v>289</v>
+      </c>
+      <c r="H340" t="s">
+        <v>43</v>
+      </c>
+      <c r="I340">
+        <v>2</v>
+      </c>
+      <c r="J340" t="s">
+        <v>18</v>
+      </c>
+      <c r="K340" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A341" s="2"/>
+      <c r="B341" s="2"/>
+      <c r="C341" s="2"/>
+      <c r="D341" s="2"/>
+      <c r="E341" s="3"/>
+      <c r="F341" s="2"/>
+      <c r="G341" t="s">
+        <v>290</v>
+      </c>
+      <c r="H341" t="s">
+        <v>43</v>
+      </c>
+      <c r="I341">
+        <v>2</v>
+      </c>
+      <c r="J341" t="s">
+        <v>18</v>
+      </c>
+      <c r="K341" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A342" s="2"/>
+      <c r="B342" s="2"/>
+      <c r="C342" s="2"/>
+      <c r="D342" s="2"/>
+      <c r="E342" s="3"/>
+      <c r="F342" s="2"/>
+      <c r="G342" t="s">
+        <v>291</v>
+      </c>
+      <c r="H342" t="s">
+        <v>43</v>
+      </c>
+      <c r="I342">
+        <v>2</v>
+      </c>
+      <c r="J342" t="s">
+        <v>18</v>
+      </c>
+      <c r="K342" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A343" s="2"/>
+      <c r="B343" s="2"/>
+      <c r="C343" s="2"/>
+      <c r="D343" s="2"/>
+      <c r="E343" s="3"/>
+      <c r="F343" s="2"/>
+      <c r="G343" t="s">
+        <v>292</v>
+      </c>
+      <c r="H343" t="s">
+        <v>43</v>
+      </c>
+      <c r="I343">
+        <v>3</v>
+      </c>
+      <c r="J343" t="s">
+        <v>18</v>
+      </c>
+      <c r="K343" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A344" s="2"/>
+      <c r="B344" s="2"/>
+      <c r="C344" s="2"/>
+      <c r="D344" s="2"/>
+      <c r="E344" s="3"/>
+      <c r="F344" s="2"/>
+      <c r="G344" t="s">
+        <v>293</v>
+      </c>
+      <c r="H344" t="s">
+        <v>17</v>
+      </c>
+      <c r="I344">
+        <v>2</v>
+      </c>
+      <c r="J344" t="s">
+        <v>18</v>
+      </c>
+      <c r="K344" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A345" s="2"/>
+      <c r="B345" s="2"/>
+      <c r="C345" s="2"/>
+      <c r="D345" s="2"/>
+      <c r="E345" s="3"/>
+      <c r="F345" s="2"/>
+      <c r="G345" t="s">
+        <v>237</v>
+      </c>
+      <c r="H345" t="s">
+        <v>43</v>
+      </c>
+      <c r="I345">
+        <v>2</v>
+      </c>
+      <c r="J345" t="s">
+        <v>18</v>
+      </c>
+      <c r="K345" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A346" s="2"/>
+      <c r="B346" s="2"/>
+      <c r="C346" s="2"/>
+      <c r="D346" s="2"/>
+      <c r="E346" s="3"/>
+      <c r="F346" s="2"/>
+      <c r="G346" t="s">
+        <v>238</v>
+      </c>
+      <c r="H346" t="s">
+        <v>17</v>
+      </c>
+      <c r="I346">
+        <v>1</v>
+      </c>
+      <c r="J346" t="s">
+        <v>18</v>
+      </c>
+      <c r="K346" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A347" s="2"/>
+      <c r="B347" s="2"/>
+      <c r="C347" s="2"/>
+      <c r="D347" s="2"/>
+      <c r="E347" s="3"/>
+      <c r="F347" s="2"/>
+      <c r="G347" t="s">
+        <v>239</v>
+      </c>
+      <c r="H347" t="s">
+        <v>43</v>
+      </c>
+      <c r="I347">
+        <v>1</v>
+      </c>
+      <c r="J347" t="s">
+        <v>18</v>
+      </c>
+      <c r="K347" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A348" s="2"/>
+      <c r="B348" s="2"/>
+      <c r="C348" s="2"/>
+      <c r="D348" s="2"/>
+      <c r="E348" s="3"/>
+      <c r="F348" s="2"/>
+      <c r="G348" t="s">
+        <v>67</v>
+      </c>
+      <c r="H348" t="s">
+        <v>43</v>
+      </c>
+      <c r="I348">
+        <v>2</v>
+      </c>
+      <c r="J348" t="s">
+        <v>18</v>
+      </c>
+      <c r="K348" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A349" s="2"/>
+      <c r="B349" s="2"/>
+      <c r="C349" s="2"/>
+      <c r="D349" s="2"/>
+      <c r="E349" s="3"/>
+      <c r="F349" s="2"/>
+      <c r="G349" t="s">
+        <v>48</v>
+      </c>
+      <c r="H349" t="s">
+        <v>17</v>
+      </c>
+      <c r="I349">
+        <v>10</v>
+      </c>
+      <c r="J349" t="s">
+        <v>18</v>
+      </c>
+      <c r="K349" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A350" s="2"/>
+      <c r="B350" s="2"/>
+      <c r="C350" s="2"/>
+      <c r="D350" s="2"/>
+      <c r="E350" s="3"/>
+      <c r="F350" s="2"/>
+      <c r="G350" t="s">
+        <v>71</v>
+      </c>
+      <c r="H350" t="s">
+        <v>43</v>
+      </c>
+      <c r="I350">
+        <v>5</v>
+      </c>
+      <c r="J350" t="s">
+        <v>18</v>
+      </c>
+      <c r="K350" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A352" s="2">
+        <v>35</v>
+      </c>
+      <c r="B352" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E352" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F352" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G352" t="s">
+        <v>31</v>
+      </c>
+      <c r="H352" t="s">
+        <v>17</v>
+      </c>
+      <c r="I352">
+        <v>20</v>
+      </c>
+      <c r="J352" t="s">
+        <v>18</v>
+      </c>
+      <c r="K352" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A353" s="2"/>
+      <c r="B353" s="2"/>
+      <c r="C353" s="2"/>
+      <c r="D353" s="2"/>
+      <c r="E353" s="3"/>
+      <c r="F353" s="2"/>
+      <c r="G353" t="s">
+        <v>306</v>
+      </c>
+      <c r="H353" t="s">
+        <v>17</v>
+      </c>
+      <c r="I353">
+        <v>10</v>
+      </c>
+      <c r="J353" t="s">
+        <v>18</v>
+      </c>
+      <c r="K353" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A354" s="2"/>
+      <c r="B354" s="2"/>
+      <c r="C354" s="2"/>
+      <c r="D354" s="2"/>
+      <c r="E354" s="3"/>
+      <c r="F354" s="2"/>
+      <c r="G354" t="s">
+        <v>307</v>
+      </c>
+      <c r="H354" t="s">
+        <v>17</v>
+      </c>
+      <c r="I354">
+        <v>5</v>
+      </c>
+      <c r="J354" t="s">
+        <v>18</v>
+      </c>
+      <c r="K354" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A355" s="2"/>
+      <c r="B355" s="2"/>
+      <c r="C355" s="2"/>
+      <c r="D355" s="2"/>
+      <c r="E355" s="3"/>
+      <c r="F355" s="2"/>
+      <c r="G355" t="s">
+        <v>308</v>
+      </c>
+      <c r="H355" t="s">
+        <v>17</v>
+      </c>
+      <c r="I355">
+        <v>5</v>
+      </c>
+      <c r="J355" t="s">
+        <v>18</v>
+      </c>
+      <c r="K355" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A356" s="2"/>
+      <c r="B356" s="2"/>
+      <c r="C356" s="2"/>
+      <c r="D356" s="2"/>
+      <c r="E356" s="3"/>
+      <c r="F356" s="2"/>
+      <c r="G356" t="s">
+        <v>309</v>
+      </c>
+      <c r="H356" t="s">
+        <v>17</v>
+      </c>
+      <c r="I356">
+        <v>10</v>
+      </c>
+      <c r="J356" t="s">
+        <v>18</v>
+      </c>
+      <c r="K356" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A357" s="2"/>
+      <c r="B357" s="2"/>
+      <c r="C357" s="2"/>
+      <c r="D357" s="2"/>
+      <c r="E357" s="3"/>
+      <c r="F357" s="2"/>
+      <c r="G357" t="s">
+        <v>125</v>
+      </c>
+      <c r="H357" t="s">
+        <v>17</v>
+      </c>
+      <c r="I357">
+        <v>10</v>
+      </c>
+      <c r="J357" t="s">
+        <v>18</v>
+      </c>
+      <c r="K357" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A358" s="2"/>
+      <c r="B358" s="2"/>
+      <c r="C358" s="2"/>
+      <c r="D358" s="2"/>
+      <c r="E358" s="3"/>
+      <c r="F358" s="2"/>
+      <c r="G358" t="s">
+        <v>310</v>
+      </c>
+      <c r="H358" t="s">
+        <v>17</v>
+      </c>
+      <c r="I358">
+        <v>5</v>
+      </c>
+      <c r="J358" t="s">
+        <v>18</v>
+      </c>
+      <c r="K358" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A359" s="2"/>
+      <c r="B359" s="2"/>
+      <c r="C359" s="2"/>
+      <c r="D359" s="2"/>
+      <c r="E359" s="3"/>
+      <c r="F359" s="2"/>
+      <c r="G359" t="s">
+        <v>311</v>
+      </c>
+      <c r="H359" t="s">
+        <v>17</v>
+      </c>
+      <c r="I359">
+        <v>5</v>
+      </c>
+      <c r="J359" t="s">
+        <v>18</v>
+      </c>
+      <c r="K359" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A360" s="2"/>
+      <c r="B360" s="2"/>
+      <c r="C360" s="2"/>
+      <c r="D360" s="2"/>
+      <c r="E360" s="3"/>
+      <c r="F360" s="2"/>
+      <c r="G360" t="s">
+        <v>312</v>
+      </c>
+      <c r="H360" t="s">
+        <v>17</v>
+      </c>
+      <c r="I360">
+        <v>5</v>
+      </c>
+      <c r="J360" t="s">
+        <v>18</v>
+      </c>
+      <c r="K360" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A361" s="2"/>
+      <c r="B361" s="2"/>
+      <c r="C361" s="2"/>
+      <c r="D361" s="2"/>
+      <c r="E361" s="3"/>
+      <c r="F361" s="2"/>
+      <c r="G361" t="s">
+        <v>313</v>
+      </c>
+      <c r="H361" t="s">
+        <v>17</v>
+      </c>
+      <c r="I361">
+        <v>5</v>
+      </c>
+      <c r="J361" t="s">
+        <v>18</v>
+      </c>
+      <c r="K361" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A362" s="2"/>
+      <c r="B362" s="2"/>
+      <c r="C362" s="2"/>
+      <c r="D362" s="2"/>
+      <c r="E362" s="3"/>
+      <c r="F362" s="2"/>
+      <c r="G362" t="s">
+        <v>157</v>
+      </c>
+      <c r="H362" t="s">
+        <v>17</v>
+      </c>
+      <c r="I362">
+        <v>5</v>
+      </c>
+      <c r="J362" t="s">
+        <v>18</v>
+      </c>
+      <c r="K362" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A363" s="2"/>
+      <c r="B363" s="2"/>
+      <c r="C363" s="2"/>
+      <c r="D363" s="2"/>
+      <c r="E363" s="3"/>
+      <c r="F363" s="2"/>
+      <c r="G363" t="s">
+        <v>314</v>
+      </c>
+      <c r="H363" t="s">
+        <v>17</v>
+      </c>
+      <c r="I363">
+        <v>5</v>
+      </c>
+      <c r="J363" t="s">
+        <v>18</v>
+      </c>
+      <c r="K363" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A364" s="2"/>
+      <c r="B364" s="2"/>
+      <c r="C364" s="2"/>
+      <c r="D364" s="2"/>
+      <c r="E364" s="3"/>
+      <c r="F364" s="2"/>
+      <c r="G364" t="s">
+        <v>88</v>
+      </c>
+      <c r="H364" t="s">
+        <v>17</v>
+      </c>
+      <c r="I364">
+        <v>20</v>
+      </c>
+      <c r="J364" t="s">
+        <v>18</v>
+      </c>
+      <c r="K364" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A365" s="2"/>
+      <c r="B365" s="2"/>
+      <c r="C365" s="2"/>
+      <c r="D365" s="2"/>
+      <c r="E365" s="3"/>
+      <c r="F365" s="2"/>
+      <c r="G365" t="s">
+        <v>42</v>
+      </c>
+      <c r="H365" t="s">
+        <v>43</v>
+      </c>
+      <c r="I365">
+        <v>10</v>
+      </c>
+      <c r="J365" t="s">
+        <v>18</v>
+      </c>
+      <c r="K365" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A367" s="2">
+        <v>36</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="E367" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="F367" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="G367" t="s">
+        <v>31</v>
+      </c>
+      <c r="H367" t="s">
+        <v>17</v>
+      </c>
+      <c r="I367">
+        <v>20</v>
+      </c>
+      <c r="J367" t="s">
+        <v>17</v>
+      </c>
+      <c r="K367" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A368" s="2"/>
+      <c r="B368" s="2"/>
+      <c r="C368" s="2"/>
+      <c r="D368" s="2"/>
+      <c r="E368" s="3"/>
+      <c r="F368" s="2"/>
+      <c r="G368" t="s">
+        <v>306</v>
+      </c>
+      <c r="H368" t="s">
+        <v>17</v>
+      </c>
+      <c r="I368">
+        <v>10</v>
+      </c>
+      <c r="J368" t="s">
+        <v>17</v>
+      </c>
+      <c r="K368" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="369" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A369" s="2"/>
+      <c r="B369" s="2"/>
+      <c r="C369" s="2"/>
+      <c r="D369" s="2"/>
+      <c r="E369" s="3"/>
+      <c r="F369" s="2"/>
+      <c r="G369" t="s">
+        <v>307</v>
+      </c>
+      <c r="H369" t="s">
+        <v>17</v>
+      </c>
+      <c r="I369">
+        <v>5</v>
+      </c>
+      <c r="J369" t="s">
+        <v>17</v>
+      </c>
+      <c r="K369" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="370" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A370" s="2"/>
+      <c r="B370" s="2"/>
+      <c r="C370" s="2"/>
+      <c r="D370" s="2"/>
+      <c r="E370" s="3"/>
+      <c r="F370" s="2"/>
+      <c r="G370" t="s">
+        <v>55</v>
+      </c>
+      <c r="H370" t="s">
+        <v>17</v>
+      </c>
+      <c r="I370">
+        <v>5</v>
+      </c>
+      <c r="J370" t="s">
+        <v>17</v>
+      </c>
+      <c r="K370" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="371" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A371" s="2"/>
+      <c r="B371" s="2"/>
+      <c r="C371" s="2"/>
+      <c r="D371" s="2"/>
+      <c r="E371" s="3"/>
+      <c r="F371" s="2"/>
+      <c r="G371" t="s">
+        <v>309</v>
+      </c>
+      <c r="H371" t="s">
+        <v>17</v>
+      </c>
+      <c r="I371">
+        <v>10</v>
+      </c>
+      <c r="J371" t="s">
+        <v>17</v>
+      </c>
+      <c r="K371" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="372" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A372" s="2"/>
+      <c r="B372" s="2"/>
+      <c r="C372" s="2"/>
+      <c r="D372" s="2"/>
+      <c r="E372" s="3"/>
+      <c r="F372" s="2"/>
+      <c r="G372" t="s">
+        <v>55</v>
+      </c>
+      <c r="H372" t="s">
+        <v>17</v>
+      </c>
+      <c r="I372">
+        <v>10</v>
+      </c>
+      <c r="J372" t="s">
+        <v>17</v>
+      </c>
+      <c r="K372" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="373" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A373" s="2"/>
+      <c r="B373" s="2"/>
+      <c r="C373" s="2"/>
+      <c r="D373" s="2"/>
+      <c r="E373" s="3"/>
+      <c r="F373" s="2"/>
+      <c r="G373" t="s">
+        <v>310</v>
+      </c>
+      <c r="H373" t="s">
+        <v>17</v>
+      </c>
+      <c r="I373">
+        <v>5</v>
+      </c>
+      <c r="J373" t="s">
+        <v>17</v>
+      </c>
+      <c r="K373" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="374" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A374" s="2"/>
+      <c r="B374" s="2"/>
+      <c r="C374" s="2"/>
+      <c r="D374" s="2"/>
+      <c r="E374" s="3"/>
+      <c r="F374" s="2"/>
+      <c r="G374" t="s">
+        <v>311</v>
+      </c>
+      <c r="H374" t="s">
+        <v>17</v>
+      </c>
+      <c r="I374">
+        <v>5</v>
+      </c>
+      <c r="J374" t="s">
+        <v>17</v>
+      </c>
+      <c r="K374" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="375" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A375" s="2"/>
+      <c r="B375" s="2"/>
+      <c r="C375" s="2"/>
+      <c r="D375" s="2"/>
+      <c r="E375" s="3"/>
+      <c r="F375" s="2"/>
+      <c r="G375" t="s">
+        <v>312</v>
+      </c>
+      <c r="H375" t="s">
+        <v>17</v>
+      </c>
+      <c r="I375">
+        <v>5</v>
+      </c>
+      <c r="J375" t="s">
+        <v>17</v>
+      </c>
+      <c r="K375" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="376" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A376" s="2"/>
+      <c r="B376" s="2"/>
+      <c r="C376" s="2"/>
+      <c r="D376" s="2"/>
+      <c r="E376" s="3"/>
+      <c r="F376" s="2"/>
+      <c r="G376" t="s">
+        <v>313</v>
+      </c>
+      <c r="H376" t="s">
+        <v>17</v>
+      </c>
+      <c r="I376">
+        <v>5</v>
+      </c>
+      <c r="J376" t="s">
+        <v>17</v>
+      </c>
+      <c r="K376" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="377" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A377" s="2"/>
+      <c r="B377" s="2"/>
+      <c r="C377" s="2"/>
+      <c r="D377" s="2"/>
+      <c r="E377" s="3"/>
+      <c r="F377" s="2"/>
+      <c r="G377" t="s">
+        <v>157</v>
+      </c>
+      <c r="H377" t="s">
+        <v>17</v>
+      </c>
+      <c r="I377">
+        <v>1</v>
+      </c>
+      <c r="J377" t="s">
+        <v>17</v>
+      </c>
+      <c r="K377" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="378" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A378" s="2"/>
+      <c r="B378" s="2"/>
+      <c r="C378" s="2"/>
+      <c r="D378" s="2"/>
+      <c r="E378" s="3"/>
+      <c r="F378" s="2"/>
+      <c r="G378" t="s">
+        <v>181</v>
+      </c>
+      <c r="H378" t="s">
+        <v>36</v>
+      </c>
+      <c r="I378">
+        <v>5</v>
+      </c>
+      <c r="J378" t="s">
+        <v>36</v>
+      </c>
+      <c r="K378" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="379" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A379" s="2"/>
+      <c r="B379" s="2"/>
+      <c r="C379" s="2"/>
+      <c r="D379" s="2"/>
+      <c r="E379" s="3"/>
+      <c r="F379" s="2"/>
+      <c r="G379" t="s">
+        <v>193</v>
+      </c>
+      <c r="H379" t="s">
+        <v>17</v>
+      </c>
+      <c r="I379">
+        <v>10</v>
+      </c>
+      <c r="J379" t="s">
+        <v>17</v>
+      </c>
+      <c r="K379" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="380" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A380" s="2"/>
+      <c r="B380" s="2"/>
+      <c r="C380" s="2"/>
+      <c r="D380" s="2"/>
+      <c r="E380" s="3"/>
+      <c r="F380" s="2"/>
+      <c r="G380" t="s">
+        <v>314</v>
+      </c>
+      <c r="H380" t="s">
+        <v>17</v>
+      </c>
+      <c r="I380">
+        <v>5</v>
+      </c>
+      <c r="J380" t="s">
+        <v>17</v>
+      </c>
+      <c r="K380" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="381" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A381" s="2"/>
+      <c r="B381" s="2"/>
+      <c r="C381" s="2"/>
+      <c r="D381" s="2"/>
+      <c r="E381" s="3"/>
+      <c r="F381" s="2"/>
+      <c r="G381" t="s">
+        <v>88</v>
+      </c>
+      <c r="H381" t="s">
+        <v>17</v>
+      </c>
+      <c r="I381">
+        <v>20</v>
+      </c>
+      <c r="J381" t="s">
+        <v>17</v>
+      </c>
+      <c r="K381" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="382" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A382" s="2"/>
+      <c r="B382" s="2"/>
+      <c r="C382" s="2"/>
+      <c r="D382" s="2"/>
+      <c r="E382" s="3"/>
+      <c r="F382" s="2"/>
+      <c r="G382" t="s">
+        <v>42</v>
+      </c>
+      <c r="H382" t="s">
+        <v>43</v>
+      </c>
+      <c r="I382">
+        <v>10</v>
+      </c>
+      <c r="J382" t="s">
+        <v>43</v>
+      </c>
+      <c r="K382" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="384" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A384" s="2">
+        <v>37</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E384" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F384" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G384" t="s">
+        <v>272</v>
+      </c>
+      <c r="H384" t="s">
+        <v>17</v>
+      </c>
+      <c r="I384">
+        <v>12</v>
+      </c>
+      <c r="J384" t="s">
+        <v>18</v>
+      </c>
+      <c r="K384" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A385" s="2"/>
+      <c r="B385" s="2"/>
+      <c r="C385" s="2"/>
+      <c r="D385" s="2"/>
+      <c r="E385" s="3"/>
+      <c r="F385" s="2"/>
+      <c r="G385" t="s">
+        <v>318</v>
+      </c>
+      <c r="H385" t="s">
+        <v>17</v>
+      </c>
+      <c r="I385">
+        <v>4</v>
+      </c>
+      <c r="J385" t="s">
+        <v>18</v>
+      </c>
+      <c r="K385" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A387" s="2">
+        <v>38</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E387" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F387" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G387" t="s">
+        <v>174</v>
+      </c>
+      <c r="H387" t="s">
+        <v>17</v>
+      </c>
+      <c r="I387">
+        <v>6</v>
+      </c>
+      <c r="J387" t="s">
+        <v>18</v>
+      </c>
+      <c r="K387" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A389" s="2">
+        <v>39</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E389" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F389" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G389" t="s">
+        <v>323</v>
+      </c>
+      <c r="H389" t="s">
+        <v>36</v>
+      </c>
+      <c r="I389">
+        <v>3</v>
+      </c>
+      <c r="J389" t="s">
+        <v>18</v>
+      </c>
+      <c r="K389" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A390" s="2"/>
+      <c r="B390" s="2"/>
+      <c r="C390" s="2"/>
+      <c r="D390" s="2"/>
+      <c r="E390" s="3"/>
+      <c r="F390" s="2"/>
+      <c r="G390" t="s">
+        <v>324</v>
+      </c>
+      <c r="H390" t="s">
+        <v>17</v>
+      </c>
+      <c r="I390">
+        <v>4</v>
+      </c>
+      <c r="J390" t="s">
+        <v>18</v>
+      </c>
+      <c r="K390" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A391" s="2"/>
+      <c r="B391" s="2"/>
+      <c r="C391" s="2"/>
+      <c r="D391" s="2"/>
+      <c r="E391" s="3"/>
+      <c r="F391" s="2"/>
+      <c r="G391" t="s">
+        <v>111</v>
+      </c>
+      <c r="H391" t="s">
+        <v>36</v>
+      </c>
+      <c r="I391">
+        <v>2</v>
+      </c>
+      <c r="J391" t="s">
+        <v>18</v>
+      </c>
+      <c r="K391" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A393" s="2">
+        <v>40</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E393" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F393" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="G393" t="s">
+        <v>93</v>
+      </c>
+      <c r="H393" t="s">
+        <v>36</v>
+      </c>
+      <c r="I393">
+        <v>3</v>
+      </c>
+      <c r="J393" t="s">
+        <v>18</v>
+      </c>
+      <c r="K393" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A394" s="2"/>
+      <c r="B394" s="2"/>
+      <c r="C394" s="2"/>
+      <c r="D394" s="2"/>
+      <c r="E394" s="3"/>
+      <c r="F394" s="2"/>
+      <c r="G394" t="s">
+        <v>94</v>
+      </c>
+      <c r="H394" t="s">
+        <v>17</v>
+      </c>
+      <c r="I394">
+        <v>8</v>
+      </c>
+      <c r="J394" t="s">
+        <v>18</v>
+      </c>
+      <c r="K394" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A396" s="2">
+        <v>41</v>
+      </c>
+      <c r="B396" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E396" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F396" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G396" t="s">
+        <v>329</v>
+      </c>
+      <c r="H396" t="s">
+        <v>17</v>
+      </c>
+      <c r="I396">
+        <v>2</v>
+      </c>
+      <c r="J396" t="s">
+        <v>18</v>
+      </c>
+      <c r="K396" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A397" s="2"/>
+      <c r="B397" s="2"/>
+      <c r="C397" s="2"/>
+      <c r="D397" s="2"/>
+      <c r="E397" s="3"/>
+      <c r="F397" s="2"/>
+      <c r="G397" t="s">
+        <v>35</v>
+      </c>
+      <c r="H397" t="s">
+        <v>36</v>
+      </c>
+      <c r="I397">
+        <v>2</v>
+      </c>
+      <c r="J397" t="s">
+        <v>18</v>
+      </c>
+      <c r="K397" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A398" s="2"/>
+      <c r="B398" s="2"/>
+      <c r="C398" s="2"/>
+      <c r="D398" s="2"/>
+      <c r="E398" s="3"/>
+      <c r="F398" s="2"/>
+      <c r="G398" t="s">
+        <v>194</v>
+      </c>
+      <c r="H398" t="s">
+        <v>17</v>
+      </c>
+      <c r="I398">
+        <v>8</v>
+      </c>
+      <c r="J398" t="s">
+        <v>18</v>
+      </c>
+      <c r="K398" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A399" s="2"/>
+      <c r="B399" s="2"/>
+      <c r="C399" s="2"/>
+      <c r="D399" s="2"/>
+      <c r="E399" s="3"/>
+      <c r="F399" s="2"/>
+      <c r="G399" t="s">
+        <v>193</v>
+      </c>
+      <c r="H399" t="s">
+        <v>17</v>
+      </c>
+      <c r="I399">
+        <v>3</v>
+      </c>
+      <c r="J399" t="s">
+        <v>18</v>
+      </c>
+      <c r="K399" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A400" s="2"/>
+      <c r="B400" s="2"/>
+      <c r="C400" s="2"/>
+      <c r="D400" s="2"/>
+      <c r="E400" s="3"/>
+      <c r="F400" s="2"/>
+      <c r="G400" t="s">
+        <v>169</v>
+      </c>
+      <c r="H400" t="s">
+        <v>36</v>
+      </c>
+      <c r="I400">
+        <v>12</v>
+      </c>
+      <c r="J400" t="s">
+        <v>18</v>
+      </c>
+      <c r="K400" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A401" s="2"/>
+      <c r="B401" s="2"/>
+      <c r="C401" s="2"/>
+      <c r="D401" s="2"/>
+      <c r="E401" s="3"/>
+      <c r="F401" s="2"/>
+      <c r="G401" t="s">
+        <v>306</v>
+      </c>
+      <c r="H401" t="s">
+        <v>17</v>
+      </c>
+      <c r="I401">
+        <v>3</v>
+      </c>
+      <c r="J401" t="s">
+        <v>18</v>
+      </c>
+      <c r="K401" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A402" s="2"/>
+      <c r="B402" s="2"/>
+      <c r="C402" s="2"/>
+      <c r="D402" s="2"/>
+      <c r="E402" s="3"/>
+      <c r="F402" s="2"/>
+      <c r="G402" t="s">
+        <v>330</v>
+      </c>
+      <c r="H402" t="s">
+        <v>17</v>
+      </c>
+      <c r="I402">
+        <v>3</v>
+      </c>
+      <c r="J402" t="s">
+        <v>18</v>
+      </c>
+      <c r="K402" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A403" s="2"/>
+      <c r="B403" s="2"/>
+      <c r="C403" s="2"/>
+      <c r="D403" s="2"/>
+      <c r="E403" s="3"/>
+      <c r="F403" s="2"/>
+      <c r="G403" t="s">
+        <v>331</v>
+      </c>
+      <c r="H403" t="s">
+        <v>17</v>
+      </c>
+      <c r="I403">
+        <v>4</v>
+      </c>
+      <c r="J403" t="s">
+        <v>18</v>
+      </c>
+      <c r="K403" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A404" s="2"/>
+      <c r="B404" s="2"/>
+      <c r="C404" s="2"/>
+      <c r="D404" s="2"/>
+      <c r="E404" s="3"/>
+      <c r="F404" s="2"/>
+      <c r="G404" t="s">
+        <v>332</v>
+      </c>
+      <c r="H404" t="s">
+        <v>43</v>
+      </c>
+      <c r="I404">
+        <v>4</v>
+      </c>
+      <c r="J404" t="s">
+        <v>18</v>
+      </c>
+      <c r="K404" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A405" s="2"/>
+      <c r="B405" s="2"/>
+      <c r="C405" s="2"/>
+      <c r="D405" s="2"/>
+      <c r="E405" s="3"/>
+      <c r="F405" s="2"/>
+      <c r="G405" t="s">
+        <v>193</v>
+      </c>
+      <c r="H405" t="s">
+        <v>17</v>
+      </c>
+      <c r="I405">
+        <v>3</v>
+      </c>
+      <c r="J405" t="s">
+        <v>18</v>
+      </c>
+      <c r="K405" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A406" s="2"/>
+      <c r="B406" s="2"/>
+      <c r="C406" s="2"/>
+      <c r="D406" s="2"/>
+      <c r="E406" s="3"/>
+      <c r="F406" s="2"/>
+      <c r="G406" t="s">
+        <v>333</v>
+      </c>
+      <c r="H406" t="s">
+        <v>17</v>
+      </c>
+      <c r="I406">
+        <v>2</v>
+      </c>
+      <c r="J406" t="s">
+        <v>18</v>
+      </c>
+      <c r="K406" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A407" s="2"/>
+      <c r="B407" s="2"/>
+      <c r="C407" s="2"/>
+      <c r="D407" s="2"/>
+      <c r="E407" s="3"/>
+      <c r="F407" s="2"/>
+      <c r="G407" t="s">
+        <v>334</v>
+      </c>
+      <c r="H407" t="s">
+        <v>17</v>
+      </c>
+      <c r="I407">
+        <v>4</v>
+      </c>
+      <c r="J407" t="s">
+        <v>18</v>
+      </c>
+      <c r="K407" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A408" s="2"/>
+      <c r="B408" s="2"/>
+      <c r="C408" s="2"/>
+      <c r="D408" s="2"/>
+      <c r="E408" s="3"/>
+      <c r="F408" s="2"/>
+      <c r="G408" t="s">
+        <v>335</v>
+      </c>
+      <c r="H408" t="s">
+        <v>17</v>
+      </c>
+      <c r="I408">
+        <v>4</v>
+      </c>
+      <c r="J408" t="s">
+        <v>18</v>
+      </c>
+      <c r="K408" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A409" s="2"/>
+      <c r="B409" s="2"/>
+      <c r="C409" s="2"/>
+      <c r="D409" s="2"/>
+      <c r="E409" s="3"/>
+      <c r="F409" s="2"/>
+      <c r="G409" t="s">
+        <v>30</v>
+      </c>
+      <c r="H409" t="s">
+        <v>17</v>
+      </c>
+      <c r="I409">
+        <v>2</v>
+      </c>
+      <c r="J409" t="s">
+        <v>18</v>
+      </c>
+      <c r="K409" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A410" s="2"/>
+      <c r="B410" s="2"/>
+      <c r="C410" s="2"/>
+      <c r="D410" s="2"/>
+      <c r="E410" s="3"/>
+      <c r="F410" s="2"/>
+      <c r="G410" t="s">
+        <v>336</v>
+      </c>
+      <c r="H410" t="s">
+        <v>17</v>
+      </c>
+      <c r="I410">
+        <v>1</v>
+      </c>
+      <c r="J410" t="s">
+        <v>18</v>
+      </c>
+      <c r="K410" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A412" s="2">
+        <v>42</v>
+      </c>
+      <c r="B412" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E412" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F412" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G412" t="s">
+        <v>339</v>
+      </c>
+      <c r="H412" t="s">
+        <v>17</v>
+      </c>
+      <c r="I412">
+        <v>2</v>
+      </c>
+      <c r="J412" t="s">
+        <v>18</v>
+      </c>
+      <c r="K412" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A413" s="2"/>
+      <c r="B413" s="2"/>
+      <c r="C413" s="2"/>
+      <c r="D413" s="2"/>
+      <c r="E413" s="3"/>
+      <c r="F413" s="2"/>
+      <c r="G413" t="s">
+        <v>35</v>
+      </c>
+      <c r="H413" t="s">
+        <v>36</v>
+      </c>
+      <c r="I413">
+        <v>2</v>
+      </c>
+      <c r="J413" t="s">
+        <v>18</v>
+      </c>
+      <c r="K413" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A414" s="2"/>
+      <c r="B414" s="2"/>
+      <c r="C414" s="2"/>
+      <c r="D414" s="2"/>
+      <c r="E414" s="3"/>
+      <c r="F414" s="2"/>
+      <c r="G414" t="s">
+        <v>194</v>
+      </c>
+      <c r="H414" t="s">
+        <v>17</v>
+      </c>
+      <c r="I414">
+        <v>8</v>
+      </c>
+      <c r="J414" t="s">
+        <v>18</v>
+      </c>
+      <c r="K414" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A415" s="2"/>
+      <c r="B415" s="2"/>
+      <c r="C415" s="2"/>
+      <c r="D415" s="2"/>
+      <c r="E415" s="3"/>
+      <c r="F415" s="2"/>
+      <c r="G415" t="s">
+        <v>193</v>
+      </c>
+      <c r="H415" t="s">
+        <v>17</v>
+      </c>
+      <c r="I415">
+        <v>3</v>
+      </c>
+      <c r="J415" t="s">
+        <v>18</v>
+      </c>
+      <c r="K415" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A416" s="2"/>
+      <c r="B416" s="2"/>
+      <c r="C416" s="2"/>
+      <c r="D416" s="2"/>
+      <c r="E416" s="3"/>
+      <c r="F416" s="2"/>
+      <c r="G416" t="s">
+        <v>169</v>
+      </c>
+      <c r="H416" t="s">
+        <v>36</v>
+      </c>
+      <c r="I416">
+        <v>12</v>
+      </c>
+      <c r="J416" t="s">
+        <v>18</v>
+      </c>
+      <c r="K416" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A417" s="2"/>
+      <c r="B417" s="2"/>
+      <c r="C417" s="2"/>
+      <c r="D417" s="2"/>
+      <c r="E417" s="3"/>
+      <c r="F417" s="2"/>
+      <c r="G417" t="s">
+        <v>306</v>
+      </c>
+      <c r="H417" t="s">
+        <v>17</v>
+      </c>
+      <c r="I417">
+        <v>3</v>
+      </c>
+      <c r="J417" t="s">
+        <v>18</v>
+      </c>
+      <c r="K417" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A418" s="2"/>
+      <c r="B418" s="2"/>
+      <c r="C418" s="2"/>
+      <c r="D418" s="2"/>
+      <c r="E418" s="3"/>
+      <c r="F418" s="2"/>
+      <c r="G418" t="s">
+        <v>340</v>
+      </c>
+      <c r="H418" t="s">
+        <v>17</v>
+      </c>
+      <c r="I418">
+        <v>3</v>
+      </c>
+      <c r="J418" t="s">
+        <v>18</v>
+      </c>
+      <c r="K418" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A419" s="2"/>
+      <c r="B419" s="2"/>
+      <c r="C419" s="2"/>
+      <c r="D419" s="2"/>
+      <c r="E419" s="3"/>
+      <c r="F419" s="2"/>
+      <c r="G419" t="s">
+        <v>341</v>
+      </c>
+      <c r="H419" t="s">
+        <v>43</v>
+      </c>
+      <c r="I419">
+        <v>4</v>
+      </c>
+      <c r="J419" t="s">
+        <v>18</v>
+      </c>
+      <c r="K419" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A420" s="2"/>
+      <c r="B420" s="2"/>
+      <c r="C420" s="2"/>
+      <c r="D420" s="2"/>
+      <c r="E420" s="3"/>
+      <c r="F420" s="2"/>
+      <c r="G420" t="s">
+        <v>332</v>
+      </c>
+      <c r="H420" t="s">
+        <v>43</v>
+      </c>
+      <c r="I420">
+        <v>4</v>
+      </c>
+      <c r="J420" t="s">
+        <v>18</v>
+      </c>
+      <c r="K420" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A422" s="2">
+        <v>43</v>
+      </c>
+      <c r="B422" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E422" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F422" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="G422" t="s">
+        <v>343</v>
+      </c>
+      <c r="H422" t="s">
+        <v>17</v>
+      </c>
+      <c r="I422">
+        <v>5</v>
+      </c>
+      <c r="J422" t="s">
+        <v>18</v>
+      </c>
+      <c r="K422" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A423" s="2"/>
+      <c r="B423" s="2"/>
+      <c r="C423" s="2"/>
+      <c r="D423" s="2"/>
+      <c r="E423" s="3"/>
+      <c r="F423" s="2"/>
+      <c r="G423" t="s">
+        <v>30</v>
+      </c>
+      <c r="H423" t="s">
+        <v>17</v>
+      </c>
+      <c r="I423">
+        <v>2</v>
+      </c>
+      <c r="J423" t="s">
+        <v>18</v>
+      </c>
+      <c r="K423" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A424" s="2"/>
+      <c r="B424" s="2"/>
+      <c r="C424" s="2"/>
+      <c r="D424" s="2"/>
+      <c r="E424" s="3"/>
+      <c r="F424" s="2"/>
+      <c r="G424" t="s">
+        <v>336</v>
+      </c>
+      <c r="H424" t="s">
+        <v>17</v>
+      </c>
+      <c r="I424">
+        <v>1</v>
+      </c>
+      <c r="J424" t="s">
+        <v>18</v>
+      </c>
+      <c r="K424" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A425" s="2"/>
+      <c r="B425" s="2"/>
+      <c r="C425" s="2"/>
+      <c r="D425" s="2"/>
+      <c r="E425" s="3"/>
+      <c r="F425" s="2"/>
+      <c r="G425" t="s">
+        <v>193</v>
+      </c>
+      <c r="H425" t="s">
+        <v>17</v>
+      </c>
+      <c r="I425">
+        <v>3</v>
+      </c>
+      <c r="J425" t="s">
+        <v>18</v>
+      </c>
+      <c r="K425" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A426" s="2"/>
+      <c r="B426" s="2"/>
+      <c r="C426" s="2"/>
+      <c r="D426" s="2"/>
+      <c r="E426" s="3"/>
+      <c r="F426" s="2"/>
+      <c r="G426" t="s">
+        <v>333</v>
+      </c>
+      <c r="H426" t="s">
+        <v>17</v>
+      </c>
+      <c r="I426">
+        <v>2</v>
+      </c>
+      <c r="J426" t="s">
+        <v>18</v>
+      </c>
+      <c r="K426" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A427" s="2"/>
+      <c r="B427" s="2"/>
+      <c r="C427" s="2"/>
+      <c r="D427" s="2"/>
+      <c r="E427" s="3"/>
+      <c r="F427" s="2"/>
+      <c r="G427" t="s">
+        <v>334</v>
+      </c>
+      <c r="H427" t="s">
+        <v>17</v>
+      </c>
+      <c r="I427">
+        <v>4</v>
+      </c>
+      <c r="J427" t="s">
+        <v>18</v>
+      </c>
+      <c r="K427" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A428" s="2"/>
+      <c r="B428" s="2"/>
+      <c r="C428" s="2"/>
+      <c r="D428" s="2"/>
+      <c r="E428" s="3"/>
+      <c r="F428" s="2"/>
+      <c r="G428" t="s">
+        <v>335</v>
+      </c>
+      <c r="H428" t="s">
+        <v>17</v>
+      </c>
+      <c r="I428">
+        <v>4</v>
+      </c>
+      <c r="J428" t="s">
+        <v>18</v>
+      </c>
+      <c r="K428" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A430" s="2">
+        <v>44</v>
+      </c>
+      <c r="B430" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E430" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F430" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="G430" t="s">
+        <v>346</v>
+      </c>
+      <c r="H430" t="s">
+        <v>17</v>
+      </c>
+      <c r="I430">
+        <v>3</v>
+      </c>
+      <c r="J430" t="s">
+        <v>18</v>
+      </c>
+      <c r="K430" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A431" s="2"/>
+      <c r="B431" s="2"/>
+      <c r="C431" s="2"/>
+      <c r="D431" s="2"/>
+      <c r="E431" s="3"/>
+      <c r="F431" s="2"/>
+      <c r="G431" t="s">
+        <v>176</v>
+      </c>
+      <c r="H431" t="s">
+        <v>17</v>
+      </c>
+      <c r="I431">
+        <v>2</v>
+      </c>
+      <c r="J431" t="s">
+        <v>18</v>
+      </c>
+      <c r="K431" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A432" s="2"/>
+      <c r="B432" s="2"/>
+      <c r="C432" s="2"/>
+      <c r="D432" s="2"/>
+      <c r="E432" s="3"/>
+      <c r="F432" s="2"/>
+      <c r="G432" t="s">
+        <v>347</v>
+      </c>
+      <c r="H432" t="s">
+        <v>17</v>
+      </c>
+      <c r="I432">
+        <v>6</v>
+      </c>
+      <c r="J432" t="s">
+        <v>18</v>
+      </c>
+      <c r="K432" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A433" s="2"/>
+      <c r="B433" s="2"/>
+      <c r="C433" s="2"/>
+      <c r="D433" s="2"/>
+      <c r="E433" s="3"/>
+      <c r="F433" s="2"/>
+      <c r="G433" t="s">
+        <v>52</v>
+      </c>
+      <c r="H433" t="s">
+        <v>43</v>
+      </c>
+      <c r="I433">
+        <v>6</v>
+      </c>
+      <c r="J433" t="s">
+        <v>18</v>
+      </c>
+      <c r="K433" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A434" s="2"/>
+      <c r="B434" s="2"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
+      <c r="E434" s="3"/>
+      <c r="F434" s="2"/>
+      <c r="G434" t="s">
+        <v>47</v>
+      </c>
+      <c r="H434" t="s">
+        <v>43</v>
+      </c>
+      <c r="I434">
+        <v>6</v>
+      </c>
+      <c r="J434" t="s">
+        <v>18</v>
+      </c>
+      <c r="K434" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A435" s="2"/>
+      <c r="B435" s="2"/>
+      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
+      <c r="E435" s="3"/>
+      <c r="F435" s="2"/>
+      <c r="G435" t="s">
+        <v>157</v>
+      </c>
+      <c r="H435" t="s">
+        <v>17</v>
+      </c>
+      <c r="I435">
+        <v>6</v>
+      </c>
+      <c r="J435" t="s">
+        <v>18</v>
+      </c>
+      <c r="K435" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A436" s="2"/>
+      <c r="B436" s="2"/>
+      <c r="C436" s="2"/>
+      <c r="D436" s="2"/>
+      <c r="E436" s="3"/>
+      <c r="F436" s="2"/>
+      <c r="G436" t="s">
+        <v>88</v>
+      </c>
+      <c r="H436" t="s">
+        <v>17</v>
+      </c>
+      <c r="I436">
+        <v>6</v>
+      </c>
+      <c r="J436" t="s">
+        <v>18</v>
+      </c>
+      <c r="K436" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A438" s="2">
+        <v>45</v>
+      </c>
+      <c r="B438" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E438" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F438" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G438" t="s">
+        <v>350</v>
+      </c>
+      <c r="H438" t="s">
+        <v>17</v>
+      </c>
+      <c r="I438">
+        <v>4</v>
+      </c>
+      <c r="J438" t="s">
+        <v>18</v>
+      </c>
+      <c r="K438" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A439" s="2"/>
+      <c r="B439" s="2"/>
+      <c r="C439" s="2"/>
+      <c r="D439" s="2"/>
+      <c r="E439" s="3"/>
+      <c r="F439" s="2"/>
+      <c r="G439" t="s">
+        <v>157</v>
+      </c>
+      <c r="H439" t="s">
+        <v>17</v>
+      </c>
+      <c r="I439">
+        <v>5</v>
+      </c>
+      <c r="J439" t="s">
+        <v>18</v>
+      </c>
+      <c r="K439" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A440" s="2"/>
+      <c r="B440" s="2"/>
+      <c r="C440" s="2"/>
+      <c r="D440" s="2"/>
+      <c r="E440" s="3"/>
+      <c r="F440" s="2"/>
+      <c r="G440" t="s">
+        <v>142</v>
+      </c>
+      <c r="H440" t="s">
+        <v>17</v>
+      </c>
+      <c r="I440">
+        <v>5</v>
+      </c>
+      <c r="J440" t="s">
+        <v>18</v>
+      </c>
+      <c r="K440" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A441" s="2"/>
+      <c r="B441" s="2"/>
+      <c r="C441" s="2"/>
+      <c r="D441" s="2"/>
+      <c r="E441" s="3"/>
+      <c r="F441" s="2"/>
+      <c r="G441" t="s">
+        <v>351</v>
+      </c>
+      <c r="H441" t="s">
+        <v>17</v>
+      </c>
+      <c r="I441">
+        <v>4</v>
+      </c>
+      <c r="J441" t="s">
+        <v>18</v>
+      </c>
+      <c r="K441" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A443" s="2">
+        <v>46</v>
+      </c>
+      <c r="B443" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E443" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F443" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G443" t="s">
+        <v>354</v>
+      </c>
+      <c r="H443" t="s">
+        <v>17</v>
+      </c>
+      <c r="I443">
+        <v>2</v>
+      </c>
+      <c r="J443" t="s">
+        <v>18</v>
+      </c>
+      <c r="K443" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A444" s="2"/>
+      <c r="B444" s="2"/>
+      <c r="C444" s="2"/>
+      <c r="D444" s="2"/>
+      <c r="E444" s="3"/>
+      <c r="F444" s="2"/>
+      <c r="G444" t="s">
+        <v>185</v>
+      </c>
+      <c r="H444" t="s">
+        <v>17</v>
+      </c>
+      <c r="I444">
+        <v>1</v>
+      </c>
+      <c r="J444" t="s">
+        <v>18</v>
+      </c>
+      <c r="K444" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A445" s="2"/>
+      <c r="B445" s="2"/>
+      <c r="C445" s="2"/>
+      <c r="D445" s="2"/>
+      <c r="E445" s="3"/>
+      <c r="F445" s="2"/>
+      <c r="G445" t="s">
+        <v>355</v>
+      </c>
+      <c r="H445" t="s">
+        <v>17</v>
+      </c>
+      <c r="I445">
+        <v>1</v>
+      </c>
+      <c r="J445" t="s">
+        <v>18</v>
+      </c>
+      <c r="K445" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A446" s="2"/>
+      <c r="B446" s="2"/>
+      <c r="C446" s="2"/>
+      <c r="D446" s="2"/>
+      <c r="E446" s="3"/>
+      <c r="F446" s="2"/>
+      <c r="G446" t="s">
+        <v>88</v>
+      </c>
+      <c r="H446" t="s">
+        <v>17</v>
+      </c>
+      <c r="I446">
+        <v>1</v>
+      </c>
+      <c r="J446" t="s">
+        <v>18</v>
+      </c>
+      <c r="K446" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A447" s="2"/>
+      <c r="B447" s="2"/>
+      <c r="C447" s="2"/>
+      <c r="D447" s="2"/>
+      <c r="E447" s="3"/>
+      <c r="F447" s="2"/>
+      <c r="G447" t="s">
+        <v>356</v>
+      </c>
+      <c r="H447" t="s">
+        <v>43</v>
+      </c>
+      <c r="I447">
+        <v>2</v>
+      </c>
+      <c r="J447" t="s">
+        <v>18</v>
+      </c>
+      <c r="K447" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A448" s="2"/>
+      <c r="B448" s="2"/>
+      <c r="C448" s="2"/>
+      <c r="D448" s="2"/>
+      <c r="E448" s="3"/>
+      <c r="F448" s="2"/>
+      <c r="G448" t="s">
+        <v>247</v>
+      </c>
+      <c r="H448" t="s">
+        <v>43</v>
+      </c>
+      <c r="I448">
+        <v>2</v>
+      </c>
+      <c r="J448" t="s">
+        <v>18</v>
+      </c>
+      <c r="K448" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A449" s="2"/>
+      <c r="B449" s="2"/>
+      <c r="C449" s="2"/>
+      <c r="D449" s="2"/>
+      <c r="E449" s="3"/>
+      <c r="F449" s="2"/>
+      <c r="G449" t="s">
+        <v>162</v>
+      </c>
+      <c r="H449" t="s">
+        <v>17</v>
+      </c>
+      <c r="I449">
+        <v>2</v>
+      </c>
+      <c r="J449" t="s">
+        <v>18</v>
+      </c>
+      <c r="K449" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A450" s="2"/>
+      <c r="B450" s="2"/>
+      <c r="C450" s="2"/>
+      <c r="D450" s="2"/>
+      <c r="E450" s="3"/>
+      <c r="F450" s="2"/>
+      <c r="G450" t="s">
+        <v>37</v>
+      </c>
+      <c r="H450" t="s">
+        <v>36</v>
+      </c>
+      <c r="I450">
+        <v>3</v>
+      </c>
+      <c r="J450" t="s">
+        <v>18</v>
+      </c>
+      <c r="K450" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A451" s="2"/>
+      <c r="B451" s="2"/>
+      <c r="C451" s="2"/>
+      <c r="D451" s="2"/>
+      <c r="E451" s="3"/>
+      <c r="F451" s="2"/>
+      <c r="G451" t="s">
+        <v>357</v>
+      </c>
+      <c r="H451" t="s">
+        <v>17</v>
+      </c>
+      <c r="I451">
+        <v>4</v>
+      </c>
+      <c r="J451" t="s">
+        <v>18</v>
+      </c>
+      <c r="K451" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A453" s="2">
+        <v>47</v>
+      </c>
+      <c r="B453" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E453" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F453" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G453" t="s">
+        <v>360</v>
+      </c>
+      <c r="H453" t="s">
+        <v>36</v>
+      </c>
+      <c r="I453">
+        <v>2</v>
+      </c>
+      <c r="J453" t="s">
+        <v>18</v>
+      </c>
+      <c r="K453" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A454" s="2"/>
+      <c r="B454" s="2"/>
+      <c r="C454" s="2"/>
+      <c r="D454" s="2"/>
+      <c r="E454" s="3"/>
+      <c r="F454" s="2"/>
+      <c r="G454" t="s">
+        <v>142</v>
+      </c>
+      <c r="H454" t="s">
+        <v>17</v>
+      </c>
+      <c r="I454">
+        <v>4</v>
+      </c>
+      <c r="J454" t="s">
+        <v>18</v>
+      </c>
+      <c r="K454" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A455" s="2"/>
+      <c r="B455" s="2"/>
+      <c r="C455" s="2"/>
+      <c r="D455" s="2"/>
+      <c r="E455" s="3"/>
+      <c r="F455" s="2"/>
+      <c r="G455" t="s">
+        <v>185</v>
+      </c>
+      <c r="H455" t="s">
+        <v>17</v>
+      </c>
+      <c r="I455">
+        <v>1</v>
+      </c>
+      <c r="J455" t="s">
+        <v>18</v>
+      </c>
+      <c r="K455" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A456" s="2"/>
+      <c r="B456" s="2"/>
+      <c r="C456" s="2"/>
+      <c r="D456" s="2"/>
+      <c r="E456" s="3"/>
+      <c r="F456" s="2"/>
+      <c r="G456" t="s">
+        <v>361</v>
+      </c>
+      <c r="H456" t="s">
+        <v>17</v>
+      </c>
+      <c r="I456">
+        <v>2</v>
+      </c>
+      <c r="J456" t="s">
+        <v>18</v>
+      </c>
+      <c r="K456" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A457" s="2"/>
+      <c r="B457" s="2"/>
+      <c r="C457" s="2"/>
+      <c r="D457" s="2"/>
+      <c r="E457" s="3"/>
+      <c r="F457" s="2"/>
+      <c r="G457" t="s">
+        <v>194</v>
+      </c>
+      <c r="H457" t="s">
+        <v>17</v>
+      </c>
+      <c r="I457">
+        <v>3</v>
+      </c>
+      <c r="J457" t="s">
+        <v>18</v>
+      </c>
+      <c r="K457" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A458" s="2"/>
+      <c r="B458" s="2"/>
+      <c r="C458" s="2"/>
+      <c r="D458" s="2"/>
+      <c r="E458" s="3"/>
+      <c r="F458" s="2"/>
+      <c r="G458" t="s">
+        <v>268</v>
+      </c>
+      <c r="H458" t="s">
+        <v>43</v>
+      </c>
+      <c r="I458">
+        <v>1</v>
+      </c>
+      <c r="J458" t="s">
+        <v>18</v>
+      </c>
+      <c r="K458" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A459" s="2"/>
+      <c r="B459" s="2"/>
+      <c r="C459" s="2"/>
+      <c r="D459" s="2"/>
+      <c r="E459" s="3"/>
+      <c r="F459" s="2"/>
+      <c r="G459" t="s">
+        <v>293</v>
+      </c>
+      <c r="H459" t="s">
+        <v>17</v>
+      </c>
+      <c r="I459">
+        <v>1</v>
+      </c>
+      <c r="J459" t="s">
+        <v>18</v>
+      </c>
+      <c r="K459" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A460" s="2"/>
+      <c r="B460" s="2"/>
+      <c r="C460" s="2"/>
+      <c r="D460" s="2"/>
+      <c r="E460" s="3"/>
+      <c r="F460" s="2"/>
+      <c r="G460" t="s">
+        <v>169</v>
+      </c>
+      <c r="H460" t="s">
+        <v>36</v>
+      </c>
+      <c r="I460">
+        <v>2</v>
+      </c>
+      <c r="J460" t="s">
+        <v>18</v>
+      </c>
+      <c r="K460" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A462" s="2">
+        <v>48</v>
+      </c>
+      <c r="B462" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C462" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E462" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="F462" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G462" t="s">
+        <v>364</v>
+      </c>
+      <c r="H462" t="s">
+        <v>17</v>
+      </c>
+      <c r="I462">
+        <v>8</v>
+      </c>
+      <c r="J462" t="s">
+        <v>18</v>
+      </c>
+      <c r="K462" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A463" s="2"/>
+      <c r="B463" s="2"/>
+      <c r="C463" s="2"/>
+      <c r="D463" s="2"/>
+      <c r="E463" s="3"/>
+      <c r="F463" s="2"/>
+      <c r="G463" t="s">
+        <v>365</v>
+      </c>
+      <c r="H463" t="s">
+        <v>17</v>
+      </c>
+      <c r="I463">
+        <v>8</v>
+      </c>
+      <c r="J463" t="s">
+        <v>18</v>
+      </c>
+      <c r="K463" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A464" s="2"/>
+      <c r="B464" s="2"/>
+      <c r="C464" s="2"/>
+      <c r="D464" s="2"/>
+      <c r="E464" s="3"/>
+      <c r="F464" s="2"/>
+      <c r="G464" t="s">
+        <v>366</v>
+      </c>
+      <c r="H464" t="s">
+        <v>17</v>
+      </c>
+      <c r="I464">
+        <v>4</v>
+      </c>
+      <c r="J464" t="s">
+        <v>18</v>
+      </c>
+      <c r="K464" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A465" s="2"/>
+      <c r="B465" s="2"/>
+      <c r="C465" s="2"/>
+      <c r="D465" s="2"/>
+      <c r="E465" s="3"/>
+      <c r="F465" s="2"/>
+      <c r="G465" t="s">
+        <v>367</v>
+      </c>
+      <c r="H465" t="s">
+        <v>17</v>
+      </c>
+      <c r="I465">
+        <v>2</v>
+      </c>
+      <c r="J465" t="s">
+        <v>18</v>
+      </c>
+      <c r="K465" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A466" s="2"/>
+      <c r="B466" s="2"/>
+      <c r="C466" s="2"/>
+      <c r="D466" s="2"/>
+      <c r="E466" s="3"/>
+      <c r="F466" s="2"/>
+      <c r="G466" t="s">
+        <v>368</v>
+      </c>
+      <c r="H466" t="s">
+        <v>17</v>
+      </c>
+      <c r="I466">
+        <v>2</v>
+      </c>
+      <c r="J466" t="s">
+        <v>18</v>
+      </c>
+      <c r="K466" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A467" s="2"/>
+      <c r="B467" s="2"/>
+      <c r="C467" s="2"/>
+      <c r="D467" s="2"/>
+      <c r="E467" s="3"/>
+      <c r="F467" s="2"/>
+      <c r="G467" t="s">
+        <v>369</v>
+      </c>
+      <c r="H467" t="s">
+        <v>17</v>
+      </c>
+      <c r="I467">
+        <v>2</v>
+      </c>
+      <c r="J467" t="s">
+        <v>18</v>
+      </c>
+      <c r="K467" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A468" s="2"/>
+      <c r="B468" s="2"/>
+      <c r="C468" s="2"/>
+      <c r="D468" s="2"/>
+      <c r="E468" s="3"/>
+      <c r="F468" s="2"/>
+      <c r="G468" t="s">
+        <v>370</v>
+      </c>
+      <c r="H468" t="s">
+        <v>17</v>
+      </c>
+      <c r="I468">
+        <v>4</v>
+      </c>
+      <c r="J468" t="s">
+        <v>18</v>
+      </c>
+      <c r="K468" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A469" s="2"/>
+      <c r="B469" s="2"/>
+      <c r="C469" s="2"/>
+      <c r="D469" s="2"/>
+      <c r="E469" s="3"/>
+      <c r="F469" s="2"/>
+      <c r="G469" t="s">
+        <v>371</v>
+      </c>
+      <c r="H469" t="s">
+        <v>17</v>
+      </c>
+      <c r="I469">
+        <v>8</v>
+      </c>
+      <c r="J469" t="s">
+        <v>18</v>
+      </c>
+      <c r="K469" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A470" s="2"/>
+      <c r="B470" s="2"/>
+      <c r="C470" s="2"/>
+      <c r="D470" s="2"/>
+      <c r="E470" s="3"/>
+      <c r="F470" s="2"/>
+      <c r="G470" t="s">
+        <v>372</v>
+      </c>
+      <c r="H470" t="s">
+        <v>17</v>
+      </c>
+      <c r="I470">
+        <v>4</v>
+      </c>
+      <c r="J470" t="s">
+        <v>18</v>
+      </c>
+      <c r="K470" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A471" s="2"/>
+      <c r="B471" s="2"/>
+      <c r="C471" s="2"/>
+      <c r="D471" s="2"/>
+      <c r="E471" s="3"/>
+      <c r="F471" s="2"/>
+      <c r="G471" t="s">
+        <v>373</v>
+      </c>
+      <c r="H471" t="s">
+        <v>17</v>
+      </c>
+      <c r="I471">
+        <v>4</v>
+      </c>
+      <c r="J471" t="s">
+        <v>18</v>
+      </c>
+      <c r="K471" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A472" s="2"/>
+      <c r="B472" s="2"/>
+      <c r="C472" s="2"/>
+      <c r="D472" s="2"/>
+      <c r="E472" s="3"/>
+      <c r="F472" s="2"/>
+      <c r="G472" t="s">
+        <v>374</v>
+      </c>
+      <c r="H472" t="s">
+        <v>17</v>
+      </c>
+      <c r="I472">
+        <v>4</v>
+      </c>
+      <c r="J472" t="s">
+        <v>18</v>
+      </c>
+      <c r="K472" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A473" s="2"/>
+      <c r="B473" s="2"/>
+      <c r="C473" s="2"/>
+      <c r="D473" s="2"/>
+      <c r="E473" s="3"/>
+      <c r="F473" s="2"/>
+      <c r="G473" t="s">
+        <v>375</v>
+      </c>
+      <c r="H473" t="s">
+        <v>17</v>
+      </c>
+      <c r="I473">
+        <v>4</v>
+      </c>
+      <c r="J473" t="s">
+        <v>18</v>
+      </c>
+      <c r="K473" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A474" s="2"/>
+      <c r="B474" s="2"/>
+      <c r="C474" s="2"/>
+      <c r="D474" s="2"/>
+      <c r="E474" s="3"/>
+      <c r="F474" s="2"/>
+      <c r="G474" t="s">
+        <v>376</v>
+      </c>
+      <c r="H474" t="s">
+        <v>17</v>
+      </c>
+      <c r="I474">
+        <v>8</v>
+      </c>
+      <c r="J474" t="s">
+        <v>18</v>
+      </c>
+      <c r="K474" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A475" s="2"/>
+      <c r="B475" s="2"/>
+      <c r="C475" s="2"/>
+      <c r="D475" s="2"/>
+      <c r="E475" s="3"/>
+      <c r="F475" s="2"/>
+      <c r="G475" t="s">
+        <v>377</v>
+      </c>
+      <c r="H475" t="s">
+        <v>17</v>
+      </c>
+      <c r="I475">
+        <v>4</v>
+      </c>
+      <c r="J475" t="s">
+        <v>18</v>
+      </c>
+      <c r="K475" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A476" s="2"/>
+      <c r="B476" s="2"/>
+      <c r="C476" s="2"/>
+      <c r="D476" s="2"/>
+      <c r="E476" s="3"/>
+      <c r="F476" s="2"/>
+      <c r="G476" t="s">
+        <v>378</v>
+      </c>
+      <c r="H476" t="s">
+        <v>17</v>
+      </c>
+      <c r="I476">
+        <v>4</v>
+      </c>
+      <c r="J476" t="s">
+        <v>18</v>
+      </c>
+      <c r="K476" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A477" s="2"/>
+      <c r="B477" s="2"/>
+      <c r="C477" s="2"/>
+      <c r="D477" s="2"/>
+      <c r="E477" s="3"/>
+      <c r="F477" s="2"/>
+      <c r="G477" t="s">
+        <v>379</v>
+      </c>
+      <c r="H477" t="s">
+        <v>17</v>
+      </c>
+      <c r="I477">
+        <v>4</v>
+      </c>
+      <c r="J477" t="s">
+        <v>18</v>
+      </c>
+      <c r="K477" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A478" s="2"/>
+      <c r="B478" s="2"/>
+      <c r="C478" s="2"/>
+      <c r="D478" s="2"/>
+      <c r="E478" s="3"/>
+      <c r="F478" s="2"/>
+      <c r="G478" t="s">
+        <v>380</v>
+      </c>
+      <c r="H478" t="s">
+        <v>17</v>
+      </c>
+      <c r="I478">
+        <v>4</v>
+      </c>
+      <c r="J478" t="s">
+        <v>18</v>
+      </c>
+      <c r="K478" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A479" s="2"/>
+      <c r="B479" s="2"/>
+      <c r="C479" s="2"/>
+      <c r="D479" s="2"/>
+      <c r="E479" s="3"/>
+      <c r="F479" s="2"/>
+      <c r="G479" t="s">
+        <v>381</v>
+      </c>
+      <c r="H479" t="s">
+        <v>17</v>
+      </c>
+      <c r="I479">
+        <v>4</v>
+      </c>
+      <c r="J479" t="s">
+        <v>18</v>
+      </c>
+      <c r="K479" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A480" s="2"/>
+      <c r="B480" s="2"/>
+      <c r="C480" s="2"/>
+      <c r="D480" s="2"/>
+      <c r="E480" s="3"/>
+      <c r="F480" s="2"/>
+      <c r="G480" t="s">
+        <v>382</v>
+      </c>
+      <c r="H480" t="s">
+        <v>17</v>
+      </c>
+      <c r="I480">
+        <v>4</v>
+      </c>
+      <c r="J480" t="s">
+        <v>18</v>
+      </c>
+      <c r="K480" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="84">
+  <mergeCells count="258">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="C2:C4"/>
@@ -3606,6 +12203,180 @@
     <mergeCell ref="D103:D124"/>
     <mergeCell ref="E103:E124"/>
     <mergeCell ref="F103:F124"/>
+    <mergeCell ref="A126:A130"/>
+    <mergeCell ref="B126:B130"/>
+    <mergeCell ref="C126:C130"/>
+    <mergeCell ref="D126:D130"/>
+    <mergeCell ref="E126:E130"/>
+    <mergeCell ref="F126:F130"/>
+    <mergeCell ref="A134:A135"/>
+    <mergeCell ref="B134:B135"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:D135"/>
+    <mergeCell ref="E134:E135"/>
+    <mergeCell ref="F134:F135"/>
+    <mergeCell ref="A137:A143"/>
+    <mergeCell ref="B137:B143"/>
+    <mergeCell ref="C137:C143"/>
+    <mergeCell ref="D137:D143"/>
+    <mergeCell ref="E137:E143"/>
+    <mergeCell ref="F137:F143"/>
+    <mergeCell ref="A145:A147"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="C145:C147"/>
+    <mergeCell ref="D145:D147"/>
+    <mergeCell ref="E145:E147"/>
+    <mergeCell ref="F145:F147"/>
+    <mergeCell ref="A149:A154"/>
+    <mergeCell ref="B149:B154"/>
+    <mergeCell ref="C149:C154"/>
+    <mergeCell ref="D149:D154"/>
+    <mergeCell ref="E149:E154"/>
+    <mergeCell ref="F149:F154"/>
+    <mergeCell ref="A156:A198"/>
+    <mergeCell ref="B156:B198"/>
+    <mergeCell ref="C156:C198"/>
+    <mergeCell ref="D156:D198"/>
+    <mergeCell ref="E156:E198"/>
+    <mergeCell ref="F156:F198"/>
+    <mergeCell ref="A200:A204"/>
+    <mergeCell ref="B200:B204"/>
+    <mergeCell ref="C200:C204"/>
+    <mergeCell ref="D200:D204"/>
+    <mergeCell ref="E200:E204"/>
+    <mergeCell ref="F200:F204"/>
+    <mergeCell ref="A206:A207"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="C206:C207"/>
+    <mergeCell ref="D206:D207"/>
+    <mergeCell ref="E206:E207"/>
+    <mergeCell ref="F206:F207"/>
+    <mergeCell ref="A209:A233"/>
+    <mergeCell ref="B209:B233"/>
+    <mergeCell ref="C209:C233"/>
+    <mergeCell ref="D209:D233"/>
+    <mergeCell ref="E209:E233"/>
+    <mergeCell ref="F209:F233"/>
+    <mergeCell ref="A235:A241"/>
+    <mergeCell ref="B235:B241"/>
+    <mergeCell ref="C235:C241"/>
+    <mergeCell ref="D235:D241"/>
+    <mergeCell ref="E235:E241"/>
+    <mergeCell ref="F235:F241"/>
+    <mergeCell ref="A243:A249"/>
+    <mergeCell ref="B243:B249"/>
+    <mergeCell ref="C243:C249"/>
+    <mergeCell ref="D243:D249"/>
+    <mergeCell ref="E243:E249"/>
+    <mergeCell ref="F243:F249"/>
+    <mergeCell ref="A251:A256"/>
+    <mergeCell ref="B251:B256"/>
+    <mergeCell ref="C251:C256"/>
+    <mergeCell ref="D251:D256"/>
+    <mergeCell ref="E251:E256"/>
+    <mergeCell ref="F251:F256"/>
+    <mergeCell ref="A258:A287"/>
+    <mergeCell ref="B258:B287"/>
+    <mergeCell ref="C258:C287"/>
+    <mergeCell ref="D258:D287"/>
+    <mergeCell ref="E258:E287"/>
+    <mergeCell ref="F258:F287"/>
+    <mergeCell ref="A289:A314"/>
+    <mergeCell ref="B289:B314"/>
+    <mergeCell ref="C289:C314"/>
+    <mergeCell ref="D289:D314"/>
+    <mergeCell ref="E289:E314"/>
+    <mergeCell ref="F289:F314"/>
+    <mergeCell ref="A316:A323"/>
+    <mergeCell ref="B316:B323"/>
+    <mergeCell ref="C316:C323"/>
+    <mergeCell ref="D316:D323"/>
+    <mergeCell ref="E316:E323"/>
+    <mergeCell ref="F316:F323"/>
+    <mergeCell ref="A325:A350"/>
+    <mergeCell ref="B325:B350"/>
+    <mergeCell ref="C325:C350"/>
+    <mergeCell ref="D325:D350"/>
+    <mergeCell ref="E325:E350"/>
+    <mergeCell ref="F325:F350"/>
+    <mergeCell ref="A352:A365"/>
+    <mergeCell ref="B352:B365"/>
+    <mergeCell ref="C352:C365"/>
+    <mergeCell ref="D352:D365"/>
+    <mergeCell ref="E352:E365"/>
+    <mergeCell ref="F352:F365"/>
+    <mergeCell ref="A367:A382"/>
+    <mergeCell ref="B367:B382"/>
+    <mergeCell ref="C367:C382"/>
+    <mergeCell ref="D367:D382"/>
+    <mergeCell ref="E367:E382"/>
+    <mergeCell ref="F367:F382"/>
+    <mergeCell ref="A384:A385"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="C384:C385"/>
+    <mergeCell ref="D384:D385"/>
+    <mergeCell ref="E384:E385"/>
+    <mergeCell ref="F384:F385"/>
+    <mergeCell ref="A389:A391"/>
+    <mergeCell ref="B389:B391"/>
+    <mergeCell ref="C389:C391"/>
+    <mergeCell ref="D389:D391"/>
+    <mergeCell ref="E389:E391"/>
+    <mergeCell ref="F389:F391"/>
+    <mergeCell ref="A393:A394"/>
+    <mergeCell ref="B393:B394"/>
+    <mergeCell ref="C393:C394"/>
+    <mergeCell ref="D393:D394"/>
+    <mergeCell ref="E393:E394"/>
+    <mergeCell ref="F393:F394"/>
+    <mergeCell ref="A396:A410"/>
+    <mergeCell ref="B396:B410"/>
+    <mergeCell ref="C396:C410"/>
+    <mergeCell ref="D396:D410"/>
+    <mergeCell ref="E396:E410"/>
+    <mergeCell ref="F396:F410"/>
+    <mergeCell ref="A412:A420"/>
+    <mergeCell ref="B412:B420"/>
+    <mergeCell ref="C412:C420"/>
+    <mergeCell ref="D412:D420"/>
+    <mergeCell ref="E412:E420"/>
+    <mergeCell ref="F412:F420"/>
+    <mergeCell ref="A422:A428"/>
+    <mergeCell ref="B422:B428"/>
+    <mergeCell ref="C422:C428"/>
+    <mergeCell ref="D422:D428"/>
+    <mergeCell ref="E422:E428"/>
+    <mergeCell ref="F422:F428"/>
+    <mergeCell ref="A430:A436"/>
+    <mergeCell ref="B430:B436"/>
+    <mergeCell ref="C430:C436"/>
+    <mergeCell ref="D430:D436"/>
+    <mergeCell ref="E430:E436"/>
+    <mergeCell ref="F430:F436"/>
+    <mergeCell ref="A438:A441"/>
+    <mergeCell ref="B438:B441"/>
+    <mergeCell ref="C438:C441"/>
+    <mergeCell ref="D438:D441"/>
+    <mergeCell ref="E438:E441"/>
+    <mergeCell ref="F438:F441"/>
+    <mergeCell ref="A443:A451"/>
+    <mergeCell ref="B443:B451"/>
+    <mergeCell ref="C443:C451"/>
+    <mergeCell ref="D443:D451"/>
+    <mergeCell ref="E443:E451"/>
+    <mergeCell ref="F443:F451"/>
+    <mergeCell ref="A453:A460"/>
+    <mergeCell ref="B453:B460"/>
+    <mergeCell ref="C453:C460"/>
+    <mergeCell ref="D453:D460"/>
+    <mergeCell ref="E453:E460"/>
+    <mergeCell ref="F453:F460"/>
+    <mergeCell ref="A462:A480"/>
+    <mergeCell ref="B462:B480"/>
+    <mergeCell ref="C462:C480"/>
+    <mergeCell ref="D462:D480"/>
+    <mergeCell ref="E462:E480"/>
+    <mergeCell ref="F462:F480"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2964" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4100" uniqueCount="694">
   <si>
     <t>S.No</t>
   </si>
@@ -1559,6 +1559,540 @@
   </si>
   <si>
     <t>EXTRA W/S 1969 NEW TILE RED-Q</t>
+  </si>
+  <si>
+    <t>19/08/2026, 8:59:37 am</t>
+  </si>
+  <si>
+    <t>Rehan traders</t>
+  </si>
+  <si>
+    <t>BOLD R.O.P 7704-G</t>
+  </si>
+  <si>
+    <t>19/08/2026, 9:15:44 am</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1919 ASH WHITE-Q</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1949 SAND STONE-G</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1949 SAND STONE-Q</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW3160 SKY GREY-G</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW2685 CAMEO-G</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW2685 CAMEO-Q</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1959 GOOSE WING-Q</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW3162 SILVERY-Q</t>
+  </si>
+  <si>
+    <t>BOLD WEATHER SAFE BW1951 WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE523 BEIGE-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE507 PUMICE-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE512 COURT GREY-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE533 SOFT TERRACOTTA-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE532 COCOA BROWN-Q</t>
+  </si>
+  <si>
+    <t>20/08/2026, 9:39:32 am</t>
+  </si>
+  <si>
+    <t>Al Jahangri NA H</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 13 SP SPICE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 41 OFF WHITE-G</t>
+  </si>
+  <si>
+    <t>20/08/2026, 10:09:41 am</t>
+  </si>
+  <si>
+    <t>Aamil Paint Company</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1972 PEARL-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 6172 PINK PAVAL-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S U1953 ROSE LEMON-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1971 LEAF GREEN-G</t>
+  </si>
+  <si>
+    <t>20/08/2026, 5:00:04 pm</t>
+  </si>
+  <si>
+    <t>BOLD OIL MATT 5504 SILVER WHITE-G</t>
+  </si>
+  <si>
+    <t>21/08/2026, 10:58:11 am</t>
+  </si>
+  <si>
+    <t>Muqtafs Paint</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 34 PEACH-D</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 69 DIYAR-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 225 WOOD SMOKE-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9988 CAMEO-D</t>
+  </si>
+  <si>
+    <t>21/08/2026, 11:33:33 am</t>
+  </si>
+  <si>
+    <t>لحدوا لروف</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1919-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1958-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1962-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1965-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 1968-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 2912-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 2910-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 3147-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 7048-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9028-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9048-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9058-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9058-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9059-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9061-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9018-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9075-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9075-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9074-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9073-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9006-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9024-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9019-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9032-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9071-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9068-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9069-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9067-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9007-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 9007-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 232-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 239-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 86 WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 233-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 225-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 63-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 57-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 301-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 327-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 336-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 336-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 68-Q</t>
+  </si>
+  <si>
+    <t>21/08/2026, 11:45:20 am</t>
+  </si>
+  <si>
+    <t>جوالعروف</t>
+  </si>
+  <si>
+    <t>EXTRA W/S U1955 SWEET TULIP-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 1962 MOON SHADE-G</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 2910 RED OXIDE-G</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9006 SP MERRY GOLD-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9019 SNOW FIELD-Q</t>
+  </si>
+  <si>
+    <t>EXTRA STAINLESS 9032 SHINGLE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ANTIFUNGAL DB86 OIL PRIMER-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 68 WHITE ASH-Q</t>
+  </si>
+  <si>
+    <t>21/08/2026, 11:49:35 am</t>
+  </si>
+  <si>
+    <t>abdul raouf</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8748 PEACH SHADOW-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 8746 ABSTRACT WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 22 APPLE GREEN-G</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 40 SP MANGO MOOD-G</t>
+  </si>
+  <si>
+    <t>EXTRA RED OXIDE PRIMER 312-G</t>
+  </si>
+  <si>
+    <t>21/08/2026, 4:11:05 pm</t>
+  </si>
+  <si>
+    <t>HAJI NIZAM PAINT</t>
+  </si>
+  <si>
+    <t>EXTRA SEMI 37 BLACK-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE521 SUNRISE YELLOW-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE525 SOFT VIOLET-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE515 ASH GREY-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE W/B PRIMER SEALER EX202-G</t>
+  </si>
+  <si>
+    <t>21/08/2026, 4:14:15 pm</t>
+  </si>
+  <si>
+    <t>Saeed Paint House</t>
+  </si>
+  <si>
+    <t>EXTRA W/S 2087 BEIGE-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT U229 SILVER WHITE-Q</t>
+  </si>
+  <si>
+    <t>21/08/2026, 4:24:02 pm</t>
+  </si>
+  <si>
+    <t>Mosa jee</t>
+  </si>
+  <si>
+    <t>21/08/2026, 5:05:32 pm</t>
+  </si>
+  <si>
+    <t>IMRAN PAINT GIZRI</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER ASH WHITE-D</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 8-G</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 22-G</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 30-G</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 18-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 22-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 31-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 40-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 8744-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 8745-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 8762-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 8767-Q</t>
+  </si>
+  <si>
+    <t>EXTRA DISTEMPER 8770-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 41-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 51-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 60-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 66-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 339-G</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 303-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 58-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 66-Q</t>
+  </si>
+  <si>
+    <t>EXTRA ENAMEL 69-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT WHITE-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 71-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 88-G</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 88-Q</t>
+  </si>
+  <si>
+    <t>EXTRA MATT 216-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WATER MATT 9021-G</t>
+  </si>
+  <si>
+    <t>EXTRA WATER MATT 9061-G</t>
+  </si>
+  <si>
+    <t>EXTRA WATER MATT 9065-G</t>
+  </si>
+  <si>
+    <t>EXTRA WATER MATT 9001-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WATER MATT 9021-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1952-G</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 2067-G</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 2913-G</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1951-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1952-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1919-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1956-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1958-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 1966-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 2067-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 3160-Q</t>
+  </si>
+  <si>
+    <t>EXTRA WEATHER SHIELD 4130-Q</t>
+  </si>
+  <si>
+    <t>EXTRA 3 IN 1 PLASTIC WHITE-G</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE502 WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE503 OFF WHITE-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE509 GOLD.BROWN-Q</t>
+  </si>
+  <si>
+    <t>EXCLUSIVE ENAMEL EE508 MIDDLE BLUE-Q</t>
+  </si>
+  <si>
+    <t>EXTRA PUTTY-G</t>
+  </si>
+  <si>
+    <t>EXTRA PUTTY-D</t>
+  </si>
+  <si>
+    <t>EXTRA WATER PRIMER-D</t>
+  </si>
+  <si>
+    <t>27/08/2026, 2:11:39 pm</t>
+  </si>
+  <si>
+    <t>Kaleem B/M</t>
+  </si>
+  <si>
+    <t>BOLD WATER BASED PRIMER 7702-Q</t>
+  </si>
+  <si>
+    <t>27/08/2026, 4:17:10 pm</t>
+  </si>
+  <si>
+    <t>Hamid Paint 2248</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8829 COURT GREY-Q</t>
+  </si>
+  <si>
+    <t>BOLD ENAMEL 8835 BLACK-Q</t>
+  </si>
+  <si>
+    <t>BOLD WATER MATT 6628 SOFT BLUE-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9961 STEEL GREY-G</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9961 STEEL GREY-Q</t>
+  </si>
+  <si>
+    <t>BOLD SEMI 9997 ASH WHITE-G</t>
+  </si>
+  <si>
+    <t>27/08/2026, 4:17:46 pm</t>
+  </si>
+  <si>
+    <t>Bismillah paint G Johar</t>
   </si>
 </sst>
 </file>
@@ -1954,7 +2488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K729"/>
+  <dimension ref="A1:K1009"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -18364,8 +18898,6272 @@
         <v>18</v>
       </c>
     </row>
+    <row r="731" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A731" s="2">
+        <v>38</v>
+      </c>
+      <c r="B731" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="C731" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D731" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E731" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F731" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="G731" t="s">
+        <v>518</v>
+      </c>
+      <c r="H731" t="s">
+        <v>17</v>
+      </c>
+      <c r="I731">
+        <v>2</v>
+      </c>
+      <c r="J731" t="s">
+        <v>153</v>
+      </c>
+      <c r="K731" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="733" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A733" s="2">
+        <v>39</v>
+      </c>
+      <c r="B733" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="C733" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D733" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E733" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F733" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G733" t="s">
+        <v>330</v>
+      </c>
+      <c r="H733" t="s">
+        <v>76</v>
+      </c>
+      <c r="I733">
+        <v>2</v>
+      </c>
+      <c r="J733" t="s">
+        <v>153</v>
+      </c>
+      <c r="K733" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="734" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A734" s="2"/>
+      <c r="B734" s="2"/>
+      <c r="C734" s="2"/>
+      <c r="D734" s="2"/>
+      <c r="E734" s="3"/>
+      <c r="F734" s="2"/>
+      <c r="G734" t="s">
+        <v>520</v>
+      </c>
+      <c r="H734" t="s">
+        <v>55</v>
+      </c>
+      <c r="I734">
+        <v>3</v>
+      </c>
+      <c r="J734" t="s">
+        <v>153</v>
+      </c>
+      <c r="K734" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="735" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A735" s="2"/>
+      <c r="B735" s="2"/>
+      <c r="C735" s="2"/>
+      <c r="D735" s="2"/>
+      <c r="E735" s="3"/>
+      <c r="F735" s="2"/>
+      <c r="G735" t="s">
+        <v>521</v>
+      </c>
+      <c r="H735" t="s">
+        <v>17</v>
+      </c>
+      <c r="I735">
+        <v>1</v>
+      </c>
+      <c r="J735" t="s">
+        <v>153</v>
+      </c>
+      <c r="K735" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="736" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A736" s="2"/>
+      <c r="B736" s="2"/>
+      <c r="C736" s="2"/>
+      <c r="D736" s="2"/>
+      <c r="E736" s="3"/>
+      <c r="F736" s="2"/>
+      <c r="G736" t="s">
+        <v>522</v>
+      </c>
+      <c r="H736" t="s">
+        <v>55</v>
+      </c>
+      <c r="I736">
+        <v>1</v>
+      </c>
+      <c r="J736" t="s">
+        <v>153</v>
+      </c>
+      <c r="K736" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="737" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A737" s="2"/>
+      <c r="B737" s="2"/>
+      <c r="C737" s="2"/>
+      <c r="D737" s="2"/>
+      <c r="E737" s="3"/>
+      <c r="F737" s="2"/>
+      <c r="G737" t="s">
+        <v>523</v>
+      </c>
+      <c r="H737" t="s">
+        <v>17</v>
+      </c>
+      <c r="I737">
+        <v>1</v>
+      </c>
+      <c r="J737" t="s">
+        <v>153</v>
+      </c>
+      <c r="K737" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="738" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A738" s="2"/>
+      <c r="B738" s="2"/>
+      <c r="C738" s="2"/>
+      <c r="D738" s="2"/>
+      <c r="E738" s="3"/>
+      <c r="F738" s="2"/>
+      <c r="G738" t="s">
+        <v>524</v>
+      </c>
+      <c r="H738" t="s">
+        <v>17</v>
+      </c>
+      <c r="I738">
+        <v>1</v>
+      </c>
+      <c r="J738" t="s">
+        <v>153</v>
+      </c>
+      <c r="K738" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="739" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A739" s="2"/>
+      <c r="B739" s="2"/>
+      <c r="C739" s="2"/>
+      <c r="D739" s="2"/>
+      <c r="E739" s="3"/>
+      <c r="F739" s="2"/>
+      <c r="G739" t="s">
+        <v>525</v>
+      </c>
+      <c r="H739" t="s">
+        <v>55</v>
+      </c>
+      <c r="I739">
+        <v>2</v>
+      </c>
+      <c r="J739" t="s">
+        <v>153</v>
+      </c>
+      <c r="K739" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="740" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A740" s="2"/>
+      <c r="B740" s="2"/>
+      <c r="C740" s="2"/>
+      <c r="D740" s="2"/>
+      <c r="E740" s="3"/>
+      <c r="F740" s="2"/>
+      <c r="G740" t="s">
+        <v>526</v>
+      </c>
+      <c r="H740" t="s">
+        <v>55</v>
+      </c>
+      <c r="I740">
+        <v>2</v>
+      </c>
+      <c r="J740" t="s">
+        <v>153</v>
+      </c>
+      <c r="K740" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="741" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A741" s="2"/>
+      <c r="B741" s="2"/>
+      <c r="C741" s="2"/>
+      <c r="D741" s="2"/>
+      <c r="E741" s="3"/>
+      <c r="F741" s="2"/>
+      <c r="G741" t="s">
+        <v>527</v>
+      </c>
+      <c r="H741" t="s">
+        <v>55</v>
+      </c>
+      <c r="I741">
+        <v>2</v>
+      </c>
+      <c r="J741" t="s">
+        <v>153</v>
+      </c>
+      <c r="K741" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="742" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A742" s="2"/>
+      <c r="B742" s="2"/>
+      <c r="C742" s="2"/>
+      <c r="D742" s="2"/>
+      <c r="E742" s="3"/>
+      <c r="F742" s="2"/>
+      <c r="G742" t="s">
+        <v>528</v>
+      </c>
+      <c r="H742" t="s">
+        <v>55</v>
+      </c>
+      <c r="I742">
+        <v>2</v>
+      </c>
+      <c r="J742" t="s">
+        <v>153</v>
+      </c>
+      <c r="K742" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="743" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A743" s="2"/>
+      <c r="B743" s="2"/>
+      <c r="C743" s="2"/>
+      <c r="D743" s="2"/>
+      <c r="E743" s="3"/>
+      <c r="F743" s="2"/>
+      <c r="G743" t="s">
+        <v>96</v>
+      </c>
+      <c r="H743" t="s">
+        <v>55</v>
+      </c>
+      <c r="I743">
+        <v>3</v>
+      </c>
+      <c r="J743" t="s">
+        <v>153</v>
+      </c>
+      <c r="K743" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="744" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A744" s="2"/>
+      <c r="B744" s="2"/>
+      <c r="C744" s="2"/>
+      <c r="D744" s="2"/>
+      <c r="E744" s="3"/>
+      <c r="F744" s="2"/>
+      <c r="G744" t="s">
+        <v>195</v>
+      </c>
+      <c r="H744" t="s">
+        <v>17</v>
+      </c>
+      <c r="I744">
+        <v>1</v>
+      </c>
+      <c r="J744" t="s">
+        <v>153</v>
+      </c>
+      <c r="K744" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="745" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A745" s="2"/>
+      <c r="B745" s="2"/>
+      <c r="C745" s="2"/>
+      <c r="D745" s="2"/>
+      <c r="E745" s="3"/>
+      <c r="F745" s="2"/>
+      <c r="G745" t="s">
+        <v>469</v>
+      </c>
+      <c r="H745" t="s">
+        <v>17</v>
+      </c>
+      <c r="I745">
+        <v>1</v>
+      </c>
+      <c r="J745" t="s">
+        <v>153</v>
+      </c>
+      <c r="K745" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="746" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A746" s="2"/>
+      <c r="B746" s="2"/>
+      <c r="C746" s="2"/>
+      <c r="D746" s="2"/>
+      <c r="E746" s="3"/>
+      <c r="F746" s="2"/>
+      <c r="G746" t="s">
+        <v>33</v>
+      </c>
+      <c r="H746" t="s">
+        <v>17</v>
+      </c>
+      <c r="I746">
+        <v>1</v>
+      </c>
+      <c r="J746" t="s">
+        <v>153</v>
+      </c>
+      <c r="K746" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="747" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A747" s="2"/>
+      <c r="B747" s="2"/>
+      <c r="C747" s="2"/>
+      <c r="D747" s="2"/>
+      <c r="E747" s="3"/>
+      <c r="F747" s="2"/>
+      <c r="G747" t="s">
+        <v>529</v>
+      </c>
+      <c r="H747" t="s">
+        <v>17</v>
+      </c>
+      <c r="I747">
+        <v>1</v>
+      </c>
+      <c r="J747" t="s">
+        <v>153</v>
+      </c>
+      <c r="K747" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="748" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A748" s="2"/>
+      <c r="B748" s="2"/>
+      <c r="C748" s="2"/>
+      <c r="D748" s="2"/>
+      <c r="E748" s="3"/>
+      <c r="F748" s="2"/>
+      <c r="G748" t="s">
+        <v>530</v>
+      </c>
+      <c r="H748" t="s">
+        <v>17</v>
+      </c>
+      <c r="I748">
+        <v>1</v>
+      </c>
+      <c r="J748" t="s">
+        <v>153</v>
+      </c>
+      <c r="K748" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="749" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A749" s="2"/>
+      <c r="B749" s="2"/>
+      <c r="C749" s="2"/>
+      <c r="D749" s="2"/>
+      <c r="E749" s="3"/>
+      <c r="F749" s="2"/>
+      <c r="G749" t="s">
+        <v>531</v>
+      </c>
+      <c r="H749" t="s">
+        <v>55</v>
+      </c>
+      <c r="I749">
+        <v>4</v>
+      </c>
+      <c r="J749" t="s">
+        <v>153</v>
+      </c>
+      <c r="K749" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="750" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A750" s="2"/>
+      <c r="B750" s="2"/>
+      <c r="C750" s="2"/>
+      <c r="D750" s="2"/>
+      <c r="E750" s="3"/>
+      <c r="F750" s="2"/>
+      <c r="G750" t="s">
+        <v>532</v>
+      </c>
+      <c r="H750" t="s">
+        <v>55</v>
+      </c>
+      <c r="I750">
+        <v>4</v>
+      </c>
+      <c r="J750" t="s">
+        <v>153</v>
+      </c>
+      <c r="K750" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="751" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A751" s="2"/>
+      <c r="B751" s="2"/>
+      <c r="C751" s="2"/>
+      <c r="D751" s="2"/>
+      <c r="E751" s="3"/>
+      <c r="F751" s="2"/>
+      <c r="G751" t="s">
+        <v>533</v>
+      </c>
+      <c r="H751" t="s">
+        <v>55</v>
+      </c>
+      <c r="I751">
+        <v>2</v>
+      </c>
+      <c r="J751" t="s">
+        <v>153</v>
+      </c>
+      <c r="K751" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="753" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A753" s="2">
+        <v>40</v>
+      </c>
+      <c r="B753" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="C753" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D753" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E753" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F753" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="G753" t="s">
+        <v>536</v>
+      </c>
+      <c r="H753" t="s">
+        <v>55</v>
+      </c>
+      <c r="I753">
+        <v>2</v>
+      </c>
+      <c r="J753" t="s">
+        <v>153</v>
+      </c>
+      <c r="K753" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="754" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A754" s="2"/>
+      <c r="B754" s="2"/>
+      <c r="C754" s="2"/>
+      <c r="D754" s="2"/>
+      <c r="E754" s="3"/>
+      <c r="F754" s="2"/>
+      <c r="G754" t="s">
+        <v>96</v>
+      </c>
+      <c r="H754" t="s">
+        <v>55</v>
+      </c>
+      <c r="I754">
+        <v>2</v>
+      </c>
+      <c r="J754" t="s">
+        <v>153</v>
+      </c>
+      <c r="K754" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="755" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A755" s="2"/>
+      <c r="B755" s="2"/>
+      <c r="C755" s="2"/>
+      <c r="D755" s="2"/>
+      <c r="E755" s="3"/>
+      <c r="F755" s="2"/>
+      <c r="G755" t="s">
+        <v>537</v>
+      </c>
+      <c r="H755" t="s">
+        <v>17</v>
+      </c>
+      <c r="I755">
+        <v>1</v>
+      </c>
+      <c r="J755" t="s">
+        <v>153</v>
+      </c>
+      <c r="K755" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="756" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A756" s="2"/>
+      <c r="B756" s="2"/>
+      <c r="C756" s="2"/>
+      <c r="D756" s="2"/>
+      <c r="E756" s="3"/>
+      <c r="F756" s="2"/>
+      <c r="G756" t="s">
+        <v>448</v>
+      </c>
+      <c r="H756" t="s">
+        <v>17</v>
+      </c>
+      <c r="I756">
+        <v>1</v>
+      </c>
+      <c r="J756" t="s">
+        <v>153</v>
+      </c>
+      <c r="K756" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="757" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A757" s="2"/>
+      <c r="B757" s="2"/>
+      <c r="C757" s="2"/>
+      <c r="D757" s="2"/>
+      <c r="E757" s="3"/>
+      <c r="F757" s="2"/>
+      <c r="G757" t="s">
+        <v>97</v>
+      </c>
+      <c r="H757" t="s">
+        <v>17</v>
+      </c>
+      <c r="I757">
+        <v>1</v>
+      </c>
+      <c r="J757" t="s">
+        <v>153</v>
+      </c>
+      <c r="K757" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="758" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A758" s="2"/>
+      <c r="B758" s="2"/>
+      <c r="C758" s="2"/>
+      <c r="D758" s="2"/>
+      <c r="E758" s="3"/>
+      <c r="F758" s="2"/>
+      <c r="G758" t="s">
+        <v>444</v>
+      </c>
+      <c r="H758" t="s">
+        <v>55</v>
+      </c>
+      <c r="I758">
+        <v>2</v>
+      </c>
+      <c r="J758" t="s">
+        <v>153</v>
+      </c>
+      <c r="K758" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="759" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A759" s="2"/>
+      <c r="B759" s="2"/>
+      <c r="C759" s="2"/>
+      <c r="D759" s="2"/>
+      <c r="E759" s="3"/>
+      <c r="F759" s="2"/>
+      <c r="G759" t="s">
+        <v>53</v>
+      </c>
+      <c r="H759" t="s">
+        <v>17</v>
+      </c>
+      <c r="I759">
+        <v>1</v>
+      </c>
+      <c r="J759" t="s">
+        <v>153</v>
+      </c>
+      <c r="K759" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="760" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A760" s="2"/>
+      <c r="B760" s="2"/>
+      <c r="C760" s="2"/>
+      <c r="D760" s="2"/>
+      <c r="E760" s="3"/>
+      <c r="F760" s="2"/>
+      <c r="G760" t="s">
+        <v>156</v>
+      </c>
+      <c r="H760" t="s">
+        <v>55</v>
+      </c>
+      <c r="I760">
+        <v>2</v>
+      </c>
+      <c r="J760" t="s">
+        <v>153</v>
+      </c>
+      <c r="K760" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="761" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A761" s="2"/>
+      <c r="B761" s="2"/>
+      <c r="C761" s="2"/>
+      <c r="D761" s="2"/>
+      <c r="E761" s="3"/>
+      <c r="F761" s="2"/>
+      <c r="G761" t="s">
+        <v>152</v>
+      </c>
+      <c r="H761" t="s">
+        <v>17</v>
+      </c>
+      <c r="I761">
+        <v>1</v>
+      </c>
+      <c r="J761" t="s">
+        <v>153</v>
+      </c>
+      <c r="K761" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="762" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A762" s="2"/>
+      <c r="B762" s="2"/>
+      <c r="C762" s="2"/>
+      <c r="D762" s="2"/>
+      <c r="E762" s="3"/>
+      <c r="F762" s="2"/>
+      <c r="G762" t="s">
+        <v>134</v>
+      </c>
+      <c r="H762" t="s">
+        <v>55</v>
+      </c>
+      <c r="I762">
+        <v>1</v>
+      </c>
+      <c r="J762" t="s">
+        <v>153</v>
+      </c>
+      <c r="K762" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="763" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A763" s="2"/>
+      <c r="B763" s="2"/>
+      <c r="C763" s="2"/>
+      <c r="D763" s="2"/>
+      <c r="E763" s="3"/>
+      <c r="F763" s="2"/>
+      <c r="G763" t="s">
+        <v>440</v>
+      </c>
+      <c r="H763" t="s">
+        <v>55</v>
+      </c>
+      <c r="I763">
+        <v>1</v>
+      </c>
+      <c r="J763" t="s">
+        <v>153</v>
+      </c>
+      <c r="K763" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="764" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A764" s="2"/>
+      <c r="B764" s="2"/>
+      <c r="C764" s="2"/>
+      <c r="D764" s="2"/>
+      <c r="E764" s="3"/>
+      <c r="F764" s="2"/>
+      <c r="G764" t="s">
+        <v>113</v>
+      </c>
+      <c r="H764" t="s">
+        <v>55</v>
+      </c>
+      <c r="I764">
+        <v>2</v>
+      </c>
+      <c r="J764" t="s">
+        <v>153</v>
+      </c>
+      <c r="K764" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="765" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A765" s="2"/>
+      <c r="B765" s="2"/>
+      <c r="C765" s="2"/>
+      <c r="D765" s="2"/>
+      <c r="E765" s="3"/>
+      <c r="F765" s="2"/>
+      <c r="G765" t="s">
+        <v>148</v>
+      </c>
+      <c r="H765" t="s">
+        <v>17</v>
+      </c>
+      <c r="I765">
+        <v>1</v>
+      </c>
+      <c r="J765" t="s">
+        <v>153</v>
+      </c>
+      <c r="K765" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="766" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A766" s="2"/>
+      <c r="B766" s="2"/>
+      <c r="C766" s="2"/>
+      <c r="D766" s="2"/>
+      <c r="E766" s="3"/>
+      <c r="F766" s="2"/>
+      <c r="G766" t="s">
+        <v>112</v>
+      </c>
+      <c r="H766" t="s">
+        <v>55</v>
+      </c>
+      <c r="I766">
+        <v>1</v>
+      </c>
+      <c r="J766" t="s">
+        <v>153</v>
+      </c>
+      <c r="K766" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="767" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A767" s="2"/>
+      <c r="B767" s="2"/>
+      <c r="C767" s="2"/>
+      <c r="D767" s="2"/>
+      <c r="E767" s="3"/>
+      <c r="F767" s="2"/>
+      <c r="G767" t="s">
+        <v>105</v>
+      </c>
+      <c r="H767" t="s">
+        <v>17</v>
+      </c>
+      <c r="I767">
+        <v>2</v>
+      </c>
+      <c r="J767" t="s">
+        <v>153</v>
+      </c>
+      <c r="K767" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="768" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A768" s="2"/>
+      <c r="B768" s="2"/>
+      <c r="C768" s="2"/>
+      <c r="D768" s="2"/>
+      <c r="E768" s="3"/>
+      <c r="F768" s="2"/>
+      <c r="G768" t="s">
+        <v>222</v>
+      </c>
+      <c r="H768" t="s">
+        <v>76</v>
+      </c>
+      <c r="I768">
+        <v>1</v>
+      </c>
+      <c r="J768" t="s">
+        <v>153</v>
+      </c>
+      <c r="K768" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="769" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A769" s="2"/>
+      <c r="B769" s="2"/>
+      <c r="C769" s="2"/>
+      <c r="D769" s="2"/>
+      <c r="E769" s="3"/>
+      <c r="F769" s="2"/>
+      <c r="G769" t="s">
+        <v>105</v>
+      </c>
+      <c r="H769" t="s">
+        <v>17</v>
+      </c>
+      <c r="I769">
+        <v>2</v>
+      </c>
+      <c r="J769" t="s">
+        <v>153</v>
+      </c>
+      <c r="K769" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="771" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A771" s="2">
+        <v>41</v>
+      </c>
+      <c r="B771" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C771" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D771" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E771" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F771" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="G771" t="s">
+        <v>222</v>
+      </c>
+      <c r="H771" t="s">
+        <v>76</v>
+      </c>
+      <c r="I771">
+        <v>10</v>
+      </c>
+      <c r="J771" t="s">
+        <v>153</v>
+      </c>
+      <c r="K771" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="772" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A772" s="2"/>
+      <c r="B772" s="2"/>
+      <c r="C772" s="2"/>
+      <c r="D772" s="2"/>
+      <c r="E772" s="3"/>
+      <c r="F772" s="2"/>
+      <c r="G772" t="s">
+        <v>540</v>
+      </c>
+      <c r="H772" t="s">
+        <v>17</v>
+      </c>
+      <c r="I772">
+        <v>2</v>
+      </c>
+      <c r="J772" t="s">
+        <v>153</v>
+      </c>
+      <c r="K772" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="773" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A773" s="2"/>
+      <c r="B773" s="2"/>
+      <c r="C773" s="2"/>
+      <c r="D773" s="2"/>
+      <c r="E773" s="3"/>
+      <c r="F773" s="2"/>
+      <c r="G773" t="s">
+        <v>541</v>
+      </c>
+      <c r="H773" t="s">
+        <v>17</v>
+      </c>
+      <c r="I773">
+        <v>2</v>
+      </c>
+      <c r="J773" t="s">
+        <v>153</v>
+      </c>
+      <c r="K773" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="774" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A774" s="2"/>
+      <c r="B774" s="2"/>
+      <c r="C774" s="2"/>
+      <c r="D774" s="2"/>
+      <c r="E774" s="3"/>
+      <c r="F774" s="2"/>
+      <c r="G774" t="s">
+        <v>508</v>
+      </c>
+      <c r="H774" t="s">
+        <v>17</v>
+      </c>
+      <c r="I774">
+        <v>2</v>
+      </c>
+      <c r="J774" t="s">
+        <v>153</v>
+      </c>
+      <c r="K774" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="775" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A775" s="2"/>
+      <c r="B775" s="2"/>
+      <c r="C775" s="2"/>
+      <c r="D775" s="2"/>
+      <c r="E775" s="3"/>
+      <c r="F775" s="2"/>
+      <c r="G775" t="s">
+        <v>505</v>
+      </c>
+      <c r="H775" t="s">
+        <v>17</v>
+      </c>
+      <c r="I775">
+        <v>1</v>
+      </c>
+      <c r="J775" t="s">
+        <v>153</v>
+      </c>
+      <c r="K775" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="776" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A776" s="2"/>
+      <c r="B776" s="2"/>
+      <c r="C776" s="2"/>
+      <c r="D776" s="2"/>
+      <c r="E776" s="3"/>
+      <c r="F776" s="2"/>
+      <c r="G776" t="s">
+        <v>210</v>
+      </c>
+      <c r="H776" t="s">
+        <v>17</v>
+      </c>
+      <c r="I776">
+        <v>3</v>
+      </c>
+      <c r="J776" t="s">
+        <v>153</v>
+      </c>
+      <c r="K776" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="777" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A777" s="2"/>
+      <c r="B777" s="2"/>
+      <c r="C777" s="2"/>
+      <c r="D777" s="2"/>
+      <c r="E777" s="3"/>
+      <c r="F777" s="2"/>
+      <c r="G777" t="s">
+        <v>280</v>
+      </c>
+      <c r="H777" t="s">
+        <v>17</v>
+      </c>
+      <c r="I777">
+        <v>2</v>
+      </c>
+      <c r="J777" t="s">
+        <v>153</v>
+      </c>
+      <c r="K777" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="778" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A778" s="2"/>
+      <c r="B778" s="2"/>
+      <c r="C778" s="2"/>
+      <c r="D778" s="2"/>
+      <c r="E778" s="3"/>
+      <c r="F778" s="2"/>
+      <c r="G778" t="s">
+        <v>507</v>
+      </c>
+      <c r="H778" t="s">
+        <v>17</v>
+      </c>
+      <c r="I778">
+        <v>2</v>
+      </c>
+      <c r="J778" t="s">
+        <v>153</v>
+      </c>
+      <c r="K778" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="779" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A779" s="2"/>
+      <c r="B779" s="2"/>
+      <c r="C779" s="2"/>
+      <c r="D779" s="2"/>
+      <c r="E779" s="3"/>
+      <c r="F779" s="2"/>
+      <c r="G779" t="s">
+        <v>542</v>
+      </c>
+      <c r="H779" t="s">
+        <v>17</v>
+      </c>
+      <c r="I779">
+        <v>2</v>
+      </c>
+      <c r="J779" t="s">
+        <v>153</v>
+      </c>
+      <c r="K779" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="780" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A780" s="2"/>
+      <c r="B780" s="2"/>
+      <c r="C780" s="2"/>
+      <c r="D780" s="2"/>
+      <c r="E780" s="3"/>
+      <c r="F780" s="2"/>
+      <c r="G780" t="s">
+        <v>104</v>
+      </c>
+      <c r="H780" t="s">
+        <v>17</v>
+      </c>
+      <c r="I780">
+        <v>2</v>
+      </c>
+      <c r="J780" t="s">
+        <v>153</v>
+      </c>
+      <c r="K780" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="781" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A781" s="2"/>
+      <c r="B781" s="2"/>
+      <c r="C781" s="2"/>
+      <c r="D781" s="2"/>
+      <c r="E781" s="3"/>
+      <c r="F781" s="2"/>
+      <c r="G781" t="s">
+        <v>290</v>
+      </c>
+      <c r="H781" t="s">
+        <v>17</v>
+      </c>
+      <c r="I781">
+        <v>2</v>
+      </c>
+      <c r="J781" t="s">
+        <v>153</v>
+      </c>
+      <c r="K781" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="782" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A782" s="2"/>
+      <c r="B782" s="2"/>
+      <c r="C782" s="2"/>
+      <c r="D782" s="2"/>
+      <c r="E782" s="3"/>
+      <c r="F782" s="2"/>
+      <c r="G782" t="s">
+        <v>543</v>
+      </c>
+      <c r="H782" t="s">
+        <v>17</v>
+      </c>
+      <c r="I782">
+        <v>2</v>
+      </c>
+      <c r="J782" t="s">
+        <v>153</v>
+      </c>
+      <c r="K782" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="783" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A783" s="2"/>
+      <c r="B783" s="2"/>
+      <c r="C783" s="2"/>
+      <c r="D783" s="2"/>
+      <c r="E783" s="3"/>
+      <c r="F783" s="2"/>
+      <c r="G783" t="s">
+        <v>337</v>
+      </c>
+      <c r="H783" t="s">
+        <v>17</v>
+      </c>
+      <c r="I783">
+        <v>2</v>
+      </c>
+      <c r="J783" t="s">
+        <v>153</v>
+      </c>
+      <c r="K783" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="784" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A784" s="2"/>
+      <c r="B784" s="2"/>
+      <c r="C784" s="2"/>
+      <c r="D784" s="2"/>
+      <c r="E784" s="3"/>
+      <c r="F784" s="2"/>
+      <c r="G784" t="s">
+        <v>144</v>
+      </c>
+      <c r="H784" t="s">
+        <v>17</v>
+      </c>
+      <c r="I784">
+        <v>2</v>
+      </c>
+      <c r="J784" t="s">
+        <v>153</v>
+      </c>
+      <c r="K784" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="786" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A786" s="2">
+        <v>42</v>
+      </c>
+      <c r="B786" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="C786" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D786" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E786" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F786" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="G786" t="s">
+        <v>327</v>
+      </c>
+      <c r="H786" t="s">
+        <v>17</v>
+      </c>
+      <c r="I786">
+        <v>6</v>
+      </c>
+      <c r="J786" t="s">
+        <v>153</v>
+      </c>
+      <c r="K786" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="787" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A787" s="2"/>
+      <c r="B787" s="2"/>
+      <c r="C787" s="2"/>
+      <c r="D787" s="2"/>
+      <c r="E787" s="3"/>
+      <c r="F787" s="2"/>
+      <c r="G787" t="s">
+        <v>63</v>
+      </c>
+      <c r="H787" t="s">
+        <v>17</v>
+      </c>
+      <c r="I787">
+        <v>5</v>
+      </c>
+      <c r="J787" t="s">
+        <v>153</v>
+      </c>
+      <c r="K787" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="788" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A788" s="2"/>
+      <c r="B788" s="2"/>
+      <c r="C788" s="2"/>
+      <c r="D788" s="2"/>
+      <c r="E788" s="3"/>
+      <c r="F788" s="2"/>
+      <c r="G788" t="s">
+        <v>354</v>
+      </c>
+      <c r="H788" t="s">
+        <v>17</v>
+      </c>
+      <c r="I788">
+        <v>2</v>
+      </c>
+      <c r="J788" t="s">
+        <v>153</v>
+      </c>
+      <c r="K788" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="789" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A789" s="2"/>
+      <c r="B789" s="2"/>
+      <c r="C789" s="2"/>
+      <c r="D789" s="2"/>
+      <c r="E789" s="3"/>
+      <c r="F789" s="2"/>
+      <c r="G789" t="s">
+        <v>545</v>
+      </c>
+      <c r="H789" t="s">
+        <v>17</v>
+      </c>
+      <c r="I789">
+        <v>2</v>
+      </c>
+      <c r="J789" t="s">
+        <v>153</v>
+      </c>
+      <c r="K789" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="790" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A790" s="2"/>
+      <c r="B790" s="2"/>
+      <c r="C790" s="2"/>
+      <c r="D790" s="2"/>
+      <c r="E790" s="3"/>
+      <c r="F790" s="2"/>
+      <c r="G790" t="s">
+        <v>329</v>
+      </c>
+      <c r="H790" t="s">
+        <v>17</v>
+      </c>
+      <c r="I790">
+        <v>4</v>
+      </c>
+      <c r="J790" t="s">
+        <v>153</v>
+      </c>
+      <c r="K790" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="791" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A791" s="2"/>
+      <c r="B791" s="2"/>
+      <c r="C791" s="2"/>
+      <c r="D791" s="2"/>
+      <c r="E791" s="3"/>
+      <c r="F791" s="2"/>
+      <c r="G791" t="s">
+        <v>16</v>
+      </c>
+      <c r="H791" t="s">
+        <v>17</v>
+      </c>
+      <c r="I791">
+        <v>1</v>
+      </c>
+      <c r="J791" t="s">
+        <v>153</v>
+      </c>
+      <c r="K791" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="793" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A793" s="2">
+        <v>43</v>
+      </c>
+      <c r="B793" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C793" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D793" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E793" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F793" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="G793" t="s">
+        <v>222</v>
+      </c>
+      <c r="H793" t="s">
+        <v>76</v>
+      </c>
+      <c r="I793">
+        <v>15</v>
+      </c>
+      <c r="J793" t="s">
+        <v>153</v>
+      </c>
+      <c r="K793" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="794" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A794" s="2"/>
+      <c r="B794" s="2"/>
+      <c r="C794" s="2"/>
+      <c r="D794" s="2"/>
+      <c r="E794" s="3"/>
+      <c r="F794" s="2"/>
+      <c r="G794" t="s">
+        <v>548</v>
+      </c>
+      <c r="H794" t="s">
+        <v>76</v>
+      </c>
+      <c r="I794">
+        <v>1</v>
+      </c>
+      <c r="J794" t="s">
+        <v>153</v>
+      </c>
+      <c r="K794" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="795" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A795" s="2"/>
+      <c r="B795" s="2"/>
+      <c r="C795" s="2"/>
+      <c r="D795" s="2"/>
+      <c r="E795" s="3"/>
+      <c r="F795" s="2"/>
+      <c r="G795" t="s">
+        <v>549</v>
+      </c>
+      <c r="H795" t="s">
+        <v>17</v>
+      </c>
+      <c r="I795">
+        <v>4</v>
+      </c>
+      <c r="J795" t="s">
+        <v>153</v>
+      </c>
+      <c r="K795" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="796" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A796" s="2"/>
+      <c r="B796" s="2"/>
+      <c r="C796" s="2"/>
+      <c r="D796" s="2"/>
+      <c r="E796" s="3"/>
+      <c r="F796" s="2"/>
+      <c r="G796" t="s">
+        <v>131</v>
+      </c>
+      <c r="H796" t="s">
+        <v>17</v>
+      </c>
+      <c r="I796">
+        <v>2</v>
+      </c>
+      <c r="J796" t="s">
+        <v>153</v>
+      </c>
+      <c r="K796" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="797" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A797" s="2"/>
+      <c r="B797" s="2"/>
+      <c r="C797" s="2"/>
+      <c r="D797" s="2"/>
+      <c r="E797" s="3"/>
+      <c r="F797" s="2"/>
+      <c r="G797" t="s">
+        <v>293</v>
+      </c>
+      <c r="H797" t="s">
+        <v>17</v>
+      </c>
+      <c r="I797">
+        <v>2</v>
+      </c>
+      <c r="J797" t="s">
+        <v>153</v>
+      </c>
+      <c r="K797" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="798" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A798" s="2"/>
+      <c r="B798" s="2"/>
+      <c r="C798" s="2"/>
+      <c r="D798" s="2"/>
+      <c r="E798" s="3"/>
+      <c r="F798" s="2"/>
+      <c r="G798" t="s">
+        <v>102</v>
+      </c>
+      <c r="H798" t="s">
+        <v>17</v>
+      </c>
+      <c r="I798">
+        <v>2</v>
+      </c>
+      <c r="J798" t="s">
+        <v>153</v>
+      </c>
+      <c r="K798" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="799" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A799" s="2"/>
+      <c r="B799" s="2"/>
+      <c r="C799" s="2"/>
+      <c r="D799" s="2"/>
+      <c r="E799" s="3"/>
+      <c r="F799" s="2"/>
+      <c r="G799" t="s">
+        <v>448</v>
+      </c>
+      <c r="H799" t="s">
+        <v>17</v>
+      </c>
+      <c r="I799">
+        <v>2</v>
+      </c>
+      <c r="J799" t="s">
+        <v>153</v>
+      </c>
+      <c r="K799" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="800" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A800" s="2"/>
+      <c r="B800" s="2"/>
+      <c r="C800" s="2"/>
+      <c r="D800" s="2"/>
+      <c r="E800" s="3"/>
+      <c r="F800" s="2"/>
+      <c r="G800" t="s">
+        <v>294</v>
+      </c>
+      <c r="H800" t="s">
+        <v>17</v>
+      </c>
+      <c r="I800">
+        <v>3</v>
+      </c>
+      <c r="J800" t="s">
+        <v>153</v>
+      </c>
+      <c r="K800" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="801" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A801" s="2"/>
+      <c r="B801" s="2"/>
+      <c r="C801" s="2"/>
+      <c r="D801" s="2"/>
+      <c r="E801" s="3"/>
+      <c r="F801" s="2"/>
+      <c r="G801" t="s">
+        <v>454</v>
+      </c>
+      <c r="H801" t="s">
+        <v>17</v>
+      </c>
+      <c r="I801">
+        <v>2</v>
+      </c>
+      <c r="J801" t="s">
+        <v>153</v>
+      </c>
+      <c r="K801" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="802" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A802" s="2"/>
+      <c r="B802" s="2"/>
+      <c r="C802" s="2"/>
+      <c r="D802" s="2"/>
+      <c r="E802" s="3"/>
+      <c r="F802" s="2"/>
+      <c r="G802" t="s">
+        <v>550</v>
+      </c>
+      <c r="H802" t="s">
+        <v>17</v>
+      </c>
+      <c r="I802">
+        <v>2</v>
+      </c>
+      <c r="J802" t="s">
+        <v>153</v>
+      </c>
+      <c r="K802" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="803" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A803" s="2"/>
+      <c r="B803" s="2"/>
+      <c r="C803" s="2"/>
+      <c r="D803" s="2"/>
+      <c r="E803" s="3"/>
+      <c r="F803" s="2"/>
+      <c r="G803" t="s">
+        <v>551</v>
+      </c>
+      <c r="H803" t="s">
+        <v>76</v>
+      </c>
+      <c r="I803">
+        <v>2</v>
+      </c>
+      <c r="J803" t="s">
+        <v>153</v>
+      </c>
+      <c r="K803" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="804" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A804" s="2"/>
+      <c r="B804" s="2"/>
+      <c r="C804" s="2"/>
+      <c r="D804" s="2"/>
+      <c r="E804" s="3"/>
+      <c r="F804" s="2"/>
+      <c r="G804" t="s">
+        <v>393</v>
+      </c>
+      <c r="H804" t="s">
+        <v>17</v>
+      </c>
+      <c r="I804">
+        <v>2</v>
+      </c>
+      <c r="J804" t="s">
+        <v>153</v>
+      </c>
+      <c r="K804" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="806" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A806" s="2">
+        <v>44</v>
+      </c>
+      <c r="B806" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C806" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D806" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E806" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F806" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="G806" t="s">
+        <v>554</v>
+      </c>
+      <c r="H806" t="s">
+        <v>17</v>
+      </c>
+      <c r="I806">
+        <v>4</v>
+      </c>
+      <c r="J806" t="s">
+        <v>153</v>
+      </c>
+      <c r="K806" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="807" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A807" s="2"/>
+      <c r="B807" s="2"/>
+      <c r="C807" s="2"/>
+      <c r="D807" s="2"/>
+      <c r="E807" s="3"/>
+      <c r="F807" s="2"/>
+      <c r="G807" t="s">
+        <v>555</v>
+      </c>
+      <c r="H807" t="s">
+        <v>17</v>
+      </c>
+      <c r="I807">
+        <v>2</v>
+      </c>
+      <c r="J807" t="s">
+        <v>153</v>
+      </c>
+      <c r="K807" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="808" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A808" s="2"/>
+      <c r="B808" s="2"/>
+      <c r="C808" s="2"/>
+      <c r="D808" s="2"/>
+      <c r="E808" s="3"/>
+      <c r="F808" s="2"/>
+      <c r="G808" t="s">
+        <v>556</v>
+      </c>
+      <c r="H808" t="s">
+        <v>17</v>
+      </c>
+      <c r="I808">
+        <v>2</v>
+      </c>
+      <c r="J808" t="s">
+        <v>153</v>
+      </c>
+      <c r="K808" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="809" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A809" s="2"/>
+      <c r="B809" s="2"/>
+      <c r="C809" s="2"/>
+      <c r="D809" s="2"/>
+      <c r="E809" s="3"/>
+      <c r="F809" s="2"/>
+      <c r="G809" t="s">
+        <v>557</v>
+      </c>
+      <c r="H809" t="s">
+        <v>17</v>
+      </c>
+      <c r="I809">
+        <v>4</v>
+      </c>
+      <c r="J809" t="s">
+        <v>153</v>
+      </c>
+      <c r="K809" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="810" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A810" s="2"/>
+      <c r="B810" s="2"/>
+      <c r="C810" s="2"/>
+      <c r="D810" s="2"/>
+      <c r="E810" s="3"/>
+      <c r="F810" s="2"/>
+      <c r="G810" t="s">
+        <v>558</v>
+      </c>
+      <c r="H810" t="s">
+        <v>17</v>
+      </c>
+      <c r="I810">
+        <v>4</v>
+      </c>
+      <c r="J810" t="s">
+        <v>153</v>
+      </c>
+      <c r="K810" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="811" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A811" s="2"/>
+      <c r="B811" s="2"/>
+      <c r="C811" s="2"/>
+      <c r="D811" s="2"/>
+      <c r="E811" s="3"/>
+      <c r="F811" s="2"/>
+      <c r="G811" t="s">
+        <v>559</v>
+      </c>
+      <c r="H811" t="s">
+        <v>17</v>
+      </c>
+      <c r="I811">
+        <v>5</v>
+      </c>
+      <c r="J811" t="s">
+        <v>153</v>
+      </c>
+      <c r="K811" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="812" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A812" s="2"/>
+      <c r="B812" s="2"/>
+      <c r="C812" s="2"/>
+      <c r="D812" s="2"/>
+      <c r="E812" s="3"/>
+      <c r="F812" s="2"/>
+      <c r="G812" t="s">
+        <v>560</v>
+      </c>
+      <c r="H812" t="s">
+        <v>17</v>
+      </c>
+      <c r="I812">
+        <v>3</v>
+      </c>
+      <c r="J812" t="s">
+        <v>153</v>
+      </c>
+      <c r="K812" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="813" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A813" s="2"/>
+      <c r="B813" s="2"/>
+      <c r="C813" s="2"/>
+      <c r="D813" s="2"/>
+      <c r="E813" s="3"/>
+      <c r="F813" s="2"/>
+      <c r="G813" t="s">
+        <v>561</v>
+      </c>
+      <c r="H813" t="s">
+        <v>17</v>
+      </c>
+      <c r="I813">
+        <v>2</v>
+      </c>
+      <c r="J813" t="s">
+        <v>153</v>
+      </c>
+      <c r="K813" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="814" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A814" s="2"/>
+      <c r="B814" s="2"/>
+      <c r="C814" s="2"/>
+      <c r="D814" s="2"/>
+      <c r="E814" s="3"/>
+      <c r="F814" s="2"/>
+      <c r="G814" t="s">
+        <v>562</v>
+      </c>
+      <c r="H814" t="s">
+        <v>17</v>
+      </c>
+      <c r="I814">
+        <v>4</v>
+      </c>
+      <c r="J814" t="s">
+        <v>153</v>
+      </c>
+      <c r="K814" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="815" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A815" s="2"/>
+      <c r="B815" s="2"/>
+      <c r="C815" s="2"/>
+      <c r="D815" s="2"/>
+      <c r="E815" s="3"/>
+      <c r="F815" s="2"/>
+      <c r="G815" t="s">
+        <v>563</v>
+      </c>
+      <c r="H815" t="s">
+        <v>17</v>
+      </c>
+      <c r="I815">
+        <v>4</v>
+      </c>
+      <c r="J815" t="s">
+        <v>153</v>
+      </c>
+      <c r="K815" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="816" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A816" s="2"/>
+      <c r="B816" s="2"/>
+      <c r="C816" s="2"/>
+      <c r="D816" s="2"/>
+      <c r="E816" s="3"/>
+      <c r="F816" s="2"/>
+      <c r="G816" t="s">
+        <v>564</v>
+      </c>
+      <c r="H816" t="s">
+        <v>17</v>
+      </c>
+      <c r="I816">
+        <v>2</v>
+      </c>
+      <c r="J816" t="s">
+        <v>153</v>
+      </c>
+      <c r="K816" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="817" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A817" s="2"/>
+      <c r="B817" s="2"/>
+      <c r="C817" s="2"/>
+      <c r="D817" s="2"/>
+      <c r="E817" s="3"/>
+      <c r="F817" s="2"/>
+      <c r="G817" t="s">
+        <v>565</v>
+      </c>
+      <c r="H817" t="s">
+        <v>17</v>
+      </c>
+      <c r="I817">
+        <v>2</v>
+      </c>
+      <c r="J817" t="s">
+        <v>153</v>
+      </c>
+      <c r="K817" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="818" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A818" s="2"/>
+      <c r="B818" s="2"/>
+      <c r="C818" s="2"/>
+      <c r="D818" s="2"/>
+      <c r="E818" s="3"/>
+      <c r="F818" s="2"/>
+      <c r="G818" t="s">
+        <v>566</v>
+      </c>
+      <c r="H818" t="s">
+        <v>55</v>
+      </c>
+      <c r="I818">
+        <v>4</v>
+      </c>
+      <c r="J818" t="s">
+        <v>153</v>
+      </c>
+      <c r="K818" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="819" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A819" s="2"/>
+      <c r="B819" s="2"/>
+      <c r="C819" s="2"/>
+      <c r="D819" s="2"/>
+      <c r="E819" s="3"/>
+      <c r="F819" s="2"/>
+      <c r="G819" t="s">
+        <v>567</v>
+      </c>
+      <c r="H819" t="s">
+        <v>17</v>
+      </c>
+      <c r="I819">
+        <v>2</v>
+      </c>
+      <c r="J819" t="s">
+        <v>153</v>
+      </c>
+      <c r="K819" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="820" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A820" s="2"/>
+      <c r="B820" s="2"/>
+      <c r="C820" s="2"/>
+      <c r="D820" s="2"/>
+      <c r="E820" s="3"/>
+      <c r="F820" s="2"/>
+      <c r="G820" t="s">
+        <v>568</v>
+      </c>
+      <c r="H820" t="s">
+        <v>17</v>
+      </c>
+      <c r="I820">
+        <v>5</v>
+      </c>
+      <c r="J820" t="s">
+        <v>153</v>
+      </c>
+      <c r="K820" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="821" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A821" s="2"/>
+      <c r="B821" s="2"/>
+      <c r="C821" s="2"/>
+      <c r="D821" s="2"/>
+      <c r="E821" s="3"/>
+      <c r="F821" s="2"/>
+      <c r="G821" t="s">
+        <v>569</v>
+      </c>
+      <c r="H821" t="s">
+        <v>55</v>
+      </c>
+      <c r="I821">
+        <v>2</v>
+      </c>
+      <c r="J821" t="s">
+        <v>153</v>
+      </c>
+      <c r="K821" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="822" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A822" s="2"/>
+      <c r="B822" s="2"/>
+      <c r="C822" s="2"/>
+      <c r="D822" s="2"/>
+      <c r="E822" s="3"/>
+      <c r="F822" s="2"/>
+      <c r="G822" t="s">
+        <v>570</v>
+      </c>
+      <c r="H822" t="s">
+        <v>17</v>
+      </c>
+      <c r="I822">
+        <v>6</v>
+      </c>
+      <c r="J822" t="s">
+        <v>153</v>
+      </c>
+      <c r="K822" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="823" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A823" s="2"/>
+      <c r="B823" s="2"/>
+      <c r="C823" s="2"/>
+      <c r="D823" s="2"/>
+      <c r="E823" s="3"/>
+      <c r="F823" s="2"/>
+      <c r="G823" t="s">
+        <v>571</v>
+      </c>
+      <c r="H823" t="s">
+        <v>55</v>
+      </c>
+      <c r="I823">
+        <v>4</v>
+      </c>
+      <c r="J823" t="s">
+        <v>153</v>
+      </c>
+      <c r="K823" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="824" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A824" s="2"/>
+      <c r="B824" s="2"/>
+      <c r="C824" s="2"/>
+      <c r="D824" s="2"/>
+      <c r="E824" s="3"/>
+      <c r="F824" s="2"/>
+      <c r="G824" t="s">
+        <v>572</v>
+      </c>
+      <c r="H824" t="s">
+        <v>17</v>
+      </c>
+      <c r="I824">
+        <v>4</v>
+      </c>
+      <c r="J824" t="s">
+        <v>153</v>
+      </c>
+      <c r="K824" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="825" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A825" s="2"/>
+      <c r="B825" s="2"/>
+      <c r="C825" s="2"/>
+      <c r="D825" s="2"/>
+      <c r="E825" s="3"/>
+      <c r="F825" s="2"/>
+      <c r="G825" t="s">
+        <v>573</v>
+      </c>
+      <c r="H825" t="s">
+        <v>17</v>
+      </c>
+      <c r="I825">
+        <v>2</v>
+      </c>
+      <c r="J825" t="s">
+        <v>153</v>
+      </c>
+      <c r="K825" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="826" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A826" s="2"/>
+      <c r="B826" s="2"/>
+      <c r="C826" s="2"/>
+      <c r="D826" s="2"/>
+      <c r="E826" s="3"/>
+      <c r="F826" s="2"/>
+      <c r="G826" t="s">
+        <v>574</v>
+      </c>
+      <c r="H826" t="s">
+        <v>55</v>
+      </c>
+      <c r="I826">
+        <v>2</v>
+      </c>
+      <c r="J826" t="s">
+        <v>153</v>
+      </c>
+      <c r="K826" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="827" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A827" s="2"/>
+      <c r="B827" s="2"/>
+      <c r="C827" s="2"/>
+      <c r="D827" s="2"/>
+      <c r="E827" s="3"/>
+      <c r="F827" s="2"/>
+      <c r="G827" t="s">
+        <v>575</v>
+      </c>
+      <c r="H827" t="s">
+        <v>55</v>
+      </c>
+      <c r="I827">
+        <v>3</v>
+      </c>
+      <c r="J827" t="s">
+        <v>153</v>
+      </c>
+      <c r="K827" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="828" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A828" s="2"/>
+      <c r="B828" s="2"/>
+      <c r="C828" s="2"/>
+      <c r="D828" s="2"/>
+      <c r="E828" s="3"/>
+      <c r="F828" s="2"/>
+      <c r="G828" t="s">
+        <v>576</v>
+      </c>
+      <c r="H828" t="s">
+        <v>55</v>
+      </c>
+      <c r="I828">
+        <v>2</v>
+      </c>
+      <c r="J828" t="s">
+        <v>153</v>
+      </c>
+      <c r="K828" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="829" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A829" s="2"/>
+      <c r="B829" s="2"/>
+      <c r="C829" s="2"/>
+      <c r="D829" s="2"/>
+      <c r="E829" s="3"/>
+      <c r="F829" s="2"/>
+      <c r="G829" t="s">
+        <v>577</v>
+      </c>
+      <c r="H829" t="s">
+        <v>55</v>
+      </c>
+      <c r="I829">
+        <v>2</v>
+      </c>
+      <c r="J829" t="s">
+        <v>153</v>
+      </c>
+      <c r="K829" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="830" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A830" s="2"/>
+      <c r="B830" s="2"/>
+      <c r="C830" s="2"/>
+      <c r="D830" s="2"/>
+      <c r="E830" s="3"/>
+      <c r="F830" s="2"/>
+      <c r="G830" t="s">
+        <v>578</v>
+      </c>
+      <c r="H830" t="s">
+        <v>55</v>
+      </c>
+      <c r="I830">
+        <v>2</v>
+      </c>
+      <c r="J830" t="s">
+        <v>153</v>
+      </c>
+      <c r="K830" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="831" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A831" s="2"/>
+      <c r="B831" s="2"/>
+      <c r="C831" s="2"/>
+      <c r="D831" s="2"/>
+      <c r="E831" s="3"/>
+      <c r="F831" s="2"/>
+      <c r="G831" t="s">
+        <v>579</v>
+      </c>
+      <c r="H831" t="s">
+        <v>55</v>
+      </c>
+      <c r="I831">
+        <v>4</v>
+      </c>
+      <c r="J831" t="s">
+        <v>153</v>
+      </c>
+      <c r="K831" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="832" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A832" s="2"/>
+      <c r="B832" s="2"/>
+      <c r="C832" s="2"/>
+      <c r="D832" s="2"/>
+      <c r="E832" s="3"/>
+      <c r="F832" s="2"/>
+      <c r="G832" t="s">
+        <v>580</v>
+      </c>
+      <c r="H832" t="s">
+        <v>55</v>
+      </c>
+      <c r="I832">
+        <v>2</v>
+      </c>
+      <c r="J832" t="s">
+        <v>153</v>
+      </c>
+      <c r="K832" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="833" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A833" s="2"/>
+      <c r="B833" s="2"/>
+      <c r="C833" s="2"/>
+      <c r="D833" s="2"/>
+      <c r="E833" s="3"/>
+      <c r="F833" s="2"/>
+      <c r="G833" t="s">
+        <v>581</v>
+      </c>
+      <c r="H833" t="s">
+        <v>55</v>
+      </c>
+      <c r="I833">
+        <v>2</v>
+      </c>
+      <c r="J833" t="s">
+        <v>153</v>
+      </c>
+      <c r="K833" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="834" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A834" s="2"/>
+      <c r="B834" s="2"/>
+      <c r="C834" s="2"/>
+      <c r="D834" s="2"/>
+      <c r="E834" s="3"/>
+      <c r="F834" s="2"/>
+      <c r="G834" t="s">
+        <v>582</v>
+      </c>
+      <c r="H834" t="s">
+        <v>17</v>
+      </c>
+      <c r="I834">
+        <v>4</v>
+      </c>
+      <c r="J834" t="s">
+        <v>153</v>
+      </c>
+      <c r="K834" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="835" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A835" s="2"/>
+      <c r="B835" s="2"/>
+      <c r="C835" s="2"/>
+      <c r="D835" s="2"/>
+      <c r="E835" s="3"/>
+      <c r="F835" s="2"/>
+      <c r="G835" t="s">
+        <v>583</v>
+      </c>
+      <c r="H835" t="s">
+        <v>55</v>
+      </c>
+      <c r="I835">
+        <v>2</v>
+      </c>
+      <c r="J835" t="s">
+        <v>153</v>
+      </c>
+      <c r="K835" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="836" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A836" s="2"/>
+      <c r="B836" s="2"/>
+      <c r="C836" s="2"/>
+      <c r="D836" s="2"/>
+      <c r="E836" s="3"/>
+      <c r="F836" s="2"/>
+      <c r="G836" t="s">
+        <v>584</v>
+      </c>
+      <c r="H836" t="s">
+        <v>17</v>
+      </c>
+      <c r="I836">
+        <v>4</v>
+      </c>
+      <c r="J836" t="s">
+        <v>153</v>
+      </c>
+      <c r="K836" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="837" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A837" s="2"/>
+      <c r="B837" s="2"/>
+      <c r="C837" s="2"/>
+      <c r="D837" s="2"/>
+      <c r="E837" s="3"/>
+      <c r="F837" s="2"/>
+      <c r="G837" t="s">
+        <v>585</v>
+      </c>
+      <c r="H837" t="s">
+        <v>17</v>
+      </c>
+      <c r="I837">
+        <v>4</v>
+      </c>
+      <c r="J837" t="s">
+        <v>153</v>
+      </c>
+      <c r="K837" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="838" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A838" s="2"/>
+      <c r="B838" s="2"/>
+      <c r="C838" s="2"/>
+      <c r="D838" s="2"/>
+      <c r="E838" s="3"/>
+      <c r="F838" s="2"/>
+      <c r="G838" t="s">
+        <v>586</v>
+      </c>
+      <c r="H838" t="s">
+        <v>17</v>
+      </c>
+      <c r="I838">
+        <v>2</v>
+      </c>
+      <c r="J838" t="s">
+        <v>153</v>
+      </c>
+      <c r="K838" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="839" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A839" s="2"/>
+      <c r="B839" s="2"/>
+      <c r="C839" s="2"/>
+      <c r="D839" s="2"/>
+      <c r="E839" s="3"/>
+      <c r="F839" s="2"/>
+      <c r="G839" t="s">
+        <v>587</v>
+      </c>
+      <c r="H839" t="s">
+        <v>55</v>
+      </c>
+      <c r="I839">
+        <v>2</v>
+      </c>
+      <c r="J839" t="s">
+        <v>153</v>
+      </c>
+      <c r="K839" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="840" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A840" s="2"/>
+      <c r="B840" s="2"/>
+      <c r="C840" s="2"/>
+      <c r="D840" s="2"/>
+      <c r="E840" s="3"/>
+      <c r="F840" s="2"/>
+      <c r="G840" t="s">
+        <v>588</v>
+      </c>
+      <c r="H840" t="s">
+        <v>55</v>
+      </c>
+      <c r="I840">
+        <v>2</v>
+      </c>
+      <c r="J840" t="s">
+        <v>153</v>
+      </c>
+      <c r="K840" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="841" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A841" s="2"/>
+      <c r="B841" s="2"/>
+      <c r="C841" s="2"/>
+      <c r="D841" s="2"/>
+      <c r="E841" s="3"/>
+      <c r="F841" s="2"/>
+      <c r="G841" t="s">
+        <v>537</v>
+      </c>
+      <c r="H841" t="s">
+        <v>17</v>
+      </c>
+      <c r="I841">
+        <v>4</v>
+      </c>
+      <c r="J841" t="s">
+        <v>153</v>
+      </c>
+      <c r="K841" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="842" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A842" s="2"/>
+      <c r="B842" s="2"/>
+      <c r="C842" s="2"/>
+      <c r="D842" s="2"/>
+      <c r="E842" s="3"/>
+      <c r="F842" s="2"/>
+      <c r="G842" t="s">
+        <v>589</v>
+      </c>
+      <c r="H842" t="s">
+        <v>17</v>
+      </c>
+      <c r="I842">
+        <v>3</v>
+      </c>
+      <c r="J842" t="s">
+        <v>153</v>
+      </c>
+      <c r="K842" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="843" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A843" s="2"/>
+      <c r="B843" s="2"/>
+      <c r="C843" s="2"/>
+      <c r="D843" s="2"/>
+      <c r="E843" s="3"/>
+      <c r="F843" s="2"/>
+      <c r="G843" t="s">
+        <v>590</v>
+      </c>
+      <c r="H843" t="s">
+        <v>17</v>
+      </c>
+      <c r="I843">
+        <v>2</v>
+      </c>
+      <c r="J843" t="s">
+        <v>153</v>
+      </c>
+      <c r="K843" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="844" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A844" s="2"/>
+      <c r="B844" s="2"/>
+      <c r="C844" s="2"/>
+      <c r="D844" s="2"/>
+      <c r="E844" s="3"/>
+      <c r="F844" s="2"/>
+      <c r="G844" t="s">
+        <v>591</v>
+      </c>
+      <c r="H844" t="s">
+        <v>17</v>
+      </c>
+      <c r="I844">
+        <v>6</v>
+      </c>
+      <c r="J844" t="s">
+        <v>153</v>
+      </c>
+      <c r="K844" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="845" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A845" s="2"/>
+      <c r="B845" s="2"/>
+      <c r="C845" s="2"/>
+      <c r="D845" s="2"/>
+      <c r="E845" s="3"/>
+      <c r="F845" s="2"/>
+      <c r="G845" t="s">
+        <v>592</v>
+      </c>
+      <c r="H845" t="s">
+        <v>17</v>
+      </c>
+      <c r="I845">
+        <v>6</v>
+      </c>
+      <c r="J845" t="s">
+        <v>153</v>
+      </c>
+      <c r="K845" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="846" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A846" s="2"/>
+      <c r="B846" s="2"/>
+      <c r="C846" s="2"/>
+      <c r="D846" s="2"/>
+      <c r="E846" s="3"/>
+      <c r="F846" s="2"/>
+      <c r="G846" t="s">
+        <v>593</v>
+      </c>
+      <c r="H846" t="s">
+        <v>17</v>
+      </c>
+      <c r="I846">
+        <v>8</v>
+      </c>
+      <c r="J846" t="s">
+        <v>153</v>
+      </c>
+      <c r="K846" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="847" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A847" s="2"/>
+      <c r="B847" s="2"/>
+      <c r="C847" s="2"/>
+      <c r="D847" s="2"/>
+      <c r="E847" s="3"/>
+      <c r="F847" s="2"/>
+      <c r="G847" t="s">
+        <v>594</v>
+      </c>
+      <c r="H847" t="s">
+        <v>55</v>
+      </c>
+      <c r="I847">
+        <v>4</v>
+      </c>
+      <c r="J847" t="s">
+        <v>153</v>
+      </c>
+      <c r="K847" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="848" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A848" s="2"/>
+      <c r="B848" s="2"/>
+      <c r="C848" s="2"/>
+      <c r="D848" s="2"/>
+      <c r="E848" s="3"/>
+      <c r="F848" s="2"/>
+      <c r="G848" t="s">
+        <v>595</v>
+      </c>
+      <c r="H848" t="s">
+        <v>55</v>
+      </c>
+      <c r="I848">
+        <v>4</v>
+      </c>
+      <c r="J848" t="s">
+        <v>153</v>
+      </c>
+      <c r="K848" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="850" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A850" s="2">
+        <v>45</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C850" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D850" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E850" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F850" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="G850" t="s">
+        <v>82</v>
+      </c>
+      <c r="H850" t="s">
+        <v>17</v>
+      </c>
+      <c r="I850">
+        <v>4</v>
+      </c>
+      <c r="J850" t="s">
+        <v>153</v>
+      </c>
+      <c r="K850" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="851" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A851" s="2"/>
+      <c r="B851" s="2"/>
+      <c r="C851" s="2"/>
+      <c r="D851" s="2"/>
+      <c r="E851" s="3"/>
+      <c r="F851" s="2"/>
+      <c r="G851" t="s">
+        <v>598</v>
+      </c>
+      <c r="H851" t="s">
+        <v>17</v>
+      </c>
+      <c r="I851">
+        <v>2</v>
+      </c>
+      <c r="J851" t="s">
+        <v>153</v>
+      </c>
+      <c r="K851" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="852" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A852" s="2"/>
+      <c r="B852" s="2"/>
+      <c r="C852" s="2"/>
+      <c r="D852" s="2"/>
+      <c r="E852" s="3"/>
+      <c r="F852" s="2"/>
+      <c r="G852" t="s">
+        <v>599</v>
+      </c>
+      <c r="H852" t="s">
+        <v>17</v>
+      </c>
+      <c r="I852">
+        <v>2</v>
+      </c>
+      <c r="J852" t="s">
+        <v>153</v>
+      </c>
+      <c r="K852" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="853" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A853" s="2"/>
+      <c r="B853" s="2"/>
+      <c r="C853" s="2"/>
+      <c r="D853" s="2"/>
+      <c r="E853" s="3"/>
+      <c r="F853" s="2"/>
+      <c r="G853" t="s">
+        <v>512</v>
+      </c>
+      <c r="H853" t="s">
+        <v>17</v>
+      </c>
+      <c r="I853">
+        <v>4</v>
+      </c>
+      <c r="J853" t="s">
+        <v>153</v>
+      </c>
+      <c r="K853" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="854" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A854" s="2"/>
+      <c r="B854" s="2"/>
+      <c r="C854" s="2"/>
+      <c r="D854" s="2"/>
+      <c r="E854" s="3"/>
+      <c r="F854" s="2"/>
+      <c r="G854" t="s">
+        <v>205</v>
+      </c>
+      <c r="H854" t="s">
+        <v>17</v>
+      </c>
+      <c r="I854">
+        <v>4</v>
+      </c>
+      <c r="J854" t="s">
+        <v>153</v>
+      </c>
+      <c r="K854" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="855" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A855" s="2"/>
+      <c r="B855" s="2"/>
+      <c r="C855" s="2"/>
+      <c r="D855" s="2"/>
+      <c r="E855" s="3"/>
+      <c r="F855" s="2"/>
+      <c r="G855" t="s">
+        <v>503</v>
+      </c>
+      <c r="H855" t="s">
+        <v>17</v>
+      </c>
+      <c r="I855">
+        <v>5</v>
+      </c>
+      <c r="J855" t="s">
+        <v>153</v>
+      </c>
+      <c r="K855" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="856" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A856" s="2"/>
+      <c r="B856" s="2"/>
+      <c r="C856" s="2"/>
+      <c r="D856" s="2"/>
+      <c r="E856" s="3"/>
+      <c r="F856" s="2"/>
+      <c r="G856" t="s">
+        <v>600</v>
+      </c>
+      <c r="H856" t="s">
+        <v>17</v>
+      </c>
+      <c r="I856">
+        <v>3</v>
+      </c>
+      <c r="J856" t="s">
+        <v>153</v>
+      </c>
+      <c r="K856" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="857" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A857" s="2"/>
+      <c r="B857" s="2"/>
+      <c r="C857" s="2"/>
+      <c r="D857" s="2"/>
+      <c r="E857" s="3"/>
+      <c r="F857" s="2"/>
+      <c r="G857" t="s">
+        <v>339</v>
+      </c>
+      <c r="H857" t="s">
+        <v>17</v>
+      </c>
+      <c r="I857">
+        <v>2</v>
+      </c>
+      <c r="J857" t="s">
+        <v>153</v>
+      </c>
+      <c r="K857" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="858" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A858" s="2"/>
+      <c r="B858" s="2"/>
+      <c r="C858" s="2"/>
+      <c r="D858" s="2"/>
+      <c r="E858" s="3"/>
+      <c r="F858" s="2"/>
+      <c r="G858" t="s">
+        <v>511</v>
+      </c>
+      <c r="H858" t="s">
+        <v>17</v>
+      </c>
+      <c r="I858">
+        <v>4</v>
+      </c>
+      <c r="J858" t="s">
+        <v>153</v>
+      </c>
+      <c r="K858" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="859" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A859" s="2"/>
+      <c r="B859" s="2"/>
+      <c r="C859" s="2"/>
+      <c r="D859" s="2"/>
+      <c r="E859" s="3"/>
+      <c r="F859" s="2"/>
+      <c r="G859" t="s">
+        <v>485</v>
+      </c>
+      <c r="H859" t="s">
+        <v>17</v>
+      </c>
+      <c r="I859">
+        <v>4</v>
+      </c>
+      <c r="J859" t="s">
+        <v>153</v>
+      </c>
+      <c r="K859" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="860" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A860" s="2"/>
+      <c r="B860" s="2"/>
+      <c r="C860" s="2"/>
+      <c r="D860" s="2"/>
+      <c r="E860" s="3"/>
+      <c r="F860" s="2"/>
+      <c r="G860" t="s">
+        <v>488</v>
+      </c>
+      <c r="H860" t="s">
+        <v>17</v>
+      </c>
+      <c r="I860">
+        <v>2</v>
+      </c>
+      <c r="J860" t="s">
+        <v>153</v>
+      </c>
+      <c r="K860" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="861" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A861" s="2"/>
+      <c r="B861" s="2"/>
+      <c r="C861" s="2"/>
+      <c r="D861" s="2"/>
+      <c r="E861" s="3"/>
+      <c r="F861" s="2"/>
+      <c r="G861" t="s">
+        <v>22</v>
+      </c>
+      <c r="H861" t="s">
+        <v>17</v>
+      </c>
+      <c r="I861">
+        <v>2</v>
+      </c>
+      <c r="J861" t="s">
+        <v>153</v>
+      </c>
+      <c r="K861" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="862" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A862" s="2"/>
+      <c r="B862" s="2"/>
+      <c r="C862" s="2"/>
+      <c r="D862" s="2"/>
+      <c r="E862" s="3"/>
+      <c r="F862" s="2"/>
+      <c r="G862" t="s">
+        <v>185</v>
+      </c>
+      <c r="H862" t="s">
+        <v>55</v>
+      </c>
+      <c r="I862">
+        <v>4</v>
+      </c>
+      <c r="J862" t="s">
+        <v>153</v>
+      </c>
+      <c r="K862" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="863" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A863" s="2"/>
+      <c r="B863" s="2"/>
+      <c r="C863" s="2"/>
+      <c r="D863" s="2"/>
+      <c r="E863" s="3"/>
+      <c r="F863" s="2"/>
+      <c r="G863" t="s">
+        <v>491</v>
+      </c>
+      <c r="H863" t="s">
+        <v>17</v>
+      </c>
+      <c r="I863">
+        <v>2</v>
+      </c>
+      <c r="J863" t="s">
+        <v>153</v>
+      </c>
+      <c r="K863" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="864" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A864" s="2"/>
+      <c r="B864" s="2"/>
+      <c r="C864" s="2"/>
+      <c r="D864" s="2"/>
+      <c r="E864" s="3"/>
+      <c r="F864" s="2"/>
+      <c r="G864" t="s">
+        <v>26</v>
+      </c>
+      <c r="H864" t="s">
+        <v>17</v>
+      </c>
+      <c r="I864">
+        <v>5</v>
+      </c>
+      <c r="J864" t="s">
+        <v>153</v>
+      </c>
+      <c r="K864" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="865" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A865" s="2"/>
+      <c r="B865" s="2"/>
+      <c r="C865" s="2"/>
+      <c r="D865" s="2"/>
+      <c r="E865" s="3"/>
+      <c r="F865" s="2"/>
+      <c r="G865" t="s">
+        <v>226</v>
+      </c>
+      <c r="H865" t="s">
+        <v>17</v>
+      </c>
+      <c r="I865">
+        <v>6</v>
+      </c>
+      <c r="J865" t="s">
+        <v>153</v>
+      </c>
+      <c r="K865" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="866" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A866" s="2"/>
+      <c r="B866" s="2"/>
+      <c r="C866" s="2"/>
+      <c r="D866" s="2"/>
+      <c r="E866" s="3"/>
+      <c r="F866" s="2"/>
+      <c r="G866" t="s">
+        <v>227</v>
+      </c>
+      <c r="H866" t="s">
+        <v>55</v>
+      </c>
+      <c r="I866">
+        <v>4</v>
+      </c>
+      <c r="J866" t="s">
+        <v>153</v>
+      </c>
+      <c r="K866" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="867" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A867" s="2"/>
+      <c r="B867" s="2"/>
+      <c r="C867" s="2"/>
+      <c r="D867" s="2"/>
+      <c r="E867" s="3"/>
+      <c r="F867" s="2"/>
+      <c r="G867" t="s">
+        <v>31</v>
+      </c>
+      <c r="H867" t="s">
+        <v>17</v>
+      </c>
+      <c r="I867">
+        <v>4</v>
+      </c>
+      <c r="J867" t="s">
+        <v>153</v>
+      </c>
+      <c r="K867" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="868" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A868" s="2"/>
+      <c r="B868" s="2"/>
+      <c r="C868" s="2"/>
+      <c r="D868" s="2"/>
+      <c r="E868" s="3"/>
+      <c r="F868" s="2"/>
+      <c r="G868" t="s">
+        <v>34</v>
+      </c>
+      <c r="H868" t="s">
+        <v>17</v>
+      </c>
+      <c r="I868">
+        <v>2</v>
+      </c>
+      <c r="J868" t="s">
+        <v>153</v>
+      </c>
+      <c r="K868" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="869" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A869" s="2"/>
+      <c r="B869" s="2"/>
+      <c r="C869" s="2"/>
+      <c r="D869" s="2"/>
+      <c r="E869" s="3"/>
+      <c r="F869" s="2"/>
+      <c r="G869" t="s">
+        <v>601</v>
+      </c>
+      <c r="H869" t="s">
+        <v>55</v>
+      </c>
+      <c r="I869">
+        <v>2</v>
+      </c>
+      <c r="J869" t="s">
+        <v>153</v>
+      </c>
+      <c r="K869" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="870" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A870" s="2"/>
+      <c r="B870" s="2"/>
+      <c r="C870" s="2"/>
+      <c r="D870" s="2"/>
+      <c r="E870" s="3"/>
+      <c r="F870" s="2"/>
+      <c r="G870" t="s">
+        <v>74</v>
+      </c>
+      <c r="H870" t="s">
+        <v>55</v>
+      </c>
+      <c r="I870">
+        <v>3</v>
+      </c>
+      <c r="J870" t="s">
+        <v>153</v>
+      </c>
+      <c r="K870" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="871" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A871" s="2"/>
+      <c r="B871" s="2"/>
+      <c r="C871" s="2"/>
+      <c r="D871" s="2"/>
+      <c r="E871" s="3"/>
+      <c r="F871" s="2"/>
+      <c r="G871" t="s">
+        <v>602</v>
+      </c>
+      <c r="H871" t="s">
+        <v>55</v>
+      </c>
+      <c r="I871">
+        <v>2</v>
+      </c>
+      <c r="J871" t="s">
+        <v>153</v>
+      </c>
+      <c r="K871" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="872" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A872" s="2"/>
+      <c r="B872" s="2"/>
+      <c r="C872" s="2"/>
+      <c r="D872" s="2"/>
+      <c r="E872" s="3"/>
+      <c r="F872" s="2"/>
+      <c r="G872" t="s">
+        <v>603</v>
+      </c>
+      <c r="H872" t="s">
+        <v>55</v>
+      </c>
+      <c r="I872">
+        <v>2</v>
+      </c>
+      <c r="J872" t="s">
+        <v>153</v>
+      </c>
+      <c r="K872" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="873" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A873" s="2"/>
+      <c r="B873" s="2"/>
+      <c r="C873" s="2"/>
+      <c r="D873" s="2"/>
+      <c r="E873" s="3"/>
+      <c r="F873" s="2"/>
+      <c r="G873" t="s">
+        <v>143</v>
+      </c>
+      <c r="H873" t="s">
+        <v>55</v>
+      </c>
+      <c r="I873">
+        <v>4</v>
+      </c>
+      <c r="J873" t="s">
+        <v>153</v>
+      </c>
+      <c r="K873" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="874" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A874" s="2"/>
+      <c r="B874" s="2"/>
+      <c r="C874" s="2"/>
+      <c r="D874" s="2"/>
+      <c r="E874" s="3"/>
+      <c r="F874" s="2"/>
+      <c r="G874" t="s">
+        <v>261</v>
+      </c>
+      <c r="H874" t="s">
+        <v>55</v>
+      </c>
+      <c r="I874">
+        <v>4</v>
+      </c>
+      <c r="J874" t="s">
+        <v>153</v>
+      </c>
+      <c r="K874" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="875" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A875" s="2"/>
+      <c r="B875" s="2"/>
+      <c r="C875" s="2"/>
+      <c r="D875" s="2"/>
+      <c r="E875" s="3"/>
+      <c r="F875" s="2"/>
+      <c r="G875" t="s">
+        <v>321</v>
+      </c>
+      <c r="H875" t="s">
+        <v>55</v>
+      </c>
+      <c r="I875">
+        <v>2</v>
+      </c>
+      <c r="J875" t="s">
+        <v>153</v>
+      </c>
+      <c r="K875" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="876" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A876" s="2"/>
+      <c r="B876" s="2"/>
+      <c r="C876" s="2"/>
+      <c r="D876" s="2"/>
+      <c r="E876" s="3"/>
+      <c r="F876" s="2"/>
+      <c r="G876" t="s">
+        <v>320</v>
+      </c>
+      <c r="H876" t="s">
+        <v>55</v>
+      </c>
+      <c r="I876">
+        <v>2</v>
+      </c>
+      <c r="J876" t="s">
+        <v>153</v>
+      </c>
+      <c r="K876" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="877" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A877" s="2"/>
+      <c r="B877" s="2"/>
+      <c r="C877" s="2"/>
+      <c r="D877" s="2"/>
+      <c r="E877" s="3"/>
+      <c r="F877" s="2"/>
+      <c r="G877" t="s">
+        <v>16</v>
+      </c>
+      <c r="H877" t="s">
+        <v>17</v>
+      </c>
+      <c r="I877">
+        <v>4</v>
+      </c>
+      <c r="J877" t="s">
+        <v>153</v>
+      </c>
+      <c r="K877" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="878" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A878" s="2"/>
+      <c r="B878" s="2"/>
+      <c r="C878" s="2"/>
+      <c r="D878" s="2"/>
+      <c r="E878" s="3"/>
+      <c r="F878" s="2"/>
+      <c r="G878" t="s">
+        <v>315</v>
+      </c>
+      <c r="H878" t="s">
+        <v>55</v>
+      </c>
+      <c r="I878">
+        <v>2</v>
+      </c>
+      <c r="J878" t="s">
+        <v>153</v>
+      </c>
+      <c r="K878" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="879" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A879" s="2"/>
+      <c r="B879" s="2"/>
+      <c r="C879" s="2"/>
+      <c r="D879" s="2"/>
+      <c r="E879" s="3"/>
+      <c r="F879" s="2"/>
+      <c r="G879" t="s">
+        <v>469</v>
+      </c>
+      <c r="H879" t="s">
+        <v>17</v>
+      </c>
+      <c r="I879">
+        <v>4</v>
+      </c>
+      <c r="J879" t="s">
+        <v>153</v>
+      </c>
+      <c r="K879" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="880" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A880" s="2"/>
+      <c r="B880" s="2"/>
+      <c r="C880" s="2"/>
+      <c r="D880" s="2"/>
+      <c r="E880" s="3"/>
+      <c r="F880" s="2"/>
+      <c r="G880" t="s">
+        <v>473</v>
+      </c>
+      <c r="H880" t="s">
+        <v>17</v>
+      </c>
+      <c r="I880">
+        <v>4</v>
+      </c>
+      <c r="J880" t="s">
+        <v>153</v>
+      </c>
+      <c r="K880" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="881" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A881" s="2"/>
+      <c r="B881" s="2"/>
+      <c r="C881" s="2"/>
+      <c r="D881" s="2"/>
+      <c r="E881" s="3"/>
+      <c r="F881" s="2"/>
+      <c r="G881" t="s">
+        <v>604</v>
+      </c>
+      <c r="H881" t="s">
+        <v>17</v>
+      </c>
+      <c r="I881">
+        <v>4</v>
+      </c>
+      <c r="J881" t="s">
+        <v>153</v>
+      </c>
+      <c r="K881" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="882" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A882" s="2"/>
+      <c r="B882" s="2"/>
+      <c r="C882" s="2"/>
+      <c r="D882" s="2"/>
+      <c r="E882" s="3"/>
+      <c r="F882" s="2"/>
+      <c r="G882" t="s">
+        <v>216</v>
+      </c>
+      <c r="H882" t="s">
+        <v>55</v>
+      </c>
+      <c r="I882">
+        <v>2</v>
+      </c>
+      <c r="J882" t="s">
+        <v>153</v>
+      </c>
+      <c r="K882" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="883" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A883" s="2"/>
+      <c r="B883" s="2"/>
+      <c r="C883" s="2"/>
+      <c r="D883" s="2"/>
+      <c r="E883" s="3"/>
+      <c r="F883" s="2"/>
+      <c r="G883" t="s">
+        <v>470</v>
+      </c>
+      <c r="H883" t="s">
+        <v>55</v>
+      </c>
+      <c r="I883">
+        <v>2</v>
+      </c>
+      <c r="J883" t="s">
+        <v>153</v>
+      </c>
+      <c r="K883" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="884" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A884" s="2"/>
+      <c r="B884" s="2"/>
+      <c r="C884" s="2"/>
+      <c r="D884" s="2"/>
+      <c r="E884" s="3"/>
+      <c r="F884" s="2"/>
+      <c r="G884" t="s">
+        <v>346</v>
+      </c>
+      <c r="H884" t="s">
+        <v>17</v>
+      </c>
+      <c r="I884">
+        <v>3</v>
+      </c>
+      <c r="J884" t="s">
+        <v>153</v>
+      </c>
+      <c r="K884" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="885" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A885" s="2"/>
+      <c r="B885" s="2"/>
+      <c r="C885" s="2"/>
+      <c r="D885" s="2"/>
+      <c r="E885" s="3"/>
+      <c r="F885" s="2"/>
+      <c r="G885" t="s">
+        <v>293</v>
+      </c>
+      <c r="H885" t="s">
+        <v>17</v>
+      </c>
+      <c r="I885">
+        <v>2</v>
+      </c>
+      <c r="J885" t="s">
+        <v>153</v>
+      </c>
+      <c r="K885" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="886" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A886" s="2"/>
+      <c r="B886" s="2"/>
+      <c r="C886" s="2"/>
+      <c r="D886" s="2"/>
+      <c r="E886" s="3"/>
+      <c r="F886" s="2"/>
+      <c r="G886" t="s">
+        <v>97</v>
+      </c>
+      <c r="H886" t="s">
+        <v>17</v>
+      </c>
+      <c r="I886">
+        <v>6</v>
+      </c>
+      <c r="J886" t="s">
+        <v>153</v>
+      </c>
+      <c r="K886" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="887" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A887" s="2"/>
+      <c r="B887" s="2"/>
+      <c r="C887" s="2"/>
+      <c r="D887" s="2"/>
+      <c r="E887" s="3"/>
+      <c r="F887" s="2"/>
+      <c r="G887" t="s">
+        <v>99</v>
+      </c>
+      <c r="H887" t="s">
+        <v>17</v>
+      </c>
+      <c r="I887">
+        <v>6</v>
+      </c>
+      <c r="J887" t="s">
+        <v>153</v>
+      </c>
+      <c r="K887" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="888" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A888" s="2"/>
+      <c r="B888" s="2"/>
+      <c r="C888" s="2"/>
+      <c r="D888" s="2"/>
+      <c r="E888" s="3"/>
+      <c r="F888" s="2"/>
+      <c r="G888" t="s">
+        <v>131</v>
+      </c>
+      <c r="H888" t="s">
+        <v>17</v>
+      </c>
+      <c r="I888">
+        <v>8</v>
+      </c>
+      <c r="J888" t="s">
+        <v>153</v>
+      </c>
+      <c r="K888" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="889" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A889" s="2"/>
+      <c r="B889" s="2"/>
+      <c r="C889" s="2"/>
+      <c r="D889" s="2"/>
+      <c r="E889" s="3"/>
+      <c r="F889" s="2"/>
+      <c r="G889" t="s">
+        <v>68</v>
+      </c>
+      <c r="H889" t="s">
+        <v>55</v>
+      </c>
+      <c r="I889">
+        <v>4</v>
+      </c>
+      <c r="J889" t="s">
+        <v>153</v>
+      </c>
+      <c r="K889" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="890" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A890" s="2"/>
+      <c r="B890" s="2"/>
+      <c r="C890" s="2"/>
+      <c r="D890" s="2"/>
+      <c r="E890" s="3"/>
+      <c r="F890" s="2"/>
+      <c r="G890" t="s">
+        <v>605</v>
+      </c>
+      <c r="H890" t="s">
+        <v>55</v>
+      </c>
+      <c r="I890">
+        <v>4</v>
+      </c>
+      <c r="J890" t="s">
+        <v>153</v>
+      </c>
+      <c r="K890" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="892" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A892" s="2">
+        <v>46</v>
+      </c>
+      <c r="B892" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C892" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D892" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E892" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F892" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="G892" t="s">
+        <v>608</v>
+      </c>
+      <c r="H892" t="s">
+        <v>17</v>
+      </c>
+      <c r="I892">
+        <v>4</v>
+      </c>
+      <c r="J892" t="s">
+        <v>153</v>
+      </c>
+      <c r="K892" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="893" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A893" s="2"/>
+      <c r="B893" s="2"/>
+      <c r="C893" s="2"/>
+      <c r="D893" s="2"/>
+      <c r="E893" s="3"/>
+      <c r="F893" s="2"/>
+      <c r="G893" t="s">
+        <v>609</v>
+      </c>
+      <c r="H893" t="s">
+        <v>17</v>
+      </c>
+      <c r="I893">
+        <v>4</v>
+      </c>
+      <c r="J893" t="s">
+        <v>153</v>
+      </c>
+      <c r="K893" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="894" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A894" s="2"/>
+      <c r="B894" s="2"/>
+      <c r="C894" s="2"/>
+      <c r="D894" s="2"/>
+      <c r="E894" s="3"/>
+      <c r="F894" s="2"/>
+      <c r="G894" t="s">
+        <v>610</v>
+      </c>
+      <c r="H894" t="s">
+        <v>17</v>
+      </c>
+      <c r="I894">
+        <v>3</v>
+      </c>
+      <c r="J894" t="s">
+        <v>153</v>
+      </c>
+      <c r="K894" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="895" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A895" s="2"/>
+      <c r="B895" s="2"/>
+      <c r="C895" s="2"/>
+      <c r="D895" s="2"/>
+      <c r="E895" s="3"/>
+      <c r="F895" s="2"/>
+      <c r="G895" t="s">
+        <v>235</v>
+      </c>
+      <c r="H895" t="s">
+        <v>17</v>
+      </c>
+      <c r="I895">
+        <v>4</v>
+      </c>
+      <c r="J895" t="s">
+        <v>153</v>
+      </c>
+      <c r="K895" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="896" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A896" s="2"/>
+      <c r="B896" s="2"/>
+      <c r="C896" s="2"/>
+      <c r="D896" s="2"/>
+      <c r="E896" s="3"/>
+      <c r="F896" s="2"/>
+      <c r="G896" t="s">
+        <v>202</v>
+      </c>
+      <c r="H896" t="s">
+        <v>17</v>
+      </c>
+      <c r="I896">
+        <v>4</v>
+      </c>
+      <c r="J896" t="s">
+        <v>153</v>
+      </c>
+      <c r="K896" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="897" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A897" s="2"/>
+      <c r="B897" s="2"/>
+      <c r="C897" s="2"/>
+      <c r="D897" s="2"/>
+      <c r="E897" s="3"/>
+      <c r="F897" s="2"/>
+      <c r="G897" t="s">
+        <v>611</v>
+      </c>
+      <c r="H897" t="s">
+        <v>17</v>
+      </c>
+      <c r="I897">
+        <v>16</v>
+      </c>
+      <c r="J897" t="s">
+        <v>153</v>
+      </c>
+      <c r="K897" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="898" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A898" s="2"/>
+      <c r="B898" s="2"/>
+      <c r="C898" s="2"/>
+      <c r="D898" s="2"/>
+      <c r="E898" s="3"/>
+      <c r="F898" s="2"/>
+      <c r="G898" t="s">
+        <v>237</v>
+      </c>
+      <c r="H898" t="s">
+        <v>17</v>
+      </c>
+      <c r="I898">
+        <v>4</v>
+      </c>
+      <c r="J898" t="s">
+        <v>153</v>
+      </c>
+      <c r="K898" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="899" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A899" s="2"/>
+      <c r="B899" s="2"/>
+      <c r="C899" s="2"/>
+      <c r="D899" s="2"/>
+      <c r="E899" s="3"/>
+      <c r="F899" s="2"/>
+      <c r="G899" t="s">
+        <v>236</v>
+      </c>
+      <c r="H899" t="s">
+        <v>55</v>
+      </c>
+      <c r="I899">
+        <v>4</v>
+      </c>
+      <c r="J899" t="s">
+        <v>153</v>
+      </c>
+      <c r="K899" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="900" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A900" s="2"/>
+      <c r="B900" s="2"/>
+      <c r="C900" s="2"/>
+      <c r="D900" s="2"/>
+      <c r="E900" s="3"/>
+      <c r="F900" s="2"/>
+      <c r="G900" t="s">
+        <v>240</v>
+      </c>
+      <c r="H900" t="s">
+        <v>55</v>
+      </c>
+      <c r="I900">
+        <v>2</v>
+      </c>
+      <c r="J900" t="s">
+        <v>153</v>
+      </c>
+      <c r="K900" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="901" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A901" s="2"/>
+      <c r="B901" s="2"/>
+      <c r="C901" s="2"/>
+      <c r="D901" s="2"/>
+      <c r="E901" s="3"/>
+      <c r="F901" s="2"/>
+      <c r="G901" t="s">
+        <v>612</v>
+      </c>
+      <c r="H901" t="s">
+        <v>17</v>
+      </c>
+      <c r="I901">
+        <v>10</v>
+      </c>
+      <c r="J901" t="s">
+        <v>153</v>
+      </c>
+      <c r="K901" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="902" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A902" s="2"/>
+      <c r="B902" s="2"/>
+      <c r="C902" s="2"/>
+      <c r="D902" s="2"/>
+      <c r="E902" s="3"/>
+      <c r="F902" s="2"/>
+      <c r="G902" t="s">
+        <v>110</v>
+      </c>
+      <c r="H902" t="s">
+        <v>55</v>
+      </c>
+      <c r="I902">
+        <v>6</v>
+      </c>
+      <c r="J902" t="s">
+        <v>153</v>
+      </c>
+      <c r="K902" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="903" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A903" s="2"/>
+      <c r="B903" s="2"/>
+      <c r="C903" s="2"/>
+      <c r="D903" s="2"/>
+      <c r="E903" s="3"/>
+      <c r="F903" s="2"/>
+      <c r="G903" t="s">
+        <v>331</v>
+      </c>
+      <c r="H903" t="s">
+        <v>76</v>
+      </c>
+      <c r="I903">
+        <v>6</v>
+      </c>
+      <c r="J903" t="s">
+        <v>153</v>
+      </c>
+      <c r="K903" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="904" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A904" s="2"/>
+      <c r="B904" s="2"/>
+      <c r="C904" s="2"/>
+      <c r="D904" s="2"/>
+      <c r="E904" s="3"/>
+      <c r="F904" s="2"/>
+      <c r="G904" t="s">
+        <v>612</v>
+      </c>
+      <c r="H904" t="s">
+        <v>17</v>
+      </c>
+      <c r="I904">
+        <v>8</v>
+      </c>
+      <c r="J904" t="s">
+        <v>153</v>
+      </c>
+      <c r="K904" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="906" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A906" s="2">
+        <v>47</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C906" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D906" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E906" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F906" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="G906" t="s">
+        <v>197</v>
+      </c>
+      <c r="H906" t="s">
+        <v>76</v>
+      </c>
+      <c r="I906">
+        <v>3</v>
+      </c>
+      <c r="J906" t="s">
+        <v>153</v>
+      </c>
+      <c r="K906" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="907" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A907" s="2"/>
+      <c r="B907" s="2"/>
+      <c r="C907" s="2"/>
+      <c r="D907" s="2"/>
+      <c r="E907" s="3"/>
+      <c r="F907" s="2"/>
+      <c r="G907" t="s">
+        <v>159</v>
+      </c>
+      <c r="H907" t="s">
+        <v>17</v>
+      </c>
+      <c r="I907">
+        <v>1</v>
+      </c>
+      <c r="J907" t="s">
+        <v>153</v>
+      </c>
+      <c r="K907" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="908" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A908" s="2"/>
+      <c r="B908" s="2"/>
+      <c r="C908" s="2"/>
+      <c r="D908" s="2"/>
+      <c r="E908" s="3"/>
+      <c r="F908" s="2"/>
+      <c r="G908" t="s">
+        <v>325</v>
+      </c>
+      <c r="H908" t="s">
+        <v>17</v>
+      </c>
+      <c r="I908">
+        <v>2</v>
+      </c>
+      <c r="J908" t="s">
+        <v>153</v>
+      </c>
+      <c r="K908" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="909" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A909" s="2"/>
+      <c r="B909" s="2"/>
+      <c r="C909" s="2"/>
+      <c r="D909" s="2"/>
+      <c r="E909" s="3"/>
+      <c r="F909" s="2"/>
+      <c r="G909" t="s">
+        <v>73</v>
+      </c>
+      <c r="H909" t="s">
+        <v>17</v>
+      </c>
+      <c r="I909">
+        <v>2</v>
+      </c>
+      <c r="J909" t="s">
+        <v>153</v>
+      </c>
+      <c r="K909" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="910" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A910" s="2"/>
+      <c r="B910" s="2"/>
+      <c r="C910" s="2"/>
+      <c r="D910" s="2"/>
+      <c r="E910" s="3"/>
+      <c r="F910" s="2"/>
+      <c r="G910" t="s">
+        <v>615</v>
+      </c>
+      <c r="H910" t="s">
+        <v>55</v>
+      </c>
+      <c r="I910">
+        <v>1</v>
+      </c>
+      <c r="J910" t="s">
+        <v>153</v>
+      </c>
+      <c r="K910" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="911" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A911" s="2"/>
+      <c r="B911" s="2"/>
+      <c r="C911" s="2"/>
+      <c r="D911" s="2"/>
+      <c r="E911" s="3"/>
+      <c r="F911" s="2"/>
+      <c r="G911" t="s">
+        <v>330</v>
+      </c>
+      <c r="H911" t="s">
+        <v>76</v>
+      </c>
+      <c r="I911">
+        <v>3</v>
+      </c>
+      <c r="J911" t="s">
+        <v>153</v>
+      </c>
+      <c r="K911" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="912" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A912" s="2"/>
+      <c r="B912" s="2"/>
+      <c r="C912" s="2"/>
+      <c r="D912" s="2"/>
+      <c r="E912" s="3"/>
+      <c r="F912" s="2"/>
+      <c r="G912" t="s">
+        <v>427</v>
+      </c>
+      <c r="H912" t="s">
+        <v>76</v>
+      </c>
+      <c r="I912">
+        <v>2</v>
+      </c>
+      <c r="J912" t="s">
+        <v>153</v>
+      </c>
+      <c r="K912" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="913" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A913" s="2"/>
+      <c r="B913" s="2"/>
+      <c r="C913" s="2"/>
+      <c r="D913" s="2"/>
+      <c r="E913" s="3"/>
+      <c r="F913" s="2"/>
+      <c r="G913" t="s">
+        <v>616</v>
+      </c>
+      <c r="H913" t="s">
+        <v>17</v>
+      </c>
+      <c r="I913">
+        <v>1</v>
+      </c>
+      <c r="J913" t="s">
+        <v>153</v>
+      </c>
+      <c r="K913" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="914" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A914" s="2"/>
+      <c r="B914" s="2"/>
+      <c r="C914" s="2"/>
+      <c r="D914" s="2"/>
+      <c r="E914" s="3"/>
+      <c r="F914" s="2"/>
+      <c r="G914" t="s">
+        <v>617</v>
+      </c>
+      <c r="H914" t="s">
+        <v>17</v>
+      </c>
+      <c r="I914">
+        <v>1</v>
+      </c>
+      <c r="J914" t="s">
+        <v>153</v>
+      </c>
+      <c r="K914" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="915" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A915" s="2"/>
+      <c r="B915" s="2"/>
+      <c r="C915" s="2"/>
+      <c r="D915" s="2"/>
+      <c r="E915" s="3"/>
+      <c r="F915" s="2"/>
+      <c r="G915" t="s">
+        <v>254</v>
+      </c>
+      <c r="H915" t="s">
+        <v>55</v>
+      </c>
+      <c r="I915">
+        <v>1</v>
+      </c>
+      <c r="J915" t="s">
+        <v>153</v>
+      </c>
+      <c r="K915" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="916" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A916" s="2"/>
+      <c r="B916" s="2"/>
+      <c r="C916" s="2"/>
+      <c r="D916" s="2"/>
+      <c r="E916" s="3"/>
+      <c r="F916" s="2"/>
+      <c r="G916" t="s">
+        <v>618</v>
+      </c>
+      <c r="H916" t="s">
+        <v>17</v>
+      </c>
+      <c r="I916">
+        <v>1</v>
+      </c>
+      <c r="J916" t="s">
+        <v>153</v>
+      </c>
+      <c r="K916" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="917" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A917" s="2"/>
+      <c r="B917" s="2"/>
+      <c r="C917" s="2"/>
+      <c r="D917" s="2"/>
+      <c r="E917" s="3"/>
+      <c r="F917" s="2"/>
+      <c r="G917" t="s">
+        <v>619</v>
+      </c>
+      <c r="H917" t="s">
+        <v>17</v>
+      </c>
+      <c r="I917">
+        <v>2</v>
+      </c>
+      <c r="J917" t="s">
+        <v>153</v>
+      </c>
+      <c r="K917" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="919" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A919" s="2">
+        <v>48</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D919" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E919" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F919" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="G919" t="s">
+        <v>622</v>
+      </c>
+      <c r="H919" t="s">
+        <v>17</v>
+      </c>
+      <c r="I919">
+        <v>2</v>
+      </c>
+      <c r="J919" t="s">
+        <v>153</v>
+      </c>
+      <c r="K919" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="920" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A920" s="2"/>
+      <c r="B920" s="2"/>
+      <c r="C920" s="2"/>
+      <c r="D920" s="2"/>
+      <c r="E920" s="3"/>
+      <c r="F920" s="2"/>
+      <c r="G920" t="s">
+        <v>300</v>
+      </c>
+      <c r="H920" t="s">
+        <v>17</v>
+      </c>
+      <c r="I920">
+        <v>4</v>
+      </c>
+      <c r="J920" t="s">
+        <v>153</v>
+      </c>
+      <c r="K920" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="921" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A921" s="2"/>
+      <c r="B921" s="2"/>
+      <c r="C921" s="2"/>
+      <c r="D921" s="2"/>
+      <c r="E921" s="3"/>
+      <c r="F921" s="2"/>
+      <c r="G921" t="s">
+        <v>105</v>
+      </c>
+      <c r="H921" t="s">
+        <v>17</v>
+      </c>
+      <c r="I921">
+        <v>10</v>
+      </c>
+      <c r="J921" t="s">
+        <v>153</v>
+      </c>
+      <c r="K921" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="922" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A922" s="2"/>
+      <c r="B922" s="2"/>
+      <c r="C922" s="2"/>
+      <c r="D922" s="2"/>
+      <c r="E922" s="3"/>
+      <c r="F922" s="2"/>
+      <c r="G922" t="s">
+        <v>96</v>
+      </c>
+      <c r="H922" t="s">
+        <v>55</v>
+      </c>
+      <c r="I922">
+        <v>5</v>
+      </c>
+      <c r="J922" t="s">
+        <v>153</v>
+      </c>
+      <c r="K922" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="923" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A923" s="2"/>
+      <c r="B923" s="2"/>
+      <c r="C923" s="2"/>
+      <c r="D923" s="2"/>
+      <c r="E923" s="3"/>
+      <c r="F923" s="2"/>
+      <c r="G923" t="s">
+        <v>623</v>
+      </c>
+      <c r="H923" t="s">
+        <v>55</v>
+      </c>
+      <c r="I923">
+        <v>5</v>
+      </c>
+      <c r="J923" t="s">
+        <v>153</v>
+      </c>
+      <c r="K923" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="925" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A925" s="2">
+        <v>49</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="C925" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D925" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E925" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F925" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="G925" t="s">
+        <v>306</v>
+      </c>
+      <c r="H925" t="s">
+        <v>17</v>
+      </c>
+      <c r="I925">
+        <v>3</v>
+      </c>
+      <c r="J925" t="s">
+        <v>153</v>
+      </c>
+      <c r="K925" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="926" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A926" s="2"/>
+      <c r="B926" s="2"/>
+      <c r="C926" s="2"/>
+      <c r="D926" s="2"/>
+      <c r="E926" s="3"/>
+      <c r="F926" s="2"/>
+      <c r="G926" t="s">
+        <v>223</v>
+      </c>
+      <c r="H926" t="s">
+        <v>17</v>
+      </c>
+      <c r="I926">
+        <v>3</v>
+      </c>
+      <c r="J926" t="s">
+        <v>153</v>
+      </c>
+      <c r="K926" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="927" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A927" s="2"/>
+      <c r="B927" s="2"/>
+      <c r="C927" s="2"/>
+      <c r="D927" s="2"/>
+      <c r="E927" s="3"/>
+      <c r="F927" s="2"/>
+      <c r="G927" t="s">
+        <v>537</v>
+      </c>
+      <c r="H927" t="s">
+        <v>17</v>
+      </c>
+      <c r="I927">
+        <v>2</v>
+      </c>
+      <c r="J927" t="s">
+        <v>153</v>
+      </c>
+      <c r="K927" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="928" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A928" s="2"/>
+      <c r="B928" s="2"/>
+      <c r="C928" s="2"/>
+      <c r="D928" s="2"/>
+      <c r="E928" s="3"/>
+      <c r="F928" s="2"/>
+      <c r="G928" t="s">
+        <v>102</v>
+      </c>
+      <c r="H928" t="s">
+        <v>17</v>
+      </c>
+      <c r="I928">
+        <v>2</v>
+      </c>
+      <c r="J928" t="s">
+        <v>153</v>
+      </c>
+      <c r="K928" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="929" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A929" s="2"/>
+      <c r="B929" s="2"/>
+      <c r="C929" s="2"/>
+      <c r="D929" s="2"/>
+      <c r="E929" s="3"/>
+      <c r="F929" s="2"/>
+      <c r="G929" t="s">
+        <v>322</v>
+      </c>
+      <c r="H929" t="s">
+        <v>17</v>
+      </c>
+      <c r="I929">
+        <v>1</v>
+      </c>
+      <c r="J929" t="s">
+        <v>153</v>
+      </c>
+      <c r="K929" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="930" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A930" s="2"/>
+      <c r="B930" s="2"/>
+      <c r="C930" s="2"/>
+      <c r="D930" s="2"/>
+      <c r="E930" s="3"/>
+      <c r="F930" s="2"/>
+      <c r="G930" t="s">
+        <v>129</v>
+      </c>
+      <c r="H930" t="s">
+        <v>17</v>
+      </c>
+      <c r="I930">
+        <v>1</v>
+      </c>
+      <c r="J930" t="s">
+        <v>153</v>
+      </c>
+      <c r="K930" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="932" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A932" s="2">
+        <v>50</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C932" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D932" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E932" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F932" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="G932" t="s">
+        <v>628</v>
+      </c>
+      <c r="H932" t="s">
+        <v>76</v>
+      </c>
+      <c r="I932">
+        <v>6</v>
+      </c>
+      <c r="J932" t="s">
+        <v>153</v>
+      </c>
+      <c r="K932" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="933" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A933" s="2"/>
+      <c r="B933" s="2"/>
+      <c r="C933" s="2"/>
+      <c r="D933" s="2"/>
+      <c r="E933" s="3"/>
+      <c r="F933" s="2"/>
+      <c r="G933" t="s">
+        <v>629</v>
+      </c>
+      <c r="H933" t="s">
+        <v>17</v>
+      </c>
+      <c r="I933">
+        <v>15</v>
+      </c>
+      <c r="J933" t="s">
+        <v>153</v>
+      </c>
+      <c r="K933" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="934" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A934" s="2"/>
+      <c r="B934" s="2"/>
+      <c r="C934" s="2"/>
+      <c r="D934" s="2"/>
+      <c r="E934" s="3"/>
+      <c r="F934" s="2"/>
+      <c r="G934" t="s">
+        <v>630</v>
+      </c>
+      <c r="H934" t="s">
+        <v>17</v>
+      </c>
+      <c r="I934">
+        <v>1</v>
+      </c>
+      <c r="J934" t="s">
+        <v>153</v>
+      </c>
+      <c r="K934" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="935" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A935" s="2"/>
+      <c r="B935" s="2"/>
+      <c r="C935" s="2"/>
+      <c r="D935" s="2"/>
+      <c r="E935" s="3"/>
+      <c r="F935" s="2"/>
+      <c r="G935" t="s">
+        <v>631</v>
+      </c>
+      <c r="H935" t="s">
+        <v>17</v>
+      </c>
+      <c r="I935">
+        <v>2</v>
+      </c>
+      <c r="J935" t="s">
+        <v>153</v>
+      </c>
+      <c r="K935" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="936" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A936" s="2"/>
+      <c r="B936" s="2"/>
+      <c r="C936" s="2"/>
+      <c r="D936" s="2"/>
+      <c r="E936" s="3"/>
+      <c r="F936" s="2"/>
+      <c r="G936" t="s">
+        <v>632</v>
+      </c>
+      <c r="H936" t="s">
+        <v>17</v>
+      </c>
+      <c r="I936">
+        <v>4</v>
+      </c>
+      <c r="J936" t="s">
+        <v>153</v>
+      </c>
+      <c r="K936" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="937" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A937" s="2"/>
+      <c r="B937" s="2"/>
+      <c r="C937" s="2"/>
+      <c r="D937" s="2"/>
+      <c r="E937" s="3"/>
+      <c r="F937" s="2"/>
+      <c r="G937" t="s">
+        <v>633</v>
+      </c>
+      <c r="H937" t="s">
+        <v>55</v>
+      </c>
+      <c r="I937">
+        <v>2</v>
+      </c>
+      <c r="J937" t="s">
+        <v>153</v>
+      </c>
+      <c r="K937" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="938" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A938" s="2"/>
+      <c r="B938" s="2"/>
+      <c r="C938" s="2"/>
+      <c r="D938" s="2"/>
+      <c r="E938" s="3"/>
+      <c r="F938" s="2"/>
+      <c r="G938" t="s">
+        <v>634</v>
+      </c>
+      <c r="H938" t="s">
+        <v>55</v>
+      </c>
+      <c r="I938">
+        <v>1</v>
+      </c>
+      <c r="J938" t="s">
+        <v>153</v>
+      </c>
+      <c r="K938" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="939" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A939" s="2"/>
+      <c r="B939" s="2"/>
+      <c r="C939" s="2"/>
+      <c r="D939" s="2"/>
+      <c r="E939" s="3"/>
+      <c r="F939" s="2"/>
+      <c r="G939" t="s">
+        <v>635</v>
+      </c>
+      <c r="H939" t="s">
+        <v>55</v>
+      </c>
+      <c r="I939">
+        <v>3</v>
+      </c>
+      <c r="J939" t="s">
+        <v>153</v>
+      </c>
+      <c r="K939" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="940" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A940" s="2"/>
+      <c r="B940" s="2"/>
+      <c r="C940" s="2"/>
+      <c r="D940" s="2"/>
+      <c r="E940" s="3"/>
+      <c r="F940" s="2"/>
+      <c r="G940" t="s">
+        <v>636</v>
+      </c>
+      <c r="H940" t="s">
+        <v>55</v>
+      </c>
+      <c r="I940">
+        <v>1</v>
+      </c>
+      <c r="J940" t="s">
+        <v>153</v>
+      </c>
+      <c r="K940" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="941" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A941" s="2"/>
+      <c r="B941" s="2"/>
+      <c r="C941" s="2"/>
+      <c r="D941" s="2"/>
+      <c r="E941" s="3"/>
+      <c r="F941" s="2"/>
+      <c r="G941" t="s">
+        <v>637</v>
+      </c>
+      <c r="H941" t="s">
+        <v>55</v>
+      </c>
+      <c r="I941">
+        <v>2</v>
+      </c>
+      <c r="J941" t="s">
+        <v>153</v>
+      </c>
+      <c r="K941" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="942" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A942" s="2"/>
+      <c r="B942" s="2"/>
+      <c r="C942" s="2"/>
+      <c r="D942" s="2"/>
+      <c r="E942" s="3"/>
+      <c r="F942" s="2"/>
+      <c r="G942" t="s">
+        <v>638</v>
+      </c>
+      <c r="H942" t="s">
+        <v>55</v>
+      </c>
+      <c r="I942">
+        <v>1</v>
+      </c>
+      <c r="J942" t="s">
+        <v>153</v>
+      </c>
+      <c r="K942" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="943" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A943" s="2"/>
+      <c r="B943" s="2"/>
+      <c r="C943" s="2"/>
+      <c r="D943" s="2"/>
+      <c r="E943" s="3"/>
+      <c r="F943" s="2"/>
+      <c r="G943" t="s">
+        <v>639</v>
+      </c>
+      <c r="H943" t="s">
+        <v>55</v>
+      </c>
+      <c r="I943">
+        <v>1</v>
+      </c>
+      <c r="J943" t="s">
+        <v>153</v>
+      </c>
+      <c r="K943" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="944" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A944" s="2"/>
+      <c r="B944" s="2"/>
+      <c r="C944" s="2"/>
+      <c r="D944" s="2"/>
+      <c r="E944" s="3"/>
+      <c r="F944" s="2"/>
+      <c r="G944" t="s">
+        <v>640</v>
+      </c>
+      <c r="H944" t="s">
+        <v>55</v>
+      </c>
+      <c r="I944">
+        <v>2</v>
+      </c>
+      <c r="J944" t="s">
+        <v>153</v>
+      </c>
+      <c r="K944" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="945" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A945" s="2"/>
+      <c r="B945" s="2"/>
+      <c r="C945" s="2"/>
+      <c r="D945" s="2"/>
+      <c r="E945" s="3"/>
+      <c r="F945" s="2"/>
+      <c r="G945" t="s">
+        <v>641</v>
+      </c>
+      <c r="H945" t="s">
+        <v>55</v>
+      </c>
+      <c r="I945">
+        <v>1</v>
+      </c>
+      <c r="J945" t="s">
+        <v>153</v>
+      </c>
+      <c r="K945" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="946" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A946" s="2"/>
+      <c r="B946" s="2"/>
+      <c r="C946" s="2"/>
+      <c r="D946" s="2"/>
+      <c r="E946" s="3"/>
+      <c r="F946" s="2"/>
+      <c r="G946" t="s">
+        <v>642</v>
+      </c>
+      <c r="H946" t="s">
+        <v>17</v>
+      </c>
+      <c r="I946">
+        <v>4</v>
+      </c>
+      <c r="J946" t="s">
+        <v>153</v>
+      </c>
+      <c r="K946" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="947" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A947" s="2"/>
+      <c r="B947" s="2"/>
+      <c r="C947" s="2"/>
+      <c r="D947" s="2"/>
+      <c r="E947" s="3"/>
+      <c r="F947" s="2"/>
+      <c r="G947" t="s">
+        <v>643</v>
+      </c>
+      <c r="H947" t="s">
+        <v>17</v>
+      </c>
+      <c r="I947">
+        <v>2</v>
+      </c>
+      <c r="J947" t="s">
+        <v>153</v>
+      </c>
+      <c r="K947" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="948" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A948" s="2"/>
+      <c r="B948" s="2"/>
+      <c r="C948" s="2"/>
+      <c r="D948" s="2"/>
+      <c r="E948" s="3"/>
+      <c r="F948" s="2"/>
+      <c r="G948" t="s">
+        <v>644</v>
+      </c>
+      <c r="H948" t="s">
+        <v>17</v>
+      </c>
+      <c r="I948">
+        <v>2</v>
+      </c>
+      <c r="J948" t="s">
+        <v>153</v>
+      </c>
+      <c r="K948" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="949" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A949" s="2"/>
+      <c r="B949" s="2"/>
+      <c r="C949" s="2"/>
+      <c r="D949" s="2"/>
+      <c r="E949" s="3"/>
+      <c r="F949" s="2"/>
+      <c r="G949" t="s">
+        <v>645</v>
+      </c>
+      <c r="H949" t="s">
+        <v>17</v>
+      </c>
+      <c r="I949">
+        <v>4</v>
+      </c>
+      <c r="J949" t="s">
+        <v>153</v>
+      </c>
+      <c r="K949" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="950" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A950" s="2"/>
+      <c r="B950" s="2"/>
+      <c r="C950" s="2"/>
+      <c r="D950" s="2"/>
+      <c r="E950" s="3"/>
+      <c r="F950" s="2"/>
+      <c r="G950" t="s">
+        <v>591</v>
+      </c>
+      <c r="H950" t="s">
+        <v>17</v>
+      </c>
+      <c r="I950">
+        <v>3</v>
+      </c>
+      <c r="J950" t="s">
+        <v>153</v>
+      </c>
+      <c r="K950" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="951" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A951" s="2"/>
+      <c r="B951" s="2"/>
+      <c r="C951" s="2"/>
+      <c r="D951" s="2"/>
+      <c r="E951" s="3"/>
+      <c r="F951" s="2"/>
+      <c r="G951" t="s">
+        <v>646</v>
+      </c>
+      <c r="H951" t="s">
+        <v>17</v>
+      </c>
+      <c r="I951">
+        <v>2</v>
+      </c>
+      <c r="J951" t="s">
+        <v>153</v>
+      </c>
+      <c r="K951" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="952" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A952" s="2"/>
+      <c r="B952" s="2"/>
+      <c r="C952" s="2"/>
+      <c r="D952" s="2"/>
+      <c r="E952" s="3"/>
+      <c r="F952" s="2"/>
+      <c r="G952" t="s">
+        <v>647</v>
+      </c>
+      <c r="H952" t="s">
+        <v>55</v>
+      </c>
+      <c r="I952">
+        <v>4</v>
+      </c>
+      <c r="J952" t="s">
+        <v>153</v>
+      </c>
+      <c r="K952" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="953" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A953" s="2"/>
+      <c r="B953" s="2"/>
+      <c r="C953" s="2"/>
+      <c r="D953" s="2"/>
+      <c r="E953" s="3"/>
+      <c r="F953" s="2"/>
+      <c r="G953" t="s">
+        <v>648</v>
+      </c>
+      <c r="H953" t="s">
+        <v>55</v>
+      </c>
+      <c r="I953">
+        <v>2</v>
+      </c>
+      <c r="J953" t="s">
+        <v>153</v>
+      </c>
+      <c r="K953" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="954" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A954" s="2"/>
+      <c r="B954" s="2"/>
+      <c r="C954" s="2"/>
+      <c r="D954" s="2"/>
+      <c r="E954" s="3"/>
+      <c r="F954" s="2"/>
+      <c r="G954" t="s">
+        <v>649</v>
+      </c>
+      <c r="H954" t="s">
+        <v>55</v>
+      </c>
+      <c r="I954">
+        <v>3</v>
+      </c>
+      <c r="J954" t="s">
+        <v>153</v>
+      </c>
+      <c r="K954" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="955" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A955" s="2"/>
+      <c r="B955" s="2"/>
+      <c r="C955" s="2"/>
+      <c r="D955" s="2"/>
+      <c r="E955" s="3"/>
+      <c r="F955" s="2"/>
+      <c r="G955" t="s">
+        <v>650</v>
+      </c>
+      <c r="H955" t="s">
+        <v>55</v>
+      </c>
+      <c r="I955">
+        <v>3</v>
+      </c>
+      <c r="J955" t="s">
+        <v>153</v>
+      </c>
+      <c r="K955" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="956" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A956" s="2"/>
+      <c r="B956" s="2"/>
+      <c r="C956" s="2"/>
+      <c r="D956" s="2"/>
+      <c r="E956" s="3"/>
+      <c r="F956" s="2"/>
+      <c r="G956" t="s">
+        <v>651</v>
+      </c>
+      <c r="H956" t="s">
+        <v>17</v>
+      </c>
+      <c r="I956">
+        <v>8</v>
+      </c>
+      <c r="J956" t="s">
+        <v>153</v>
+      </c>
+      <c r="K956" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="957" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A957" s="2"/>
+      <c r="B957" s="2"/>
+      <c r="C957" s="2"/>
+      <c r="D957" s="2"/>
+      <c r="E957" s="3"/>
+      <c r="F957" s="2"/>
+      <c r="G957" t="s">
+        <v>652</v>
+      </c>
+      <c r="H957" t="s">
+        <v>17</v>
+      </c>
+      <c r="I957">
+        <v>4</v>
+      </c>
+      <c r="J957" t="s">
+        <v>153</v>
+      </c>
+      <c r="K957" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="958" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A958" s="2"/>
+      <c r="B958" s="2"/>
+      <c r="C958" s="2"/>
+      <c r="D958" s="2"/>
+      <c r="E958" s="3"/>
+      <c r="F958" s="2"/>
+      <c r="G958" t="s">
+        <v>653</v>
+      </c>
+      <c r="H958" t="s">
+        <v>17</v>
+      </c>
+      <c r="I958">
+        <v>4</v>
+      </c>
+      <c r="J958" t="s">
+        <v>153</v>
+      </c>
+      <c r="K958" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="959" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A959" s="2"/>
+      <c r="B959" s="2"/>
+      <c r="C959" s="2"/>
+      <c r="D959" s="2"/>
+      <c r="E959" s="3"/>
+      <c r="F959" s="2"/>
+      <c r="G959" t="s">
+        <v>654</v>
+      </c>
+      <c r="H959" t="s">
+        <v>55</v>
+      </c>
+      <c r="I959">
+        <v>2</v>
+      </c>
+      <c r="J959" t="s">
+        <v>153</v>
+      </c>
+      <c r="K959" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="960" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A960" s="2"/>
+      <c r="B960" s="2"/>
+      <c r="C960" s="2"/>
+      <c r="D960" s="2"/>
+      <c r="E960" s="3"/>
+      <c r="F960" s="2"/>
+      <c r="G960" t="s">
+        <v>655</v>
+      </c>
+      <c r="H960" t="s">
+        <v>55</v>
+      </c>
+      <c r="I960">
+        <v>1</v>
+      </c>
+      <c r="J960" t="s">
+        <v>153</v>
+      </c>
+      <c r="K960" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="961" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A961" s="2"/>
+      <c r="B961" s="2"/>
+      <c r="C961" s="2"/>
+      <c r="D961" s="2"/>
+      <c r="E961" s="3"/>
+      <c r="F961" s="2"/>
+      <c r="G961" t="s">
+        <v>656</v>
+      </c>
+      <c r="H961" t="s">
+        <v>17</v>
+      </c>
+      <c r="I961">
+        <v>3</v>
+      </c>
+      <c r="J961" t="s">
+        <v>153</v>
+      </c>
+      <c r="K961" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="962" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A962" s="2"/>
+      <c r="B962" s="2"/>
+      <c r="C962" s="2"/>
+      <c r="D962" s="2"/>
+      <c r="E962" s="3"/>
+      <c r="F962" s="2"/>
+      <c r="G962" t="s">
+        <v>657</v>
+      </c>
+      <c r="H962" t="s">
+        <v>17</v>
+      </c>
+      <c r="I962">
+        <v>2</v>
+      </c>
+      <c r="J962" t="s">
+        <v>153</v>
+      </c>
+      <c r="K962" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="963" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A963" s="2"/>
+      <c r="B963" s="2"/>
+      <c r="C963" s="2"/>
+      <c r="D963" s="2"/>
+      <c r="E963" s="3"/>
+      <c r="F963" s="2"/>
+      <c r="G963" t="s">
+        <v>658</v>
+      </c>
+      <c r="H963" t="s">
+        <v>17</v>
+      </c>
+      <c r="I963">
+        <v>2</v>
+      </c>
+      <c r="J963" t="s">
+        <v>153</v>
+      </c>
+      <c r="K963" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="964" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A964" s="2"/>
+      <c r="B964" s="2"/>
+      <c r="C964" s="2"/>
+      <c r="D964" s="2"/>
+      <c r="E964" s="3"/>
+      <c r="F964" s="2"/>
+      <c r="G964" t="s">
+        <v>659</v>
+      </c>
+      <c r="H964" t="s">
+        <v>55</v>
+      </c>
+      <c r="I964">
+        <v>6</v>
+      </c>
+      <c r="J964" t="s">
+        <v>153</v>
+      </c>
+      <c r="K964" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="965" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A965" s="2"/>
+      <c r="B965" s="2"/>
+      <c r="C965" s="2"/>
+      <c r="D965" s="2"/>
+      <c r="E965" s="3"/>
+      <c r="F965" s="2"/>
+      <c r="G965" t="s">
+        <v>660</v>
+      </c>
+      <c r="H965" t="s">
+        <v>55</v>
+      </c>
+      <c r="I965">
+        <v>2</v>
+      </c>
+      <c r="J965" t="s">
+        <v>153</v>
+      </c>
+      <c r="K965" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="966" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A966" s="2"/>
+      <c r="B966" s="2"/>
+      <c r="C966" s="2"/>
+      <c r="D966" s="2"/>
+      <c r="E966" s="3"/>
+      <c r="F966" s="2"/>
+      <c r="G966" t="s">
+        <v>661</v>
+      </c>
+      <c r="H966" t="s">
+        <v>17</v>
+      </c>
+      <c r="I966">
+        <v>9</v>
+      </c>
+      <c r="J966" t="s">
+        <v>153</v>
+      </c>
+      <c r="K966" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="967" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A967" s="2"/>
+      <c r="B967" s="2"/>
+      <c r="C967" s="2"/>
+      <c r="D967" s="2"/>
+      <c r="E967" s="3"/>
+      <c r="F967" s="2"/>
+      <c r="G967" t="s">
+        <v>662</v>
+      </c>
+      <c r="H967" t="s">
+        <v>17</v>
+      </c>
+      <c r="I967">
+        <v>4</v>
+      </c>
+      <c r="J967" t="s">
+        <v>153</v>
+      </c>
+      <c r="K967" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="968" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A968" s="2"/>
+      <c r="B968" s="2"/>
+      <c r="C968" s="2"/>
+      <c r="D968" s="2"/>
+      <c r="E968" s="3"/>
+      <c r="F968" s="2"/>
+      <c r="G968" t="s">
+        <v>663</v>
+      </c>
+      <c r="H968" t="s">
+        <v>17</v>
+      </c>
+      <c r="I968">
+        <v>2</v>
+      </c>
+      <c r="J968" t="s">
+        <v>153</v>
+      </c>
+      <c r="K968" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="969" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A969" s="2"/>
+      <c r="B969" s="2"/>
+      <c r="C969" s="2"/>
+      <c r="D969" s="2"/>
+      <c r="E969" s="3"/>
+      <c r="F969" s="2"/>
+      <c r="G969" t="s">
+        <v>664</v>
+      </c>
+      <c r="H969" t="s">
+        <v>55</v>
+      </c>
+      <c r="I969">
+        <v>2</v>
+      </c>
+      <c r="J969" t="s">
+        <v>153</v>
+      </c>
+      <c r="K969" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="970" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A970" s="2"/>
+      <c r="B970" s="2"/>
+      <c r="C970" s="2"/>
+      <c r="D970" s="2"/>
+      <c r="E970" s="3"/>
+      <c r="F970" s="2"/>
+      <c r="G970" t="s">
+        <v>665</v>
+      </c>
+      <c r="H970" t="s">
+        <v>55</v>
+      </c>
+      <c r="I970">
+        <v>2</v>
+      </c>
+      <c r="J970" t="s">
+        <v>153</v>
+      </c>
+      <c r="K970" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="971" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A971" s="2"/>
+      <c r="B971" s="2"/>
+      <c r="C971" s="2"/>
+      <c r="D971" s="2"/>
+      <c r="E971" s="3"/>
+      <c r="F971" s="2"/>
+      <c r="G971" t="s">
+        <v>666</v>
+      </c>
+      <c r="H971" t="s">
+        <v>55</v>
+      </c>
+      <c r="I971">
+        <v>1</v>
+      </c>
+      <c r="J971" t="s">
+        <v>153</v>
+      </c>
+      <c r="K971" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="972" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A972" s="2"/>
+      <c r="B972" s="2"/>
+      <c r="C972" s="2"/>
+      <c r="D972" s="2"/>
+      <c r="E972" s="3"/>
+      <c r="F972" s="2"/>
+      <c r="G972" t="s">
+        <v>667</v>
+      </c>
+      <c r="H972" t="s">
+        <v>55</v>
+      </c>
+      <c r="I972">
+        <v>1</v>
+      </c>
+      <c r="J972" t="s">
+        <v>153</v>
+      </c>
+      <c r="K972" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="973" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A973" s="2"/>
+      <c r="B973" s="2"/>
+      <c r="C973" s="2"/>
+      <c r="D973" s="2"/>
+      <c r="E973" s="3"/>
+      <c r="F973" s="2"/>
+      <c r="G973" t="s">
+        <v>668</v>
+      </c>
+      <c r="H973" t="s">
+        <v>55</v>
+      </c>
+      <c r="I973">
+        <v>1</v>
+      </c>
+      <c r="J973" t="s">
+        <v>153</v>
+      </c>
+      <c r="K973" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="974" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A974" s="2"/>
+      <c r="B974" s="2"/>
+      <c r="C974" s="2"/>
+      <c r="D974" s="2"/>
+      <c r="E974" s="3"/>
+      <c r="F974" s="2"/>
+      <c r="G974" t="s">
+        <v>669</v>
+      </c>
+      <c r="H974" t="s">
+        <v>55</v>
+      </c>
+      <c r="I974">
+        <v>2</v>
+      </c>
+      <c r="J974" t="s">
+        <v>153</v>
+      </c>
+      <c r="K974" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="975" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A975" s="2"/>
+      <c r="B975" s="2"/>
+      <c r="C975" s="2"/>
+      <c r="D975" s="2"/>
+      <c r="E975" s="3"/>
+      <c r="F975" s="2"/>
+      <c r="G975" t="s">
+        <v>670</v>
+      </c>
+      <c r="H975" t="s">
+        <v>55</v>
+      </c>
+      <c r="I975">
+        <v>1</v>
+      </c>
+      <c r="J975" t="s">
+        <v>153</v>
+      </c>
+      <c r="K975" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="976" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A976" s="2"/>
+      <c r="B976" s="2"/>
+      <c r="C976" s="2"/>
+      <c r="D976" s="2"/>
+      <c r="E976" s="3"/>
+      <c r="F976" s="2"/>
+      <c r="G976" t="s">
+        <v>671</v>
+      </c>
+      <c r="H976" t="s">
+        <v>55</v>
+      </c>
+      <c r="I976">
+        <v>2</v>
+      </c>
+      <c r="J976" t="s">
+        <v>153</v>
+      </c>
+      <c r="K976" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="977" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A977" s="2"/>
+      <c r="B977" s="2"/>
+      <c r="C977" s="2"/>
+      <c r="D977" s="2"/>
+      <c r="E977" s="3"/>
+      <c r="F977" s="2"/>
+      <c r="G977" t="s">
+        <v>672</v>
+      </c>
+      <c r="H977" t="s">
+        <v>55</v>
+      </c>
+      <c r="I977">
+        <v>1</v>
+      </c>
+      <c r="J977" t="s">
+        <v>153</v>
+      </c>
+      <c r="K977" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="978" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A978" s="2"/>
+      <c r="B978" s="2"/>
+      <c r="C978" s="2"/>
+      <c r="D978" s="2"/>
+      <c r="E978" s="3"/>
+      <c r="F978" s="2"/>
+      <c r="G978" t="s">
+        <v>673</v>
+      </c>
+      <c r="H978" t="s">
+        <v>17</v>
+      </c>
+      <c r="I978">
+        <v>5</v>
+      </c>
+      <c r="J978" t="s">
+        <v>153</v>
+      </c>
+      <c r="K978" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="979" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A979" s="2"/>
+      <c r="B979" s="2"/>
+      <c r="C979" s="2"/>
+      <c r="D979" s="2"/>
+      <c r="E979" s="3"/>
+      <c r="F979" s="2"/>
+      <c r="G979" t="s">
+        <v>111</v>
+      </c>
+      <c r="H979" t="s">
+        <v>55</v>
+      </c>
+      <c r="I979">
+        <v>1</v>
+      </c>
+      <c r="J979" t="s">
+        <v>153</v>
+      </c>
+      <c r="K979" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="980" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A980" s="2"/>
+      <c r="B980" s="2"/>
+      <c r="C980" s="2"/>
+      <c r="D980" s="2"/>
+      <c r="E980" s="3"/>
+      <c r="F980" s="2"/>
+      <c r="G980" t="s">
+        <v>674</v>
+      </c>
+      <c r="H980" t="s">
+        <v>55</v>
+      </c>
+      <c r="I980">
+        <v>1</v>
+      </c>
+      <c r="J980" t="s">
+        <v>153</v>
+      </c>
+      <c r="K980" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="981" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A981" s="2"/>
+      <c r="B981" s="2"/>
+      <c r="C981" s="2"/>
+      <c r="D981" s="2"/>
+      <c r="E981" s="3"/>
+      <c r="F981" s="2"/>
+      <c r="G981" t="s">
+        <v>675</v>
+      </c>
+      <c r="H981" t="s">
+        <v>55</v>
+      </c>
+      <c r="I981">
+        <v>1</v>
+      </c>
+      <c r="J981" t="s">
+        <v>153</v>
+      </c>
+      <c r="K981" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="982" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A982" s="2"/>
+      <c r="B982" s="2"/>
+      <c r="C982" s="2"/>
+      <c r="D982" s="2"/>
+      <c r="E982" s="3"/>
+      <c r="F982" s="2"/>
+      <c r="G982" t="s">
+        <v>252</v>
+      </c>
+      <c r="H982" t="s">
+        <v>55</v>
+      </c>
+      <c r="I982">
+        <v>1</v>
+      </c>
+      <c r="J982" t="s">
+        <v>153</v>
+      </c>
+      <c r="K982" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="983" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A983" s="2"/>
+      <c r="B983" s="2"/>
+      <c r="C983" s="2"/>
+      <c r="D983" s="2"/>
+      <c r="E983" s="3"/>
+      <c r="F983" s="2"/>
+      <c r="G983" t="s">
+        <v>676</v>
+      </c>
+      <c r="H983" t="s">
+        <v>55</v>
+      </c>
+      <c r="I983">
+        <v>3</v>
+      </c>
+      <c r="J983" t="s">
+        <v>153</v>
+      </c>
+      <c r="K983" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="984" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A984" s="2"/>
+      <c r="B984" s="2"/>
+      <c r="C984" s="2"/>
+      <c r="D984" s="2"/>
+      <c r="E984" s="3"/>
+      <c r="F984" s="2"/>
+      <c r="G984" t="s">
+        <v>677</v>
+      </c>
+      <c r="H984" t="s">
+        <v>55</v>
+      </c>
+      <c r="I984">
+        <v>3</v>
+      </c>
+      <c r="J984" t="s">
+        <v>153</v>
+      </c>
+      <c r="K984" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="985" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A985" s="2"/>
+      <c r="B985" s="2"/>
+      <c r="C985" s="2"/>
+      <c r="D985" s="2"/>
+      <c r="E985" s="3"/>
+      <c r="F985" s="2"/>
+      <c r="G985" t="s">
+        <v>678</v>
+      </c>
+      <c r="H985" t="s">
+        <v>17</v>
+      </c>
+      <c r="I985">
+        <v>10</v>
+      </c>
+      <c r="J985" t="s">
+        <v>153</v>
+      </c>
+      <c r="K985" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="986" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A986" s="2"/>
+      <c r="B986" s="2"/>
+      <c r="C986" s="2"/>
+      <c r="D986" s="2"/>
+      <c r="E986" s="3"/>
+      <c r="F986" s="2"/>
+      <c r="G986" t="s">
+        <v>679</v>
+      </c>
+      <c r="H986" t="s">
+        <v>76</v>
+      </c>
+      <c r="I986">
+        <v>10</v>
+      </c>
+      <c r="J986" t="s">
+        <v>153</v>
+      </c>
+      <c r="K986" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="987" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A987" s="2"/>
+      <c r="B987" s="2"/>
+      <c r="C987" s="2"/>
+      <c r="D987" s="2"/>
+      <c r="E987" s="3"/>
+      <c r="F987" s="2"/>
+      <c r="G987" t="s">
+        <v>680</v>
+      </c>
+      <c r="H987" t="s">
+        <v>76</v>
+      </c>
+      <c r="I987">
+        <v>2</v>
+      </c>
+      <c r="J987" t="s">
+        <v>153</v>
+      </c>
+      <c r="K987" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="989" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A989" s="2">
+        <v>51</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C989" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D989" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E989" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F989" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="G989" t="s">
+        <v>683</v>
+      </c>
+      <c r="H989" t="s">
+        <v>55</v>
+      </c>
+      <c r="I989">
+        <v>3</v>
+      </c>
+      <c r="J989" t="s">
+        <v>153</v>
+      </c>
+      <c r="K989" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="990" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A990" s="2"/>
+      <c r="B990" s="2"/>
+      <c r="C990" s="2"/>
+      <c r="D990" s="2"/>
+      <c r="E990" s="3"/>
+      <c r="F990" s="2"/>
+      <c r="G990" t="s">
+        <v>219</v>
+      </c>
+      <c r="H990" t="s">
+        <v>55</v>
+      </c>
+      <c r="I990">
+        <v>6</v>
+      </c>
+      <c r="J990" t="s">
+        <v>153</v>
+      </c>
+      <c r="K990" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="992" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A992" s="2">
+        <v>52</v>
+      </c>
+      <c r="B992" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="C992" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D992" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E992" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F992" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="G992" t="s">
+        <v>426</v>
+      </c>
+      <c r="H992" t="s">
+        <v>17</v>
+      </c>
+      <c r="I992">
+        <v>1</v>
+      </c>
+      <c r="J992" t="s">
+        <v>153</v>
+      </c>
+      <c r="K992" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="993" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A993" s="2"/>
+      <c r="B993" s="2"/>
+      <c r="C993" s="2"/>
+      <c r="D993" s="2"/>
+      <c r="E993" s="3"/>
+      <c r="F993" s="2"/>
+      <c r="G993" t="s">
+        <v>686</v>
+      </c>
+      <c r="H993" t="s">
+        <v>55</v>
+      </c>
+      <c r="I993">
+        <v>1</v>
+      </c>
+      <c r="J993" t="s">
+        <v>153</v>
+      </c>
+      <c r="K993" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="994" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A994" s="2"/>
+      <c r="B994" s="2"/>
+      <c r="C994" s="2"/>
+      <c r="D994" s="2"/>
+      <c r="E994" s="3"/>
+      <c r="F994" s="2"/>
+      <c r="G994" t="s">
+        <v>243</v>
+      </c>
+      <c r="H994" t="s">
+        <v>17</v>
+      </c>
+      <c r="I994">
+        <v>1</v>
+      </c>
+      <c r="J994" t="s">
+        <v>153</v>
+      </c>
+      <c r="K994" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="995" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A995" s="2"/>
+      <c r="B995" s="2"/>
+      <c r="C995" s="2"/>
+      <c r="D995" s="2"/>
+      <c r="E995" s="3"/>
+      <c r="F995" s="2"/>
+      <c r="G995" t="s">
+        <v>687</v>
+      </c>
+      <c r="H995" t="s">
+        <v>55</v>
+      </c>
+      <c r="I995">
+        <v>1</v>
+      </c>
+      <c r="J995" t="s">
+        <v>153</v>
+      </c>
+      <c r="K995" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="996" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A996" s="2"/>
+      <c r="B996" s="2"/>
+      <c r="C996" s="2"/>
+      <c r="D996" s="2"/>
+      <c r="E996" s="3"/>
+      <c r="F996" s="2"/>
+      <c r="G996" t="s">
+        <v>688</v>
+      </c>
+      <c r="H996" t="s">
+        <v>17</v>
+      </c>
+      <c r="I996">
+        <v>1</v>
+      </c>
+      <c r="J996" t="s">
+        <v>153</v>
+      </c>
+      <c r="K996" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="997" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A997" s="2"/>
+      <c r="B997" s="2"/>
+      <c r="C997" s="2"/>
+      <c r="D997" s="2"/>
+      <c r="E997" s="3"/>
+      <c r="F997" s="2"/>
+      <c r="G997" t="s">
+        <v>356</v>
+      </c>
+      <c r="H997" t="s">
+        <v>17</v>
+      </c>
+      <c r="I997">
+        <v>1</v>
+      </c>
+      <c r="J997" t="s">
+        <v>153</v>
+      </c>
+      <c r="K997" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="998" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A998" s="2"/>
+      <c r="B998" s="2"/>
+      <c r="C998" s="2"/>
+      <c r="D998" s="2"/>
+      <c r="E998" s="3"/>
+      <c r="F998" s="2"/>
+      <c r="G998" t="s">
+        <v>391</v>
+      </c>
+      <c r="H998" t="s">
+        <v>55</v>
+      </c>
+      <c r="I998">
+        <v>2</v>
+      </c>
+      <c r="J998" t="s">
+        <v>153</v>
+      </c>
+      <c r="K998" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="999" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A999" s="2"/>
+      <c r="B999" s="2"/>
+      <c r="C999" s="2"/>
+      <c r="D999" s="2"/>
+      <c r="E999" s="3"/>
+      <c r="F999" s="2"/>
+      <c r="G999" t="s">
+        <v>689</v>
+      </c>
+      <c r="H999" t="s">
+        <v>17</v>
+      </c>
+      <c r="I999">
+        <v>1</v>
+      </c>
+      <c r="J999" t="s">
+        <v>153</v>
+      </c>
+      <c r="K999" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1000" s="2"/>
+      <c r="B1000" s="2"/>
+      <c r="C1000" s="2"/>
+      <c r="D1000" s="2"/>
+      <c r="E1000" s="3"/>
+      <c r="F1000" s="2"/>
+      <c r="G1000" t="s">
+        <v>690</v>
+      </c>
+      <c r="H1000" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1000">
+        <v>1</v>
+      </c>
+      <c r="J1000" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1000" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1001" s="2"/>
+      <c r="B1001" s="2"/>
+      <c r="C1001" s="2"/>
+      <c r="D1001" s="2"/>
+      <c r="E1001" s="3"/>
+      <c r="F1001" s="2"/>
+      <c r="G1001" t="s">
+        <v>219</v>
+      </c>
+      <c r="H1001" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1001">
+        <v>4</v>
+      </c>
+      <c r="J1001" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1001" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1002" s="2"/>
+      <c r="B1002" s="2"/>
+      <c r="C1002" s="2"/>
+      <c r="D1002" s="2"/>
+      <c r="E1002" s="3"/>
+      <c r="F1002" s="2"/>
+      <c r="G1002" t="s">
+        <v>691</v>
+      </c>
+      <c r="H1002" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1002">
+        <v>4</v>
+      </c>
+      <c r="J1002" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1002" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1003" s="2"/>
+      <c r="B1003" s="2"/>
+      <c r="C1003" s="2"/>
+      <c r="D1003" s="2"/>
+      <c r="E1003" s="3"/>
+      <c r="F1003" s="2"/>
+      <c r="G1003" t="s">
+        <v>400</v>
+      </c>
+      <c r="H1003" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1003">
+        <v>4</v>
+      </c>
+      <c r="J1003" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1003" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1004" s="2"/>
+      <c r="B1004" s="2"/>
+      <c r="C1004" s="2"/>
+      <c r="D1004" s="2"/>
+      <c r="E1004" s="3"/>
+      <c r="F1004" s="2"/>
+      <c r="G1004" t="s">
+        <v>401</v>
+      </c>
+      <c r="H1004" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1004">
+        <v>6</v>
+      </c>
+      <c r="J1004" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1004" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1006" s="2">
+        <v>53</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C1006" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1006" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1006" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1006" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="G1006" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1006" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1006">
+        <v>2</v>
+      </c>
+      <c r="J1006" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1006" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1007" s="2"/>
+      <c r="B1007" s="2"/>
+      <c r="C1007" s="2"/>
+      <c r="D1007" s="2"/>
+      <c r="E1007" s="3"/>
+      <c r="F1007" s="2"/>
+      <c r="G1007" t="s">
+        <v>105</v>
+      </c>
+      <c r="H1007" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1007">
+        <v>2</v>
+      </c>
+      <c r="J1007" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1007" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1008" s="2"/>
+      <c r="B1008" s="2"/>
+      <c r="C1008" s="2"/>
+      <c r="D1008" s="2"/>
+      <c r="E1008" s="3"/>
+      <c r="F1008" s="2"/>
+      <c r="G1008" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1008" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1008">
+        <v>2</v>
+      </c>
+      <c r="J1008" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1008" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1009" s="2"/>
+      <c r="B1009" s="2"/>
+      <c r="C1009" s="2"/>
+      <c r="D1009" s="2"/>
+      <c r="E1009" s="3"/>
+      <c r="F1009" s="2"/>
+      <c r="G1009" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1009" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1009">
+        <v>4</v>
+      </c>
+      <c r="J1009" t="s">
+        <v>153</v>
+      </c>
+      <c r="K1009" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="216">
+  <mergeCells count="306">
     <mergeCell ref="A2:A27"/>
     <mergeCell ref="B2:B27"/>
     <mergeCell ref="C2:C27"/>
@@ -18582,6 +25380,96 @@
     <mergeCell ref="D651:D729"/>
     <mergeCell ref="E651:E729"/>
     <mergeCell ref="F651:F729"/>
+    <mergeCell ref="A733:A751"/>
+    <mergeCell ref="B733:B751"/>
+    <mergeCell ref="C733:C751"/>
+    <mergeCell ref="D733:D751"/>
+    <mergeCell ref="E733:E751"/>
+    <mergeCell ref="F733:F751"/>
+    <mergeCell ref="A753:A769"/>
+    <mergeCell ref="B753:B769"/>
+    <mergeCell ref="C753:C769"/>
+    <mergeCell ref="D753:D769"/>
+    <mergeCell ref="E753:E769"/>
+    <mergeCell ref="F753:F769"/>
+    <mergeCell ref="A771:A784"/>
+    <mergeCell ref="B771:B784"/>
+    <mergeCell ref="C771:C784"/>
+    <mergeCell ref="D771:D784"/>
+    <mergeCell ref="E771:E784"/>
+    <mergeCell ref="F771:F784"/>
+    <mergeCell ref="A786:A791"/>
+    <mergeCell ref="B786:B791"/>
+    <mergeCell ref="C786:C791"/>
+    <mergeCell ref="D786:D791"/>
+    <mergeCell ref="E786:E791"/>
+    <mergeCell ref="F786:F791"/>
+    <mergeCell ref="A793:A804"/>
+    <mergeCell ref="B793:B804"/>
+    <mergeCell ref="C793:C804"/>
+    <mergeCell ref="D793:D804"/>
+    <mergeCell ref="E793:E804"/>
+    <mergeCell ref="F793:F804"/>
+    <mergeCell ref="A806:A848"/>
+    <mergeCell ref="B806:B848"/>
+    <mergeCell ref="C806:C848"/>
+    <mergeCell ref="D806:D848"/>
+    <mergeCell ref="E806:E848"/>
+    <mergeCell ref="F806:F848"/>
+    <mergeCell ref="A850:A890"/>
+    <mergeCell ref="B850:B890"/>
+    <mergeCell ref="C850:C890"/>
+    <mergeCell ref="D850:D890"/>
+    <mergeCell ref="E850:E890"/>
+    <mergeCell ref="F850:F890"/>
+    <mergeCell ref="A892:A904"/>
+    <mergeCell ref="B892:B904"/>
+    <mergeCell ref="C892:C904"/>
+    <mergeCell ref="D892:D904"/>
+    <mergeCell ref="E892:E904"/>
+    <mergeCell ref="F892:F904"/>
+    <mergeCell ref="A906:A917"/>
+    <mergeCell ref="B906:B917"/>
+    <mergeCell ref="C906:C917"/>
+    <mergeCell ref="D906:D917"/>
+    <mergeCell ref="E906:E917"/>
+    <mergeCell ref="F906:F917"/>
+    <mergeCell ref="A919:A923"/>
+    <mergeCell ref="B919:B923"/>
+    <mergeCell ref="C919:C923"/>
+    <mergeCell ref="D919:D923"/>
+    <mergeCell ref="E919:E923"/>
+    <mergeCell ref="F919:F923"/>
+    <mergeCell ref="A925:A930"/>
+    <mergeCell ref="B925:B930"/>
+    <mergeCell ref="C925:C930"/>
+    <mergeCell ref="D925:D930"/>
+    <mergeCell ref="E925:E930"/>
+    <mergeCell ref="F925:F930"/>
+    <mergeCell ref="A932:A987"/>
+    <mergeCell ref="B932:B987"/>
+    <mergeCell ref="C932:C987"/>
+    <mergeCell ref="D932:D987"/>
+    <mergeCell ref="E932:E987"/>
+    <mergeCell ref="F932:F987"/>
+    <mergeCell ref="A989:A990"/>
+    <mergeCell ref="B989:B990"/>
+    <mergeCell ref="C989:C990"/>
+    <mergeCell ref="D989:D990"/>
+    <mergeCell ref="E989:E990"/>
+    <mergeCell ref="F989:F990"/>
+    <mergeCell ref="A992:A1004"/>
+    <mergeCell ref="B992:B1004"/>
+    <mergeCell ref="C992:C1004"/>
+    <mergeCell ref="D992:D1004"/>
+    <mergeCell ref="E992:E1004"/>
+    <mergeCell ref="F992:F1004"/>
+    <mergeCell ref="A1006:A1009"/>
+    <mergeCell ref="B1006:B1009"/>
+    <mergeCell ref="C1006:C1009"/>
+    <mergeCell ref="D1006:D1009"/>
+    <mergeCell ref="E1006:E1009"/>
+    <mergeCell ref="F1006:F1009"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
